--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bescheinigungen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BG-Liste" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lehrgangsdoku" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hilfslisten" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Teilnehmer'!$10:$10</definedName>
+    <definedName name="Lehrkraefte">Hilfslisten!$A$2:$A$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,13 +26,24 @@
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="165" formatCode="HH:MM"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -48,17 +60,6 @@
     <font>
       <name val="Calibri"/>
       <color rgb="000F3460"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00333333"/>
       <sz val="11"/>
     </font>
     <font>
@@ -96,24 +97,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="22"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00000000"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="16"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -245,6 +235,9 @@
       </bottom>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="0070D2A6"/>
+      </left>
       <right style="medium">
         <color rgb="0070D2A6"/>
       </right>
@@ -259,51 +252,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -345,44 +338,68 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -390,32 +407,14 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -423,11 +422,6 @@
           <bgColor rgb="00FFCDD2"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="00FFFFFF"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1138,7 +1132,7 @@
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B11:C30">
+  <conditionalFormatting sqref="B11:B30">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($B11="",$C11&lt;&gt;"")</formula>
     </cfRule>
@@ -1148,12 +1142,9 @@
       <formula>AND($C11="",$B11&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültiges Datum" error="Bitte ein gültiges Datum eingeben." type="date" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Putschler, Walter,Kaya, Michelle,Krempl, Elke,Breig, Bernd,Zuber, Harry,Jochim, Benjamin,Siebert, Emanuel"</formula1>
+      <formula1>=Lehrkraefte</formula1>
     </dataValidation>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EH-Ausbildung,EH-Fortbildung,EH-Schulung"</formula1>
@@ -1174,34 +1165,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y298"/>
+  <dimension ref="A2:O298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="1" customWidth="1" min="1" max="1"/>
-    <col width="5.5" customWidth="1" min="2" max="2"/>
-    <col width="5.5" customWidth="1" min="3" max="3"/>
-    <col width="5.5" customWidth="1" min="4" max="4"/>
-    <col width="4.5" customWidth="1" min="5" max="5"/>
-    <col width="4.5" customWidth="1" min="6" max="6"/>
-    <col width="4.5" customWidth="1" min="7" max="7"/>
-    <col width="5.5" customWidth="1" min="8" max="8"/>
-    <col width="4" customWidth="1" min="9" max="9"/>
-    <col width="4" customWidth="1" min="10" max="10"/>
-    <col width="4" customWidth="1" min="11" max="11"/>
-    <col width="1" customWidth="1" min="12" max="12"/>
-    <col width="1.5" customWidth="1" min="13" max="13"/>
-    <col width="1" customWidth="1" min="14" max="14"/>
-    <col width="5.5" customWidth="1" min="15" max="15"/>
-    <col width="5.5" customWidth="1" min="16" max="16"/>
-    <col width="5.5" customWidth="1" min="17" max="17"/>
-    <col width="4.5" customWidth="1" min="18" max="18"/>
-    <col width="4.5" customWidth="1" min="19" max="19"/>
-    <col width="4.5" customWidth="1" min="20" max="20"/>
-    <col width="5.5" customWidth="1" min="21" max="21"/>
-    <col width="4" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="1" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1"/>
@@ -1210,54 +1191,54 @@
         <f>IF(Teilnehmer!B11&lt;&gt;"",Teilnehmer!B11,"")</f>
         <v/>
       </c>
-      <c r="E2" s="17">
+      <c r="C2" s="17">
         <f>IF(Teilnehmer!B11&lt;&gt;"",Teilnehmer!C11,"")</f>
         <v/>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I2" s="19">
+      <c r="F2" s="19">
         <f>IF(Teilnehmer!B11&lt;&gt;"",Teilnehmer!D11,"")</f>
         <v/>
       </c>
-      <c r="N2" s="17">
+      <c r="I2" s="17">
         <f>IF(Teilnehmer!B12&lt;&gt;"",Teilnehmer!B12,"")</f>
         <v/>
       </c>
-      <c r="R2" s="17">
+      <c r="K2" s="17">
         <f>IF(Teilnehmer!B12&lt;&gt;"",Teilnehmer!C12,"")</f>
         <v/>
       </c>
-      <c r="U2" s="18" t="inlineStr">
+      <c r="M2" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V2" s="19">
+      <c r="N2" s="19">
         <f>IF(Teilnehmer!B12&lt;&gt;"",Teilnehmer!D12,"")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="20" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O3" s="20" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S3" s="20" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -1270,7 +1251,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -1287,57 +1268,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G7" s="24">
+      <c r="D7" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I7" s="24">
+      <c r="F7" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N7" s="22" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O7" s="19">
+      <c r="J7" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q7" s="23" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T7" s="24">
+      <c r="L7" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U7" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V7" s="24">
+      <c r="N7" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W7" s="22" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -1350,25 +1331,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E9" s="25">
+      <c r="C9" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K9" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N9" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R9" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V9" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -1381,37 +1362,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N11" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T11" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U11" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W11" s="22" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -1425,26 +1406,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E14" s="19">
+      <c r="C14" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R14" s="19">
+      <c r="K14" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -1455,27 +1436,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R15" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U15" s="20" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -1484,12 +1465,12 @@
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="H18" s="20" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U18" s="20" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -1502,17 +1483,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N20" s="22" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S20" s="27" t="inlineStr">
+      <c r="L20" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -1525,7 +1506,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N22" s="22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -1537,17 +1518,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N23" s="22" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -1560,16 +1541,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F25" s="27">
+      <c r="E25" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N25" s="22" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S25" s="27">
+      <c r="M25" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -1581,7 +1562,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N27" s="28" t="inlineStr">
+      <c r="I27" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -1593,7 +1574,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N28" s="28" t="inlineStr">
+      <c r="I28" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -1607,54 +1588,54 @@
         <f>IF(Teilnehmer!B13&lt;&gt;"",Teilnehmer!B13,"")</f>
         <v/>
       </c>
-      <c r="E32" s="17">
+      <c r="C32" s="17">
         <f>IF(Teilnehmer!B13&lt;&gt;"",Teilnehmer!C13,"")</f>
         <v/>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I32" s="19">
+      <c r="F32" s="19">
         <f>IF(Teilnehmer!B13&lt;&gt;"",Teilnehmer!D13,"")</f>
         <v/>
       </c>
-      <c r="N32" s="17">
+      <c r="I32" s="17">
         <f>IF(Teilnehmer!B14&lt;&gt;"",Teilnehmer!B14,"")</f>
         <v/>
       </c>
-      <c r="R32" s="17">
+      <c r="K32" s="17">
         <f>IF(Teilnehmer!B14&lt;&gt;"",Teilnehmer!C14,"")</f>
         <v/>
       </c>
-      <c r="U32" s="18" t="inlineStr">
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V32" s="19">
+      <c r="N32" s="19">
         <f>IF(Teilnehmer!B14&lt;&gt;"",Teilnehmer!D14,"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="B33" s="20" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O33" s="20" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S33" s="20" t="inlineStr">
+      <c r="K33" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -1667,7 +1648,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N35" s="21" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -1684,57 +1665,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G37" s="24">
+      <c r="D37" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I37" s="24">
+      <c r="F37" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N37" s="22" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O37" s="19">
+      <c r="J37" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q37" s="23" t="inlineStr">
+      <c r="K37" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T37" s="24">
+      <c r="L37" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U37" s="23" t="inlineStr">
+      <c r="M37" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V37" s="24">
+      <c r="N37" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W37" s="22" t="inlineStr">
+      <c r="O37" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -1747,25 +1728,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E39" s="25">
+      <c r="C39" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I39" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K39" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N39" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R39" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V39" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -1778,37 +1759,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G41" s="26" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M41" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N41" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T41" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U41" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W41" s="22" t="inlineStr">
+      <c r="O41" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -1822,26 +1803,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="B44" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E44" s="19">
+      <c r="C44" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q44" s="22" t="inlineStr">
+      <c r="J44" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R44" s="19">
+      <c r="K44" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -1852,27 +1833,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R45" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U45" s="20" t="inlineStr">
+      <c r="M45" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -1881,12 +1862,12 @@
     <row r="46" ht="14.25" customHeight="1"/>
     <row r="47" ht="14.25" customHeight="1"/>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="H48" s="20" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U48" s="20" t="inlineStr">
+      <c r="M48" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -1899,17 +1880,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F50" s="27" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N50" s="22" t="inlineStr">
+      <c r="I50" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S50" s="27" t="inlineStr">
+      <c r="L50" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -1922,7 +1903,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N52" s="22" t="inlineStr">
+      <c r="I52" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -1934,17 +1915,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F53" s="27" t="inlineStr">
+      <c r="E53" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N53" s="22" t="inlineStr">
+      <c r="I53" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -1957,16 +1938,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F55" s="27">
+      <c r="E55" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N55" s="22" t="inlineStr">
+      <c r="I55" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S55" s="27">
+      <c r="M55" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -1978,7 +1959,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N57" s="28" t="inlineStr">
+      <c r="I57" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -1990,7 +1971,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N58" s="28" t="inlineStr">
+      <c r="I58" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -2004,54 +1985,54 @@
         <f>IF(Teilnehmer!B15&lt;&gt;"",Teilnehmer!B15,"")</f>
         <v/>
       </c>
-      <c r="E62" s="17">
+      <c r="C62" s="17">
         <f>IF(Teilnehmer!B15&lt;&gt;"",Teilnehmer!C15,"")</f>
         <v/>
       </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="E62" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I62" s="19">
+      <c r="F62" s="19">
         <f>IF(Teilnehmer!B15&lt;&gt;"",Teilnehmer!D15,"")</f>
         <v/>
       </c>
-      <c r="N62" s="17">
+      <c r="I62" s="17">
         <f>IF(Teilnehmer!B16&lt;&gt;"",Teilnehmer!B16,"")</f>
         <v/>
       </c>
-      <c r="R62" s="17">
+      <c r="K62" s="17">
         <f>IF(Teilnehmer!B16&lt;&gt;"",Teilnehmer!C16,"")</f>
         <v/>
       </c>
-      <c r="U62" s="18" t="inlineStr">
+      <c r="M62" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V62" s="19">
+      <c r="N62" s="19">
         <f>IF(Teilnehmer!B16&lt;&gt;"",Teilnehmer!D16,"")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="B63" s="20" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="C63" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O63" s="20" t="inlineStr">
+      <c r="I63" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S63" s="20" t="inlineStr">
+      <c r="K63" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -2064,7 +2045,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N65" s="21" t="inlineStr">
+      <c r="I65" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -2081,57 +2062,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D67" s="23" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G67" s="24">
+      <c r="D67" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H67" s="23" t="inlineStr">
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I67" s="24">
+      <c r="F67" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J67" s="22" t="inlineStr">
+      <c r="G67" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N67" s="22" t="inlineStr">
+      <c r="I67" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O67" s="19">
+      <c r="J67" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q67" s="23" t="inlineStr">
+      <c r="K67" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T67" s="24">
+      <c r="L67" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U67" s="23" t="inlineStr">
+      <c r="M67" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V67" s="24">
+      <c r="N67" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W67" s="22" t="inlineStr">
+      <c r="O67" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -2144,25 +2125,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E69" s="25">
+      <c r="C69" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I69" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K69" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N69" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R69" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V69" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -2175,37 +2156,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G71" s="26" t="inlineStr">
+      <c r="E71" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="F71" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J71" s="22" t="inlineStr">
+      <c r="G71" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M71" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N71" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T71" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U71" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W71" s="22" t="inlineStr">
+      <c r="O71" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -2219,26 +2200,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr">
+      <c r="B74" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E74" s="19">
+      <c r="C74" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="I74" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q74" s="22" t="inlineStr">
+      <c r="J74" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R74" s="19">
+      <c r="K74" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -2249,27 +2230,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I75" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K75" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H75" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R75" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U75" s="20" t="inlineStr">
+      <c r="M75" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -2278,12 +2259,12 @@
     <row r="76" ht="14.25" customHeight="1"/>
     <row r="77" ht="14.25" customHeight="1"/>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="H78" s="20" t="inlineStr">
+      <c r="E78" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U78" s="20" t="inlineStr">
+      <c r="M78" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -2296,17 +2277,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F80" s="27" t="inlineStr">
+      <c r="D80" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N80" s="22" t="inlineStr">
+      <c r="I80" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S80" s="27" t="inlineStr">
+      <c r="L80" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -2319,7 +2300,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N82" s="22" t="inlineStr">
+      <c r="I82" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -2331,17 +2312,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F83" s="27" t="inlineStr">
+      <c r="E83" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N83" s="22" t="inlineStr">
+      <c r="I83" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -2354,16 +2335,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F85" s="27">
+      <c r="E85" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N85" s="22" t="inlineStr">
+      <c r="I85" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S85" s="27">
+      <c r="M85" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -2375,7 +2356,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N87" s="28" t="inlineStr">
+      <c r="I87" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -2387,7 +2368,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N88" s="28" t="inlineStr">
+      <c r="I88" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -2401,54 +2382,54 @@
         <f>IF(Teilnehmer!B17&lt;&gt;"",Teilnehmer!B17,"")</f>
         <v/>
       </c>
-      <c r="E92" s="17">
+      <c r="C92" s="17">
         <f>IF(Teilnehmer!B17&lt;&gt;"",Teilnehmer!C17,"")</f>
         <v/>
       </c>
-      <c r="H92" s="18" t="inlineStr">
+      <c r="E92" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I92" s="19">
+      <c r="F92" s="19">
         <f>IF(Teilnehmer!B17&lt;&gt;"",Teilnehmer!D17,"")</f>
         <v/>
       </c>
-      <c r="N92" s="17">
+      <c r="I92" s="17">
         <f>IF(Teilnehmer!B18&lt;&gt;"",Teilnehmer!B18,"")</f>
         <v/>
       </c>
-      <c r="R92" s="17">
+      <c r="K92" s="17">
         <f>IF(Teilnehmer!B18&lt;&gt;"",Teilnehmer!C18,"")</f>
         <v/>
       </c>
-      <c r="U92" s="18" t="inlineStr">
+      <c r="M92" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V92" s="19">
+      <c r="N92" s="19">
         <f>IF(Teilnehmer!B18&lt;&gt;"",Teilnehmer!D18,"")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="B93" s="20" t="inlineStr">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
+      <c r="C93" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O93" s="20" t="inlineStr">
+      <c r="I93" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S93" s="20" t="inlineStr">
+      <c r="K93" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -2461,7 +2442,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N95" s="21" t="inlineStr">
+      <c r="I95" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -2478,57 +2459,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D97" s="23" t="inlineStr">
+      <c r="C97" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G97" s="24">
+      <c r="D97" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H97" s="23" t="inlineStr">
+      <c r="E97" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I97" s="24">
+      <c r="F97" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J97" s="22" t="inlineStr">
+      <c r="G97" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N97" s="22" t="inlineStr">
+      <c r="I97" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O97" s="19">
+      <c r="J97" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q97" s="23" t="inlineStr">
+      <c r="K97" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T97" s="24">
+      <c r="L97" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U97" s="23" t="inlineStr">
+      <c r="M97" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V97" s="24">
+      <c r="N97" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W97" s="22" t="inlineStr">
+      <c r="O97" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -2541,25 +2522,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E99" s="25">
+      <c r="C99" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I99" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K99" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N99" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R99" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V99" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -2572,37 +2553,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G101" s="26" t="inlineStr">
+      <c r="E101" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H101" s="22" t="inlineStr">
+      <c r="F101" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J101" s="22" t="inlineStr">
+      <c r="G101" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I101" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M101" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N101" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T101" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U101" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W101" s="22" t="inlineStr">
+      <c r="O101" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -2616,26 +2597,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D104" s="22" t="inlineStr">
+      <c r="B104" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E104" s="19">
+      <c r="C104" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="I104" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q104" s="22" t="inlineStr">
+      <c r="J104" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R104" s="19">
+      <c r="K104" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -2646,27 +2627,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C105" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I105" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K105" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H105" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N105" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R105" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U105" s="20" t="inlineStr">
+      <c r="M105" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -2675,12 +2656,12 @@
     <row r="106" ht="14.25" customHeight="1"/>
     <row r="107" ht="14.25" customHeight="1"/>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="H108" s="20" t="inlineStr">
+      <c r="E108" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U108" s="20" t="inlineStr">
+      <c r="M108" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -2693,17 +2674,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F110" s="27" t="inlineStr">
+      <c r="D110" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N110" s="22" t="inlineStr">
+      <c r="I110" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S110" s="27" t="inlineStr">
+      <c r="L110" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -2716,7 +2697,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N112" s="22" t="inlineStr">
+      <c r="I112" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -2728,17 +2709,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F113" s="27" t="inlineStr">
+      <c r="E113" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N113" s="22" t="inlineStr">
+      <c r="I113" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -2751,16 +2732,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F115" s="27">
+      <c r="E115" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N115" s="22" t="inlineStr">
+      <c r="I115" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S115" s="27">
+      <c r="M115" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -2772,7 +2753,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N117" s="28" t="inlineStr">
+      <c r="I117" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -2784,7 +2765,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N118" s="28" t="inlineStr">
+      <c r="I118" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -2798,54 +2779,54 @@
         <f>IF(Teilnehmer!B19&lt;&gt;"",Teilnehmer!B19,"")</f>
         <v/>
       </c>
-      <c r="E122" s="17">
+      <c r="C122" s="17">
         <f>IF(Teilnehmer!B19&lt;&gt;"",Teilnehmer!C19,"")</f>
         <v/>
       </c>
-      <c r="H122" s="18" t="inlineStr">
+      <c r="E122" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I122" s="19">
+      <c r="F122" s="19">
         <f>IF(Teilnehmer!B19&lt;&gt;"",Teilnehmer!D19,"")</f>
         <v/>
       </c>
-      <c r="N122" s="17">
+      <c r="I122" s="17">
         <f>IF(Teilnehmer!B20&lt;&gt;"",Teilnehmer!B20,"")</f>
         <v/>
       </c>
-      <c r="R122" s="17">
+      <c r="K122" s="17">
         <f>IF(Teilnehmer!B20&lt;&gt;"",Teilnehmer!C20,"")</f>
         <v/>
       </c>
-      <c r="U122" s="18" t="inlineStr">
+      <c r="M122" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V122" s="19">
+      <c r="N122" s="19">
         <f>IF(Teilnehmer!B20&lt;&gt;"",Teilnehmer!D20,"")</f>
         <v/>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="B123" s="20" t="inlineStr">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F123" s="20" t="inlineStr">
+      <c r="C123" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O123" s="20" t="inlineStr">
+      <c r="I123" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S123" s="20" t="inlineStr">
+      <c r="K123" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -2858,7 +2839,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N125" s="21" t="inlineStr">
+      <c r="I125" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -2875,57 +2856,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D127" s="23" t="inlineStr">
+      <c r="C127" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G127" s="24">
+      <c r="D127" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H127" s="23" t="inlineStr">
+      <c r="E127" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I127" s="24">
+      <c r="F127" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J127" s="22" t="inlineStr">
+      <c r="G127" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N127" s="22" t="inlineStr">
+      <c r="I127" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O127" s="19">
+      <c r="J127" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q127" s="23" t="inlineStr">
+      <c r="K127" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T127" s="24">
+      <c r="L127" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U127" s="23" t="inlineStr">
+      <c r="M127" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V127" s="24">
+      <c r="N127" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W127" s="22" t="inlineStr">
+      <c r="O127" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -2938,25 +2919,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E129" s="25">
+      <c r="C129" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F129" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I129" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K129" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N129" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R129" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V129" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -2969,37 +2950,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G131" s="26" t="inlineStr">
+      <c r="E131" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H131" s="22" t="inlineStr">
+      <c r="F131" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J131" s="22" t="inlineStr">
+      <c r="G131" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I131" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M131" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N131" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T131" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U131" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W131" s="22" t="inlineStr">
+      <c r="O131" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -3013,26 +2994,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D134" s="22" t="inlineStr">
+      <c r="B134" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E134" s="19">
+      <c r="C134" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N134" s="27" t="inlineStr">
+      <c r="I134" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q134" s="22" t="inlineStr">
+      <c r="J134" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R134" s="19">
+      <c r="K134" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -3043,27 +3024,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C135" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E135" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I135" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K135" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H135" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N135" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R135" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U135" s="20" t="inlineStr">
+      <c r="M135" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -3072,12 +3053,12 @@
     <row r="136" ht="14.25" customHeight="1"/>
     <row r="137" ht="14.25" customHeight="1"/>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="H138" s="20" t="inlineStr">
+      <c r="E138" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U138" s="20" t="inlineStr">
+      <c r="M138" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -3090,17 +3071,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F140" s="27" t="inlineStr">
+      <c r="D140" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N140" s="22" t="inlineStr">
+      <c r="I140" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S140" s="27" t="inlineStr">
+      <c r="L140" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -3113,7 +3094,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N142" s="22" t="inlineStr">
+      <c r="I142" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -3125,17 +3106,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F143" s="27" t="inlineStr">
+      <c r="E143" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N143" s="22" t="inlineStr">
+      <c r="I143" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S143" s="27" t="inlineStr">
+      <c r="M143" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -3148,16 +3129,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F145" s="27">
+      <c r="E145" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N145" s="22" t="inlineStr">
+      <c r="I145" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S145" s="27">
+      <c r="M145" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -3169,7 +3150,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N147" s="28" t="inlineStr">
+      <c r="I147" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -3181,7 +3162,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N148" s="28" t="inlineStr">
+      <c r="I148" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -3195,54 +3176,54 @@
         <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!B21,"")</f>
         <v/>
       </c>
-      <c r="E152" s="17">
+      <c r="C152" s="17">
         <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!C21,"")</f>
         <v/>
       </c>
-      <c r="H152" s="18" t="inlineStr">
+      <c r="E152" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I152" s="19">
+      <c r="F152" s="19">
         <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!D21,"")</f>
         <v/>
       </c>
-      <c r="N152" s="17">
+      <c r="I152" s="17">
         <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!B22,"")</f>
         <v/>
       </c>
-      <c r="R152" s="17">
+      <c r="K152" s="17">
         <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!C22,"")</f>
         <v/>
       </c>
-      <c r="U152" s="18" t="inlineStr">
+      <c r="M152" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V152" s="19">
+      <c r="N152" s="19">
         <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!D22,"")</f>
         <v/>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="B153" s="20" t="inlineStr">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F153" s="20" t="inlineStr">
+      <c r="C153" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O153" s="20" t="inlineStr">
+      <c r="I153" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S153" s="20" t="inlineStr">
+      <c r="K153" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -3255,7 +3236,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N155" s="21" t="inlineStr">
+      <c r="I155" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -3272,57 +3253,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D157" s="23" t="inlineStr">
+      <c r="C157" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G157" s="24">
+      <c r="D157" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H157" s="23" t="inlineStr">
+      <c r="E157" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I157" s="24">
+      <c r="F157" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J157" s="22" t="inlineStr">
+      <c r="G157" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N157" s="22" t="inlineStr">
+      <c r="I157" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O157" s="19">
+      <c r="J157" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q157" s="23" t="inlineStr">
+      <c r="K157" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T157" s="24">
+      <c r="L157" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U157" s="23" t="inlineStr">
+      <c r="M157" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V157" s="24">
+      <c r="N157" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W157" s="22" t="inlineStr">
+      <c r="O157" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -3335,25 +3316,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E159" s="25">
+      <c r="C159" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F159" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I159" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K159" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N159" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R159" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V159" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -3366,37 +3347,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G161" s="26" t="inlineStr">
+      <c r="E161" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H161" s="22" t="inlineStr">
+      <c r="F161" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J161" s="22" t="inlineStr">
+      <c r="G161" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I161" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M161" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N161" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T161" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U161" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W161" s="22" t="inlineStr">
+      <c r="O161" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -3410,26 +3391,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D164" s="22" t="inlineStr">
+      <c r="B164" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E164" s="19">
+      <c r="C164" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N164" s="27" t="inlineStr">
+      <c r="I164" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q164" s="22" t="inlineStr">
+      <c r="J164" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R164" s="19">
+      <c r="K164" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -3440,27 +3421,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C165" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E165" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I165" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K165" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H165" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N165" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R165" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U165" s="20" t="inlineStr">
+      <c r="M165" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -3469,12 +3450,12 @@
     <row r="166" ht="14.25" customHeight="1"/>
     <row r="167" ht="14.25" customHeight="1"/>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="H168" s="20" t="inlineStr">
+      <c r="E168" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U168" s="20" t="inlineStr">
+      <c r="M168" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -3487,17 +3468,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F170" s="27" t="inlineStr">
+      <c r="D170" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N170" s="22" t="inlineStr">
+      <c r="I170" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S170" s="27" t="inlineStr">
+      <c r="L170" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -3510,7 +3491,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N172" s="22" t="inlineStr">
+      <c r="I172" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -3522,17 +3503,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F173" s="27" t="inlineStr">
+      <c r="E173" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N173" s="22" t="inlineStr">
+      <c r="I173" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S173" s="27" t="inlineStr">
+      <c r="M173" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -3545,16 +3526,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F175" s="27">
+      <c r="E175" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N175" s="22" t="inlineStr">
+      <c r="I175" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S175" s="27">
+      <c r="M175" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -3566,7 +3547,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N177" s="28" t="inlineStr">
+      <c r="I177" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -3578,7 +3559,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N178" s="28" t="inlineStr">
+      <c r="I178" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -3592,54 +3573,54 @@
         <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!B23,"")</f>
         <v/>
       </c>
-      <c r="E182" s="17">
+      <c r="C182" s="17">
         <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!C23,"")</f>
         <v/>
       </c>
-      <c r="H182" s="18" t="inlineStr">
+      <c r="E182" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I182" s="19">
+      <c r="F182" s="19">
         <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!D23,"")</f>
         <v/>
       </c>
-      <c r="N182" s="17">
+      <c r="I182" s="17">
         <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!B24,"")</f>
         <v/>
       </c>
-      <c r="R182" s="17">
+      <c r="K182" s="17">
         <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!C24,"")</f>
         <v/>
       </c>
-      <c r="U182" s="18" t="inlineStr">
+      <c r="M182" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V182" s="19">
+      <c r="N182" s="19">
         <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!D24,"")</f>
         <v/>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c r="B183" s="20" t="inlineStr">
+      <c r="A183" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F183" s="20" t="inlineStr">
+      <c r="C183" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O183" s="20" t="inlineStr">
+      <c r="I183" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S183" s="20" t="inlineStr">
+      <c r="K183" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -3652,7 +3633,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N185" s="21" t="inlineStr">
+      <c r="I185" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -3669,57 +3650,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D187" s="23" t="inlineStr">
+      <c r="C187" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G187" s="24">
+      <c r="D187" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H187" s="23" t="inlineStr">
+      <c r="E187" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I187" s="24">
+      <c r="F187" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J187" s="22" t="inlineStr">
+      <c r="G187" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N187" s="22" t="inlineStr">
+      <c r="I187" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O187" s="19">
+      <c r="J187" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q187" s="23" t="inlineStr">
+      <c r="K187" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T187" s="24">
+      <c r="L187" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U187" s="23" t="inlineStr">
+      <c r="M187" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V187" s="24">
+      <c r="N187" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W187" s="22" t="inlineStr">
+      <c r="O187" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -3732,25 +3713,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E189" s="25">
+      <c r="C189" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F189" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I189" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K189" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N189" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R189" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V189" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -3763,37 +3744,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G191" s="26" t="inlineStr">
+      <c r="E191" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H191" s="22" t="inlineStr">
+      <c r="F191" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J191" s="22" t="inlineStr">
+      <c r="G191" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I191" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M191" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N191" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T191" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U191" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W191" s="22" t="inlineStr">
+      <c r="O191" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -3807,26 +3788,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
+      <c r="B194" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E194" s="19">
+      <c r="C194" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N194" s="27" t="inlineStr">
+      <c r="I194" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q194" s="22" t="inlineStr">
+      <c r="J194" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R194" s="19">
+      <c r="K194" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -3837,27 +3818,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C195" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E195" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I195" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K195" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H195" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N195" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R195" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U195" s="20" t="inlineStr">
+      <c r="M195" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -3866,12 +3847,12 @@
     <row r="196" ht="14.25" customHeight="1"/>
     <row r="197" ht="14.25" customHeight="1"/>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="H198" s="20" t="inlineStr">
+      <c r="E198" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U198" s="20" t="inlineStr">
+      <c r="M198" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -3884,17 +3865,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F200" s="27" t="inlineStr">
+      <c r="D200" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N200" s="22" t="inlineStr">
+      <c r="I200" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S200" s="27" t="inlineStr">
+      <c r="L200" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -3907,7 +3888,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N202" s="22" t="inlineStr">
+      <c r="I202" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -3919,17 +3900,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F203" s="27" t="inlineStr">
+      <c r="E203" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N203" s="22" t="inlineStr">
+      <c r="I203" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S203" s="27" t="inlineStr">
+      <c r="M203" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -3942,16 +3923,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F205" s="27">
+      <c r="E205" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N205" s="22" t="inlineStr">
+      <c r="I205" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S205" s="27">
+      <c r="M205" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -3963,7 +3944,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N207" s="28" t="inlineStr">
+      <c r="I207" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -3975,7 +3956,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N208" s="28" t="inlineStr">
+      <c r="I208" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -3989,54 +3970,54 @@
         <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!B25,"")</f>
         <v/>
       </c>
-      <c r="E212" s="17">
+      <c r="C212" s="17">
         <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!C25,"")</f>
         <v/>
       </c>
-      <c r="H212" s="18" t="inlineStr">
+      <c r="E212" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I212" s="19">
+      <c r="F212" s="19">
         <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!D25,"")</f>
         <v/>
       </c>
-      <c r="N212" s="17">
+      <c r="I212" s="17">
         <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!B26,"")</f>
         <v/>
       </c>
-      <c r="R212" s="17">
+      <c r="K212" s="17">
         <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!C26,"")</f>
         <v/>
       </c>
-      <c r="U212" s="18" t="inlineStr">
+      <c r="M212" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V212" s="19">
+      <c r="N212" s="19">
         <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!D26,"")</f>
         <v/>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="B213" s="20" t="inlineStr">
+      <c r="A213" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F213" s="20" t="inlineStr">
+      <c r="C213" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O213" s="20" t="inlineStr">
+      <c r="I213" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S213" s="20" t="inlineStr">
+      <c r="K213" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -4049,7 +4030,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N215" s="21" t="inlineStr">
+      <c r="I215" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -4066,57 +4047,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D217" s="23" t="inlineStr">
+      <c r="C217" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G217" s="24">
+      <c r="D217" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H217" s="23" t="inlineStr">
+      <c r="E217" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I217" s="24">
+      <c r="F217" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J217" s="22" t="inlineStr">
+      <c r="G217" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N217" s="22" t="inlineStr">
+      <c r="I217" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O217" s="19">
+      <c r="J217" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q217" s="23" t="inlineStr">
+      <c r="K217" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T217" s="24">
+      <c r="L217" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U217" s="23" t="inlineStr">
+      <c r="M217" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V217" s="24">
+      <c r="N217" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W217" s="22" t="inlineStr">
+      <c r="O217" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -4129,25 +4110,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E219" s="25">
+      <c r="C219" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F219" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I219" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K219" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N219" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R219" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V219" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -4160,37 +4141,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G221" s="26" t="inlineStr">
+      <c r="E221" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H221" s="22" t="inlineStr">
+      <c r="F221" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J221" s="22" t="inlineStr">
+      <c r="G221" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I221" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M221" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N221" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T221" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U221" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W221" s="22" t="inlineStr">
+      <c r="O221" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -4204,26 +4185,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D224" s="22" t="inlineStr">
+      <c r="B224" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E224" s="19">
+      <c r="C224" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N224" s="27" t="inlineStr">
+      <c r="I224" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q224" s="22" t="inlineStr">
+      <c r="J224" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R224" s="19">
+      <c r="K224" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -4234,27 +4215,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C225" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E225" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I225" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K225" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H225" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N225" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R225" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U225" s="20" t="inlineStr">
+      <c r="M225" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -4263,12 +4244,12 @@
     <row r="226" ht="14.25" customHeight="1"/>
     <row r="227" ht="14.25" customHeight="1"/>
     <row r="228" ht="14.25" customHeight="1">
-      <c r="H228" s="20" t="inlineStr">
+      <c r="E228" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U228" s="20" t="inlineStr">
+      <c r="M228" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -4281,17 +4262,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F230" s="27" t="inlineStr">
+      <c r="D230" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N230" s="22" t="inlineStr">
+      <c r="I230" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S230" s="27" t="inlineStr">
+      <c r="L230" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -4304,7 +4285,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N232" s="22" t="inlineStr">
+      <c r="I232" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -4316,17 +4297,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F233" s="27" t="inlineStr">
+      <c r="E233" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N233" s="22" t="inlineStr">
+      <c r="I233" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S233" s="27" t="inlineStr">
+      <c r="M233" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -4339,16 +4320,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F235" s="27">
+      <c r="E235" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N235" s="22" t="inlineStr">
+      <c r="I235" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S235" s="27">
+      <c r="M235" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -4360,7 +4341,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N237" s="28" t="inlineStr">
+      <c r="I237" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -4372,7 +4353,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N238" s="28" t="inlineStr">
+      <c r="I238" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -4386,54 +4367,54 @@
         <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!B27,"")</f>
         <v/>
       </c>
-      <c r="E242" s="17">
+      <c r="C242" s="17">
         <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!C27,"")</f>
         <v/>
       </c>
-      <c r="H242" s="18" t="inlineStr">
+      <c r="E242" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I242" s="19">
+      <c r="F242" s="19">
         <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!D27,"")</f>
         <v/>
       </c>
-      <c r="N242" s="17">
+      <c r="I242" s="17">
         <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!B28,"")</f>
         <v/>
       </c>
-      <c r="R242" s="17">
+      <c r="K242" s="17">
         <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!C28,"")</f>
         <v/>
       </c>
-      <c r="U242" s="18" t="inlineStr">
+      <c r="M242" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V242" s="19">
+      <c r="N242" s="19">
         <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!D28,"")</f>
         <v/>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="B243" s="20" t="inlineStr">
+      <c r="A243" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F243" s="20" t="inlineStr">
+      <c r="C243" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O243" s="20" t="inlineStr">
+      <c r="I243" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S243" s="20" t="inlineStr">
+      <c r="K243" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -4446,7 +4427,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N245" s="21" t="inlineStr">
+      <c r="I245" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -4463,57 +4444,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D247" s="23" t="inlineStr">
+      <c r="C247" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G247" s="24">
+      <c r="D247" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H247" s="23" t="inlineStr">
+      <c r="E247" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I247" s="24">
+      <c r="F247" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J247" s="22" t="inlineStr">
+      <c r="G247" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N247" s="22" t="inlineStr">
+      <c r="I247" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O247" s="19">
+      <c r="J247" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q247" s="23" t="inlineStr">
+      <c r="K247" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T247" s="24">
+      <c r="L247" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U247" s="23" t="inlineStr">
+      <c r="M247" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V247" s="24">
+      <c r="N247" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W247" s="22" t="inlineStr">
+      <c r="O247" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -4526,25 +4507,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E249" s="25">
+      <c r="C249" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F249" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I249" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K249" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N249" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R249" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V249" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -4557,37 +4538,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G251" s="26" t="inlineStr">
+      <c r="E251" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H251" s="22" t="inlineStr">
+      <c r="F251" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J251" s="22" t="inlineStr">
+      <c r="G251" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I251" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M251" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N251" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T251" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U251" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W251" s="22" t="inlineStr">
+      <c r="O251" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -4601,26 +4582,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D254" s="22" t="inlineStr">
+      <c r="B254" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E254" s="19">
+      <c r="C254" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N254" s="27" t="inlineStr">
+      <c r="I254" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q254" s="22" t="inlineStr">
+      <c r="J254" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R254" s="19">
+      <c r="K254" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -4631,27 +4612,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C255" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E255" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I255" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K255" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H255" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N255" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R255" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U255" s="20" t="inlineStr">
+      <c r="M255" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -4660,12 +4641,12 @@
     <row r="256" ht="14.25" customHeight="1"/>
     <row r="257" ht="14.25" customHeight="1"/>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="H258" s="20" t="inlineStr">
+      <c r="E258" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U258" s="20" t="inlineStr">
+      <c r="M258" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -4678,17 +4659,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F260" s="27" t="inlineStr">
+      <c r="D260" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N260" s="22" t="inlineStr">
+      <c r="I260" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S260" s="27" t="inlineStr">
+      <c r="L260" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -4701,7 +4682,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N262" s="22" t="inlineStr">
+      <c r="I262" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -4713,17 +4694,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F263" s="27" t="inlineStr">
+      <c r="E263" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N263" s="22" t="inlineStr">
+      <c r="I263" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S263" s="27" t="inlineStr">
+      <c r="M263" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -4736,16 +4717,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F265" s="27">
+      <c r="E265" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N265" s="22" t="inlineStr">
+      <c r="I265" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S265" s="27">
+      <c r="M265" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -4757,7 +4738,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N267" s="28" t="inlineStr">
+      <c r="I267" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -4769,7 +4750,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N268" s="28" t="inlineStr">
+      <c r="I268" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -4783,54 +4764,54 @@
         <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!B29,"")</f>
         <v/>
       </c>
-      <c r="E272" s="17">
+      <c r="C272" s="17">
         <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!C29,"")</f>
         <v/>
       </c>
-      <c r="H272" s="18" t="inlineStr">
+      <c r="E272" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="I272" s="19">
+      <c r="F272" s="19">
         <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!D29,"")</f>
         <v/>
       </c>
-      <c r="N272" s="17">
+      <c r="I272" s="17">
         <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!B30,"")</f>
         <v/>
       </c>
-      <c r="R272" s="17">
+      <c r="K272" s="17">
         <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!C30,"")</f>
         <v/>
       </c>
-      <c r="U272" s="18" t="inlineStr">
+      <c r="M272" s="18" t="inlineStr">
         <is>
           <t>geb. am:</t>
         </is>
       </c>
-      <c r="V272" s="19">
+      <c r="N272" s="19">
         <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!D30,"")</f>
         <v/>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="B273" s="20" t="inlineStr">
+      <c r="A273" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F273" s="20" t="inlineStr">
+      <c r="C273" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="O273" s="20" t="inlineStr">
+      <c r="I273" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="S273" s="20" t="inlineStr">
+      <c r="K273" s="20" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
@@ -4843,7 +4824,7 @@
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
       </c>
-      <c r="N275" s="21" t="inlineStr">
+      <c r="I275" s="21" t="inlineStr">
         <is>
           <t>hat an dem 9 Unterrichtseinheiten (Nettounterrichtszeit 9 x 45 Minuten) umfassenden Lehrgang</t>
         </is>
@@ -4860,57 +4841,57 @@
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="D277" s="23" t="inlineStr">
+      <c r="C277" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="G277" s="24">
+      <c r="D277" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="H277" s="23" t="inlineStr">
+      <c r="E277" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="I277" s="24">
+      <c r="F277" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="J277" s="22" t="inlineStr">
+      <c r="G277" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
       </c>
-      <c r="N277" s="22" t="inlineStr">
+      <c r="I277" s="22" t="inlineStr">
         <is>
           <t>am</t>
         </is>
       </c>
-      <c r="O277" s="19">
+      <c r="J277" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="Q277" s="23" t="inlineStr">
+      <c r="K277" s="23" t="inlineStr">
         <is>
           <t>in der Zeit von</t>
         </is>
       </c>
-      <c r="T277" s="24">
+      <c r="L277" s="24">
         <f>Teilnehmer!F3</f>
         <v/>
       </c>
-      <c r="U277" s="23" t="inlineStr">
+      <c r="M277" s="23" t="inlineStr">
         <is>
           <t>Uhr bis</t>
         </is>
       </c>
-      <c r="V277" s="24">
+      <c r="N277" s="24">
         <f>Teilnehmer!H3</f>
         <v/>
       </c>
-      <c r="W277" s="22" t="inlineStr">
+      <c r="O277" s="22" t="inlineStr">
         <is>
           <t>Uhr</t>
         </is>
@@ -4923,25 +4904,25 @@
           <t>unter der Leitung von</t>
         </is>
       </c>
-      <c r="E279" s="25">
+      <c r="C279" s="25">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
+      <c r="F279" s="22" t="inlineStr">
+        <is>
+          <t>erfolgreich teilgenommen.</t>
+        </is>
+      </c>
       <c r="I279" s="22" t="inlineStr">
         <is>
-          <t>erfolgreich teilgenommen.</t>
-        </is>
+          <t>unter der Leitung von</t>
+        </is>
+      </c>
+      <c r="K279" s="25">
+        <f>Teilnehmer!C4</f>
+        <v/>
       </c>
       <c r="N279" s="22" t="inlineStr">
-        <is>
-          <t>unter der Leitung von</t>
-        </is>
-      </c>
-      <c r="R279" s="25">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-      <c r="V279" s="22" t="inlineStr">
         <is>
           <t>erfolgreich teilgenommen.</t>
         </is>
@@ -4954,37 +4935,37 @@
           <t>Teilnehmerunterlagen ausgehändigt:</t>
         </is>
       </c>
-      <c r="G281" s="26" t="inlineStr">
+      <c r="E281" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H281" s="22" t="inlineStr">
+      <c r="F281" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J281" s="22" t="inlineStr">
+      <c r="G281" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
+      <c r="I281" s="22" t="inlineStr">
+        <is>
+          <t>Teilnehmerunterlagen ausgehändigt:</t>
+        </is>
+      </c>
+      <c r="M281" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="N281" s="22" t="inlineStr">
         <is>
-          <t>Teilnehmerunterlagen ausgehändigt:</t>
-        </is>
-      </c>
-      <c r="T281" s="26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U281" s="22" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="W281" s="22" t="inlineStr">
+      <c r="O281" s="22" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -4998,26 +4979,26 @@
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="D284" s="22" t="inlineStr">
+      <c r="B284" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="E284" s="19">
+      <c r="C284" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="N284" s="27" t="inlineStr">
+      <c r="I284" s="27" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="Q284" s="22" t="inlineStr">
+      <c r="J284" s="22" t="inlineStr">
         <is>
           <t>, den</t>
         </is>
       </c>
-      <c r="R284" s="19">
+      <c r="K284" s="19">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
@@ -5028,27 +5009,27 @@
           <t>Ort</t>
         </is>
       </c>
+      <c r="C285" s="20" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
       <c r="E285" s="20" t="inlineStr">
         <is>
+          <t>Unterschrift der Lehrkraft</t>
+        </is>
+      </c>
+      <c r="I285" s="20" t="inlineStr">
+        <is>
+          <t>Ort</t>
+        </is>
+      </c>
+      <c r="K285" s="20" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="H285" s="20" t="inlineStr">
-        <is>
-          <t>Unterschrift der Lehrkraft</t>
-        </is>
-      </c>
-      <c r="N285" s="20" t="inlineStr">
-        <is>
-          <t>Ort</t>
-        </is>
-      </c>
-      <c r="R285" s="20" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="U285" s="20" t="inlineStr">
+      <c r="M285" s="20" t="inlineStr">
         <is>
           <t>Unterschrift der Lehrkraft</t>
         </is>
@@ -5057,12 +5038,12 @@
     <row r="286" ht="14.25" customHeight="1"/>
     <row r="287" ht="14.25" customHeight="1"/>
     <row r="288" ht="14.25" customHeight="1">
-      <c r="H288" s="20" t="inlineStr">
+      <c r="E288" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
       </c>
-      <c r="U288" s="20" t="inlineStr">
+      <c r="M288" s="20" t="inlineStr">
         <is>
           <t>Ausbildungsverantwortlicher</t>
         </is>
@@ -5075,17 +5056,17 @@
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="F290" s="27" t="inlineStr">
+      <c r="D290" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
       </c>
-      <c r="N290" s="22" t="inlineStr">
+      <c r="I290" s="22" t="inlineStr">
         <is>
           <t>Name der ermächtigten Stelle:</t>
         </is>
       </c>
-      <c r="S290" s="27" t="inlineStr">
+      <c r="L290" s="27" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, Werk Rastatt</t>
         </is>
@@ -5098,7 +5079,7 @@
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
       </c>
-      <c r="N292" s="22" t="inlineStr">
+      <c r="I292" s="22" t="inlineStr">
         <is>
           <t>Kennziffer der ermächtigten Stelle</t>
         </is>
@@ -5110,17 +5091,17 @@
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="F293" s="27" t="inlineStr">
+      <c r="E293" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
       </c>
-      <c r="N293" s="22" t="inlineStr">
+      <c r="I293" s="22" t="inlineStr">
         <is>
           <t>gemäß § 26 DGUV Vorschrift:</t>
         </is>
       </c>
-      <c r="S293" s="27" t="inlineStr">
+      <c r="M293" s="27" t="inlineStr">
         <is>
           <t>7.0103</t>
         </is>
@@ -5133,16 +5114,16 @@
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="F295" s="27">
+      <c r="E295" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="N295" s="22" t="inlineStr">
+      <c r="I295" s="22" t="inlineStr">
         <is>
           <t>Registriernummer der Schulung:</t>
         </is>
       </c>
-      <c r="S295" s="27">
+      <c r="M295" s="27">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
@@ -5154,7 +5135,7 @@
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
       </c>
-      <c r="N297" s="28" t="inlineStr">
+      <c r="I297" s="28" t="inlineStr">
         <is>
           <t>* Die Teilnahme an der Ausbildung in betrieblicher Erster Hilfe gilt als Schulung in Erster Hilfe gem. § 19 Fahrerlaubnis-</t>
         </is>
@@ -5166,7 +5147,7 @@
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
       </c>
-      <c r="N298" s="28" t="inlineStr">
+      <c r="I298" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">   Verordnung (FeV).</t>
         </is>
@@ -5175,549 +5156,429 @@
     <row r="299" ht="14.25" customHeight="1"/>
     <row r="300" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="540">
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A142:E142"/>
-    <mergeCell ref="H165:L165"/>
-    <mergeCell ref="N148:Y148"/>
-    <mergeCell ref="U198:Y198"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="N215:Y215"/>
-    <mergeCell ref="V189:Y189"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="S243:T243"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="E212:G212"/>
-    <mergeCell ref="N170:R170"/>
-    <mergeCell ref="R135:S135"/>
-    <mergeCell ref="B213:D213"/>
-    <mergeCell ref="N262:R262"/>
-    <mergeCell ref="S145:V145"/>
-    <mergeCell ref="U258:Y258"/>
-    <mergeCell ref="N172:R172"/>
-    <mergeCell ref="N101:S101"/>
-    <mergeCell ref="A203:E203"/>
-    <mergeCell ref="V92:X92"/>
-    <mergeCell ref="U18:Y18"/>
-    <mergeCell ref="U285:Y285"/>
-    <mergeCell ref="N95:Y95"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="N272:Q272"/>
-    <mergeCell ref="F233:H233"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="N268:Y268"/>
-    <mergeCell ref="N182:Q182"/>
-    <mergeCell ref="S183:T183"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="N175:R175"/>
-    <mergeCell ref="D277:F277"/>
-    <mergeCell ref="N112:R112"/>
-    <mergeCell ref="H255:L255"/>
-    <mergeCell ref="I279:L279"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="N191:S191"/>
-    <mergeCell ref="U135:Y135"/>
-    <mergeCell ref="O153:Q153"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="N254:P254"/>
-    <mergeCell ref="S170:Y170"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="Q217:S217"/>
-    <mergeCell ref="A58:L58"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="R224:S224"/>
-    <mergeCell ref="S173:U173"/>
-    <mergeCell ref="A272:D272"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="N113:R113"/>
-    <mergeCell ref="N173:R173"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="E182:G182"/>
-    <mergeCell ref="S93:T93"/>
-    <mergeCell ref="R279:U279"/>
-    <mergeCell ref="F290:L290"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="A279:D279"/>
-    <mergeCell ref="S263:U263"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A215:L215"/>
-    <mergeCell ref="I189:L189"/>
-    <mergeCell ref="S115:V115"/>
-    <mergeCell ref="N212:Q212"/>
-    <mergeCell ref="N177:Y177"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="V249:Y249"/>
-    <mergeCell ref="R99:U99"/>
-    <mergeCell ref="N35:Y35"/>
-    <mergeCell ref="E272:G272"/>
-    <mergeCell ref="H258:L258"/>
-    <mergeCell ref="E249:H249"/>
-    <mergeCell ref="H195:L195"/>
-    <mergeCell ref="Q127:S127"/>
-    <mergeCell ref="E164:F164"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="U78:Y78"/>
-    <mergeCell ref="E195:F195"/>
-    <mergeCell ref="A268:L268"/>
-    <mergeCell ref="N117:Y117"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="F183:G183"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="U15:Y15"/>
-    <mergeCell ref="N5:Y5"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R104:S104"/>
-    <mergeCell ref="F205:I205"/>
-    <mergeCell ref="U225:Y225"/>
-    <mergeCell ref="F265:I265"/>
-    <mergeCell ref="N52:R52"/>
-    <mergeCell ref="R152:T152"/>
-    <mergeCell ref="H108:L108"/>
-    <mergeCell ref="F293:H293"/>
-    <mergeCell ref="N208:Y208"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="S113:U113"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="B153:D153"/>
-    <mergeCell ref="N281:S281"/>
-    <mergeCell ref="V272:X272"/>
-    <mergeCell ref="N62:Q62"/>
-    <mergeCell ref="N237:Y237"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D217:F217"/>
-    <mergeCell ref="O67:P67"/>
-    <mergeCell ref="R219:U219"/>
-    <mergeCell ref="A230:E230"/>
-    <mergeCell ref="N105:P105"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="A295:E295"/>
-    <mergeCell ref="A143:E143"/>
-    <mergeCell ref="A87:L87"/>
-    <mergeCell ref="I242:K242"/>
-    <mergeCell ref="I219:L219"/>
-    <mergeCell ref="A159:D159"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A232:E232"/>
-    <mergeCell ref="R284:S284"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="R242:T242"/>
-    <mergeCell ref="N50:R50"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="N292:R292"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="U48:Y48"/>
-    <mergeCell ref="S110:Y110"/>
-    <mergeCell ref="E129:H129"/>
-    <mergeCell ref="Q157:S157"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="O187:P187"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="O243:Q243"/>
-    <mergeCell ref="N225:P225"/>
-    <mergeCell ref="A212:D212"/>
-    <mergeCell ref="N135:P135"/>
-    <mergeCell ref="A148:L148"/>
-    <mergeCell ref="V122:X122"/>
-    <mergeCell ref="H198:L198"/>
-    <mergeCell ref="R105:S105"/>
-    <mergeCell ref="N205:R205"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="N164:P164"/>
-    <mergeCell ref="A293:E293"/>
-    <mergeCell ref="N142:R142"/>
-    <mergeCell ref="N80:R80"/>
-    <mergeCell ref="N55:R55"/>
-    <mergeCell ref="F230:L230"/>
-    <mergeCell ref="A221:F221"/>
-    <mergeCell ref="N224:P224"/>
-    <mergeCell ref="S273:T273"/>
-    <mergeCell ref="N238:Y238"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I152:K152"/>
-    <mergeCell ref="A95:L95"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="S50:Y50"/>
-    <mergeCell ref="S53:U53"/>
-    <mergeCell ref="V212:X212"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A224:C224"/>
-    <mergeCell ref="N129:Q129"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A233:E233"/>
-    <mergeCell ref="S295:V295"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="H138:L138"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A175:E175"/>
-    <mergeCell ref="A235:E235"/>
-    <mergeCell ref="U288:Y288"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="R189:U189"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="A191:F191"/>
-    <mergeCell ref="S63:T63"/>
-    <mergeCell ref="A170:E170"/>
-    <mergeCell ref="S123:T123"/>
-    <mergeCell ref="A237:L237"/>
-    <mergeCell ref="H135:L135"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="S80:Y80"/>
-    <mergeCell ref="N297:Y297"/>
-    <mergeCell ref="U168:Y168"/>
-    <mergeCell ref="N249:Q249"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N185:Y185"/>
-    <mergeCell ref="A118:L118"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="A238:L238"/>
-    <mergeCell ref="R255:S255"/>
-    <mergeCell ref="O183:Q183"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="E224:F224"/>
-    <mergeCell ref="A172:E172"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A292:E292"/>
-    <mergeCell ref="N88:Y88"/>
-    <mergeCell ref="Q247:S247"/>
-    <mergeCell ref="B183:D183"/>
-    <mergeCell ref="N23:R23"/>
-    <mergeCell ref="O127:P127"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="U75:Y75"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="N27:Y27"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="E279:H279"/>
-    <mergeCell ref="I159:L159"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="A225:C225"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="N145:R145"/>
-    <mergeCell ref="F115:I115"/>
-    <mergeCell ref="F173:H173"/>
-    <mergeCell ref="E285:F285"/>
-    <mergeCell ref="A177:L177"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="N251:S251"/>
-    <mergeCell ref="S235:V235"/>
-    <mergeCell ref="H168:L168"/>
-    <mergeCell ref="N140:R140"/>
-    <mergeCell ref="A195:C195"/>
-    <mergeCell ref="V182:X182"/>
-    <mergeCell ref="N232:R232"/>
-    <mergeCell ref="U228:Y228"/>
-    <mergeCell ref="O123:Q123"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="N263:R263"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="N242:Q242"/>
-    <mergeCell ref="N200:R200"/>
-    <mergeCell ref="A117:L117"/>
-    <mergeCell ref="F243:G243"/>
-    <mergeCell ref="R194:S194"/>
-    <mergeCell ref="N265:R265"/>
-    <mergeCell ref="N152:Q152"/>
-    <mergeCell ref="E225:F225"/>
-    <mergeCell ref="N202:R202"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A262:E262"/>
-    <mergeCell ref="N260:R260"/>
-    <mergeCell ref="H225:L225"/>
-    <mergeCell ref="H285:L285"/>
-    <mergeCell ref="E152:G152"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="N161:S161"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="N155:Y155"/>
-    <mergeCell ref="A208:L208"/>
-    <mergeCell ref="F170:L170"/>
-    <mergeCell ref="N99:Q99"/>
-    <mergeCell ref="S230:Y230"/>
-    <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A185:L185"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="S140:Y140"/>
-    <mergeCell ref="N28:Y28"/>
-    <mergeCell ref="N115:R115"/>
-    <mergeCell ref="O277:P277"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="E284:F284"/>
-    <mergeCell ref="R69:U69"/>
-    <mergeCell ref="Q187:S187"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="H75:L75"/>
-    <mergeCell ref="S200:Y200"/>
-    <mergeCell ref="N104:P104"/>
-    <mergeCell ref="N275:Y275"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="R195:S195"/>
-    <mergeCell ref="S260:Y260"/>
-    <mergeCell ref="N194:P194"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="S85:V85"/>
-    <mergeCell ref="N147:Y147"/>
-    <mergeCell ref="O273:Q273"/>
-    <mergeCell ref="A205:E205"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I182:K182"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="N178:Y178"/>
-    <mergeCell ref="H228:L228"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A147:L147"/>
-    <mergeCell ref="E219:H219"/>
-    <mergeCell ref="U165:Y165"/>
-    <mergeCell ref="N207:Y207"/>
-    <mergeCell ref="F273:G273"/>
-    <mergeCell ref="R92:T92"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="V99:Y99"/>
-    <mergeCell ref="A200:E200"/>
-    <mergeCell ref="F50:L50"/>
-    <mergeCell ref="A275:L275"/>
-    <mergeCell ref="F110:L110"/>
-    <mergeCell ref="A265:E265"/>
-    <mergeCell ref="V39:Y39"/>
-    <mergeCell ref="S175:V175"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A202:E202"/>
-    <mergeCell ref="N125:Y125"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="N20:R20"/>
-    <mergeCell ref="O63:Q63"/>
-    <mergeCell ref="R159:U159"/>
-    <mergeCell ref="A260:E260"/>
-    <mergeCell ref="F263:H263"/>
-    <mergeCell ref="E254:F254"/>
-    <mergeCell ref="S213:T213"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="N22:R22"/>
-    <mergeCell ref="B243:D243"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="R285:S285"/>
-    <mergeCell ref="E189:H189"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I69:L69"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="N57:Y57"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="V129:Y129"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="N195:P195"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="N284:P284"/>
-    <mergeCell ref="E242:G242"/>
-    <mergeCell ref="R165:S165"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="R212:T212"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="A281:F281"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="F200:L200"/>
-    <mergeCell ref="A88:L88"/>
-    <mergeCell ref="I272:K272"/>
-    <mergeCell ref="S153:T153"/>
-    <mergeCell ref="I212:K212"/>
-    <mergeCell ref="N298:Y298"/>
-    <mergeCell ref="S203:U203"/>
-    <mergeCell ref="I122:K122"/>
-    <mergeCell ref="S20:Y20"/>
-    <mergeCell ref="N279:Q279"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A285:C285"/>
-    <mergeCell ref="F260:L260"/>
-    <mergeCell ref="N53:R53"/>
-    <mergeCell ref="O157:P157"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="U105:Y105"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="N295:R295"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="A145:E145"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="N290:R290"/>
-    <mergeCell ref="U195:Y195"/>
-    <mergeCell ref="N65:Y65"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="F80:L80"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="F145:I145"/>
-    <mergeCell ref="N134:P134"/>
-    <mergeCell ref="A207:L207"/>
-    <mergeCell ref="E255:F255"/>
-    <mergeCell ref="O247:P247"/>
-    <mergeCell ref="Q97:S97"/>
-    <mergeCell ref="A65:L65"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="F203:H203"/>
-    <mergeCell ref="E194:F194"/>
-    <mergeCell ref="I249:L249"/>
-    <mergeCell ref="A152:D152"/>
-    <mergeCell ref="N203:R203"/>
-    <mergeCell ref="B247:C247"/>
-    <mergeCell ref="S265:V265"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="U108:Y108"/>
-    <mergeCell ref="A298:L298"/>
-    <mergeCell ref="F213:G213"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="A161:F161"/>
-    <mergeCell ref="N118:Y118"/>
-    <mergeCell ref="Q277:S277"/>
-    <mergeCell ref="A155:L155"/>
-    <mergeCell ref="I129:L129"/>
-    <mergeCell ref="R134:S134"/>
-    <mergeCell ref="N230:R230"/>
-    <mergeCell ref="U255:Y255"/>
-    <mergeCell ref="F295:I295"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="V279:Y279"/>
-    <mergeCell ref="S143:U143"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="R182:T182"/>
-    <mergeCell ref="A284:C284"/>
-    <mergeCell ref="D247:F247"/>
-    <mergeCell ref="N219:Q219"/>
-    <mergeCell ref="H288:L288"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="R225:S225"/>
-    <mergeCell ref="A173:E173"/>
-    <mergeCell ref="B277:C277"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="Q67:S67"/>
-    <mergeCell ref="N267:Y267"/>
-    <mergeCell ref="H78:L78"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="N110:R110"/>
-    <mergeCell ref="R249:U249"/>
-    <mergeCell ref="N58:Y58"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="U45:Y45"/>
-    <mergeCell ref="A297:L297"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="N122:Q122"/>
-    <mergeCell ref="N82:R82"/>
-    <mergeCell ref="N293:R293"/>
-    <mergeCell ref="A290:E290"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="N221:S221"/>
-    <mergeCell ref="S290:Y290"/>
-    <mergeCell ref="B273:D273"/>
-    <mergeCell ref="N92:Q92"/>
-    <mergeCell ref="N255:P255"/>
-    <mergeCell ref="N131:S131"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="N165:P165"/>
-    <mergeCell ref="V152:X152"/>
-    <mergeCell ref="F140:L140"/>
-    <mergeCell ref="N69:Q69"/>
-    <mergeCell ref="O93:Q93"/>
-    <mergeCell ref="S293:U293"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="N233:R233"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="R272:T272"/>
-    <mergeCell ref="I99:L99"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A251:F251"/>
-    <mergeCell ref="N143:R143"/>
-    <mergeCell ref="F175:I175"/>
-    <mergeCell ref="O213:Q213"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="R164:S164"/>
-    <mergeCell ref="V219:Y219"/>
-    <mergeCell ref="N235:R235"/>
-    <mergeCell ref="R122:T122"/>
-    <mergeCell ref="N285:P285"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="H45:L45"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="N74:P74"/>
-    <mergeCell ref="V242:X242"/>
-    <mergeCell ref="O217:P217"/>
-    <mergeCell ref="S233:U233"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A263:E263"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="D187:F187"/>
-    <mergeCell ref="N189:Q189"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="A178:L178"/>
-    <mergeCell ref="F143:H143"/>
-    <mergeCell ref="S205:V205"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="N83:R83"/>
-    <mergeCell ref="R254:S254"/>
-    <mergeCell ref="A219:D219"/>
-    <mergeCell ref="S55:V55"/>
-    <mergeCell ref="N25:R25"/>
-    <mergeCell ref="N85:R85"/>
-    <mergeCell ref="E165:F165"/>
-    <mergeCell ref="A267:L267"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="R39:U39"/>
-    <mergeCell ref="S25:V25"/>
-    <mergeCell ref="S83:U83"/>
-    <mergeCell ref="N87:Y87"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="V159:Y159"/>
-    <mergeCell ref="N245:Y245"/>
-    <mergeCell ref="N159:Q159"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="V69:Y69"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="B217:C217"/>
-    <mergeCell ref="A245:L245"/>
-    <mergeCell ref="F235:I235"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A189:D189"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="H105:L105"/>
-    <mergeCell ref="U138:Y138"/>
-    <mergeCell ref="R129:U129"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="O37:P37"/>
+  <mergeCells count="420">
+    <mergeCell ref="A263:D263"/>
+    <mergeCell ref="L50:O50"/>
+    <mergeCell ref="E288:G288"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="I191:L191"/>
+    <mergeCell ref="A265:D265"/>
+    <mergeCell ref="I262:L262"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="I202:L202"/>
+    <mergeCell ref="A202:D202"/>
+    <mergeCell ref="A245:G245"/>
+    <mergeCell ref="M145:O145"/>
+    <mergeCell ref="E173:F173"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E285:G285"/>
+    <mergeCell ref="I125:O125"/>
+    <mergeCell ref="I185:O185"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A251:D251"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="I173:L173"/>
+    <mergeCell ref="E138:G138"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="K152:L152"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E205:G205"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="I183:J183"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="E225:G225"/>
+    <mergeCell ref="I178:O178"/>
+    <mergeCell ref="I212:J212"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="I267:O267"/>
+    <mergeCell ref="A142:D142"/>
+    <mergeCell ref="C242:D242"/>
+    <mergeCell ref="A200:C200"/>
+    <mergeCell ref="I207:O207"/>
+    <mergeCell ref="K243:L243"/>
+    <mergeCell ref="D140:G140"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="I293:L293"/>
+    <mergeCell ref="E258:G258"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="I298:O298"/>
+    <mergeCell ref="I292:L292"/>
+    <mergeCell ref="A260:C260"/>
+    <mergeCell ref="E195:G195"/>
+    <mergeCell ref="I71:L71"/>
+    <mergeCell ref="A145:D145"/>
+    <mergeCell ref="K219:M219"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A203:D203"/>
+    <mergeCell ref="K183:L183"/>
+    <mergeCell ref="M108:O108"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="M85:O85"/>
+    <mergeCell ref="I65:O65"/>
+    <mergeCell ref="I110:K110"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I273:J273"/>
+    <mergeCell ref="A273:B273"/>
+    <mergeCell ref="K273:L273"/>
+    <mergeCell ref="I251:L251"/>
+    <mergeCell ref="I281:L281"/>
+    <mergeCell ref="A281:D281"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="E235:G235"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="I153:J153"/>
+    <mergeCell ref="N279:O279"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="K242:L242"/>
+    <mergeCell ref="I200:K200"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="L230:O230"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="A215:G215"/>
+    <mergeCell ref="M113:N113"/>
+    <mergeCell ref="M173:N173"/>
+    <mergeCell ref="K123:L123"/>
+    <mergeCell ref="M258:O258"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="F272:G272"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="D80:G80"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="C213:D213"/>
+    <mergeCell ref="C273:D273"/>
+    <mergeCell ref="E198:G198"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A268:G268"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="M205:O205"/>
+    <mergeCell ref="I58:O58"/>
+    <mergeCell ref="A152:B152"/>
+    <mergeCell ref="D200:G200"/>
+    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="E203:F203"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A161:D161"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="M235:O235"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="A243:B243"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="N219:O219"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="I203:L203"/>
+    <mergeCell ref="M55:O55"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="I177:O177"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="N212:O212"/>
+    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="I213:J213"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="N122:O122"/>
+    <mergeCell ref="I265:L265"/>
+    <mergeCell ref="K279:M279"/>
+    <mergeCell ref="I242:J242"/>
+    <mergeCell ref="A148:G148"/>
+    <mergeCell ref="A232:D232"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="A290:C290"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="A242:B242"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A249:B249"/>
+    <mergeCell ref="M285:O285"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="I215:O215"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="M138:O138"/>
+    <mergeCell ref="I82:L82"/>
+    <mergeCell ref="E295:G295"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="I245:O245"/>
+    <mergeCell ref="L80:O80"/>
+    <mergeCell ref="A293:D293"/>
+    <mergeCell ref="K213:L213"/>
+    <mergeCell ref="M198:O198"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="N189:O189"/>
+    <mergeCell ref="M135:O135"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="I152:J152"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="L140:O140"/>
+    <mergeCell ref="A237:G237"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A219:B219"/>
+    <mergeCell ref="A233:D233"/>
+    <mergeCell ref="A118:G118"/>
+    <mergeCell ref="I260:K260"/>
+    <mergeCell ref="M295:O295"/>
+    <mergeCell ref="I238:O238"/>
+    <mergeCell ref="A238:G238"/>
+    <mergeCell ref="I161:L161"/>
+    <mergeCell ref="A235:D235"/>
+    <mergeCell ref="F182:G182"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="N159:O159"/>
+    <mergeCell ref="E293:F293"/>
+    <mergeCell ref="I95:O95"/>
+    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="I85:L85"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A177:G177"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="E175:G175"/>
+    <mergeCell ref="I205:L205"/>
+    <mergeCell ref="M78:O78"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="I230:K230"/>
+    <mergeCell ref="K159:M159"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A117:G117"/>
+    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="M288:O288"/>
+    <mergeCell ref="D110:G110"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="E228:G228"/>
+    <mergeCell ref="M225:O225"/>
+    <mergeCell ref="N272:O272"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="N182:O182"/>
+    <mergeCell ref="I57:O57"/>
+    <mergeCell ref="I123:J123"/>
+    <mergeCell ref="F249:G249"/>
+    <mergeCell ref="I268:O268"/>
+    <mergeCell ref="A208:G208"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="E165:G165"/>
+    <mergeCell ref="K189:M189"/>
+    <mergeCell ref="L200:O200"/>
+    <mergeCell ref="I279:J279"/>
+    <mergeCell ref="E233:F233"/>
+    <mergeCell ref="M143:N143"/>
+    <mergeCell ref="A262:D262"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="M75:O75"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I243:J243"/>
+    <mergeCell ref="A272:B272"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I112:L112"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="M228:O228"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="A279:B279"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="I189:J189"/>
+    <mergeCell ref="A147:G147"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="I295:L295"/>
+    <mergeCell ref="K182:L182"/>
+    <mergeCell ref="A295:D295"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="E168:G168"/>
+    <mergeCell ref="I232:L232"/>
+    <mergeCell ref="I290:K290"/>
+    <mergeCell ref="A275:G275"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M175:O175"/>
+    <mergeCell ref="M233:N233"/>
+    <mergeCell ref="E255:G255"/>
+    <mergeCell ref="A205:D205"/>
+    <mergeCell ref="I233:L233"/>
+    <mergeCell ref="C272:D272"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I117:O117"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="K249:M249"/>
+    <mergeCell ref="M105:O105"/>
+    <mergeCell ref="E105:G105"/>
+    <mergeCell ref="D290:G290"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="I208:O208"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="M165:O165"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="A88:G88"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="M115:O115"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="I237:O237"/>
+    <mergeCell ref="I140:K140"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="D170:G170"/>
+    <mergeCell ref="I219:J219"/>
+    <mergeCell ref="I147:O147"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="I235:L235"/>
+    <mergeCell ref="A175:D175"/>
+    <mergeCell ref="E265:G265"/>
+    <mergeCell ref="E263:F263"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="M255:O255"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="M168:O168"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="I272:J272"/>
+    <mergeCell ref="K272:L272"/>
+    <mergeCell ref="A212:B212"/>
+    <mergeCell ref="C212:D212"/>
+    <mergeCell ref="L170:O170"/>
+    <mergeCell ref="M203:N203"/>
+    <mergeCell ref="I122:J122"/>
+    <mergeCell ref="A207:G207"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="A172:D172"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="A221:D221"/>
+    <mergeCell ref="A292:D292"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="I131:L131"/>
+    <mergeCell ref="L290:O290"/>
+    <mergeCell ref="I87:O87"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A298:G298"/>
+    <mergeCell ref="I83:L83"/>
+    <mergeCell ref="N129:O129"/>
+    <mergeCell ref="I88:O88"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="I148:O148"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="D260:G260"/>
+    <mergeCell ref="A155:G155"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="L110:O110"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A191:D191"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="M265:O265"/>
+    <mergeCell ref="E145:G145"/>
+    <mergeCell ref="N249:O249"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="F279:G279"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="K212:L212"/>
+    <mergeCell ref="I297:O297"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A297:G297"/>
+    <mergeCell ref="D230:G230"/>
+    <mergeCell ref="A185:G185"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="I172:L172"/>
+    <mergeCell ref="A173:D173"/>
+    <mergeCell ref="M195:O195"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="F242:G242"/>
+    <mergeCell ref="I159:J159"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I175:L175"/>
+    <mergeCell ref="M263:N263"/>
+    <mergeCell ref="I221:L221"/>
+    <mergeCell ref="L260:O260"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I249:J249"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="C243:D243"/>
+    <mergeCell ref="I263:L263"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="I118:O118"/>
+    <mergeCell ref="A125:G125"/>
+    <mergeCell ref="N242:O242"/>
+    <mergeCell ref="N152:O152"/>
+    <mergeCell ref="I170:K170"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="F219:G219"/>
+    <mergeCell ref="I275:O275"/>
+    <mergeCell ref="M293:N293"/>
+    <mergeCell ref="A178:G178"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="I115:L115"/>
+    <mergeCell ref="I182:J182"/>
+    <mergeCell ref="A267:G267"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="I155:O155"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;1Internal</oddHeader>
@@ -5748,567 +5609,641 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A5:D82"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Teilnehmerliste (BG)</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="6" customHeight="1"/>
-    <row r="5" ht="38" customHeight="1">
-      <c r="B5" s="29" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>Unternehmen:</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>BG / UV-Träger:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>BG-Metall Nord-Süd</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1"/>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="31" t="n">
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Mercedesstr. 1, 76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="6" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Nachname, Vorname</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Geburtsdatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B8" s="33">
         <f>IF(Teilnehmer!B11&lt;&gt;"",Teilnehmer!B11&amp;", "&amp;Teilnehmer!C11,"")</f>
         <v/>
       </c>
-      <c r="C10" s="33">
+      <c r="D8" s="34">
         <f>IF(Teilnehmer!D11&lt;&gt;"",Teilnehmer!D11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="31" t="n">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B9" s="36">
         <f>IF(Teilnehmer!B12&lt;&gt;"",Teilnehmer!B12&amp;", "&amp;Teilnehmer!C12,"")</f>
         <v/>
       </c>
-      <c r="C11" s="33">
+      <c r="D9" s="37">
         <f>IF(Teilnehmer!D12&lt;&gt;"",Teilnehmer!D12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="31" t="n">
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B10" s="33">
         <f>IF(Teilnehmer!B13&lt;&gt;"",Teilnehmer!B13&amp;", "&amp;Teilnehmer!C13,"")</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="D10" s="34">
         <f>IF(Teilnehmer!D13&lt;&gt;"",Teilnehmer!D13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="31" t="n">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B11" s="36">
         <f>IF(Teilnehmer!B14&lt;&gt;"",Teilnehmer!B14&amp;", "&amp;Teilnehmer!C14,"")</f>
         <v/>
       </c>
-      <c r="C13" s="33">
+      <c r="D11" s="37">
         <f>IF(Teilnehmer!D14&lt;&gt;"",Teilnehmer!D14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="31" t="n">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B12" s="33">
         <f>IF(Teilnehmer!B15&lt;&gt;"",Teilnehmer!B15&amp;", "&amp;Teilnehmer!C15,"")</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="D12" s="34">
         <f>IF(Teilnehmer!D15&lt;&gt;"",Teilnehmer!D15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="31" t="n">
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B13" s="36">
         <f>IF(Teilnehmer!B16&lt;&gt;"",Teilnehmer!B16&amp;", "&amp;Teilnehmer!C16,"")</f>
         <v/>
       </c>
-      <c r="C15" s="33">
+      <c r="D13" s="37">
         <f>IF(Teilnehmer!D16&lt;&gt;"",Teilnehmer!D16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="31" t="n">
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B14" s="33">
         <f>IF(Teilnehmer!B17&lt;&gt;"",Teilnehmer!B17&amp;", "&amp;Teilnehmer!C17,"")</f>
         <v/>
       </c>
-      <c r="C16" s="33">
+      <c r="D14" s="34">
         <f>IF(Teilnehmer!D17&lt;&gt;"",Teilnehmer!D17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="31" t="n">
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B15" s="36">
         <f>IF(Teilnehmer!B18&lt;&gt;"",Teilnehmer!B18&amp;", "&amp;Teilnehmer!C18,"")</f>
         <v/>
       </c>
-      <c r="C17" s="33">
+      <c r="D15" s="37">
         <f>IF(Teilnehmer!D18&lt;&gt;"",Teilnehmer!D18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="31" t="n">
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B16" s="33">
         <f>IF(Teilnehmer!B19&lt;&gt;"",Teilnehmer!B19&amp;", "&amp;Teilnehmer!C19,"")</f>
         <v/>
       </c>
-      <c r="C18" s="33">
+      <c r="D16" s="34">
         <f>IF(Teilnehmer!D19&lt;&gt;"",Teilnehmer!D19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="31" t="n">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B17" s="36">
         <f>IF(Teilnehmer!B20&lt;&gt;"",Teilnehmer!B20&amp;", "&amp;Teilnehmer!C20,"")</f>
         <v/>
       </c>
-      <c r="C19" s="33">
+      <c r="D17" s="37">
         <f>IF(Teilnehmer!D20&lt;&gt;"",Teilnehmer!D20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1"/>
+    <row r="20">
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Ansprechpartner:</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Dr. Schmidt, Sabine</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>Lehrkraft:</t>
+        </is>
+      </c>
+      <c r="E20" s="31">
+        <f>Teilnehmer!C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Telefon:</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>07222/91-22111</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Datum:</t>
+        </is>
+      </c>
+      <c r="E21" s="38">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
     <row r="22">
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>E-Mail:</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>sabine.m.schmidt@mercedes-benz.com</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Registriernr.:</t>
+        </is>
+      </c>
+      <c r="E22" s="31">
+        <f>Teilnehmer!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>QSEH-Kennziffer:</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>7.0103</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Stempel / Anschrift:</t>
+        </is>
+      </c>
+      <c r="D26" s="39" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz AG, Werksärztlicher Dienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="39" t="inlineStr">
+        <is>
+          <t>Mercedesstr. 1, 76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Datum:</t>
+        </is>
+      </c>
+      <c r="C28" s="38">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Teilnehmerliste (BG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>Unternehmen:</t>
+        </is>
+      </c>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>BG / UV-Träger:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz AG</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="inlineStr">
+        <is>
+          <t>BG-Metall Nord-Süd</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>Mercedesstr. 1, 76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="6" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Nachname, Vorname</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Geburtsdatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" s="33">
+        <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!B21&amp;", "&amp;Teilnehmer!C21,"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="34">
+        <f>IF(Teilnehmer!D21&lt;&gt;"",Teilnehmer!D21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" s="36">
+        <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!B22&amp;", "&amp;Teilnehmer!C22,"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="37">
+        <f>IF(Teilnehmer!D22&lt;&gt;"",Teilnehmer!D22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="33">
+        <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!B23&amp;", "&amp;Teilnehmer!C23,"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="34">
+        <f>IF(Teilnehmer!D23&lt;&gt;"",Teilnehmer!D23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" s="36">
+        <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!B24&amp;", "&amp;Teilnehmer!C24,"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="37">
+        <f>IF(Teilnehmer!D24&lt;&gt;"",Teilnehmer!D24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" s="33">
+        <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!B25&amp;", "&amp;Teilnehmer!C25,"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="34">
+        <f>IF(Teilnehmer!D25&lt;&gt;"",Teilnehmer!D25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B61" s="36">
+        <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!B26&amp;", "&amp;Teilnehmer!C26,"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="37">
+        <f>IF(Teilnehmer!D26&lt;&gt;"",Teilnehmer!D26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" s="33">
+        <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!B27&amp;", "&amp;Teilnehmer!C27,"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="34">
+        <f>IF(Teilnehmer!D27&lt;&gt;"",Teilnehmer!D27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" s="36">
+        <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!B28&amp;", "&amp;Teilnehmer!C28,"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="37">
+        <f>IF(Teilnehmer!D28&lt;&gt;"",Teilnehmer!D28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="33">
+        <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!B29&amp;", "&amp;Teilnehmer!C29,"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="34">
+        <f>IF(Teilnehmer!D29&lt;&gt;"",Teilnehmer!D29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B65" s="36">
+        <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!B30&amp;", "&amp;Teilnehmer!C30,"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="37">
+        <f>IF(Teilnehmer!D30&lt;&gt;"",Teilnehmer!D30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>Ansprechpartner:</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
         <is>
           <t>Dr. Schmidt, Sabine</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="34" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>Lehrkraft:</t>
+        </is>
+      </c>
+      <c r="E68" s="31">
+        <f>Teilnehmer!C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>Telefon:</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
         <is>
           <t>07222/91-22111</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="35" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>Datum:</t>
+        </is>
+      </c>
+      <c r="E69" s="38">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>E-Mail:</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
         <is>
           <t>sabine.m.schmidt@mercedes-benz.com</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="D25" s="36">
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>Registriernr.:</t>
+        </is>
+      </c>
+      <c r="E70" s="31">
+        <f>Teilnehmer!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" s="30" t="inlineStr">
+        <is>
+          <t>QSEH-Kennziffer:</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>7.0103</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>Stempel / Anschrift:</t>
+        </is>
+      </c>
+      <c r="D74" s="39" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz AG, Werksärztlicher Dienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="D75" s="39" t="inlineStr">
+        <is>
+          <t>Mercedesstr. 1, 76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>Datum:</t>
+        </is>
+      </c>
+      <c r="C76" s="38">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29">
-      <c r="C29" s="36">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.0103</t>
-        </is>
-      </c>
-      <c r="C31" s="38">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="37">
-        <f>"  "&amp;Teilnehmer!C5</f>
-        <v/>
-      </c>
-      <c r="C33" s="38" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG, PKW-Werk Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="38" t="inlineStr">
-        <is>
-          <t>Werksärztlicher Dienst</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>PKW-Werk Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="38" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="36">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-      <c r="C40" s="38" t="inlineStr">
-        <is>
-          <t>76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="47" ht="38" customHeight="1">
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>BG-Metall Nord-Süd</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="30" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="B49" s="30" t="inlineStr">
-        <is>
-          <t>76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" s="32">
-        <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!B21&amp;", "&amp;Teilnehmer!C21,"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="33">
-        <f>IF(Teilnehmer!D21&lt;&gt;"",Teilnehmer!D21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="32">
-        <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!B22&amp;", "&amp;Teilnehmer!C22,"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="33">
-        <f>IF(Teilnehmer!D22&lt;&gt;"",Teilnehmer!D22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="32">
-        <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!B23&amp;", "&amp;Teilnehmer!C23,"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="33">
-        <f>IF(Teilnehmer!D23&lt;&gt;"",Teilnehmer!D23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="B55" s="32">
-        <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!B24&amp;", "&amp;Teilnehmer!C24,"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="33">
-        <f>IF(Teilnehmer!D24&lt;&gt;"",Teilnehmer!D24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" s="32">
-        <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!B25&amp;", "&amp;Teilnehmer!C25,"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="33">
-        <f>IF(Teilnehmer!D25&lt;&gt;"",Teilnehmer!D25,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="B57" s="32">
-        <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!B26&amp;", "&amp;Teilnehmer!C26,"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="33">
-        <f>IF(Teilnehmer!D26&lt;&gt;"",Teilnehmer!D26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="B58" s="32">
-        <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!B27&amp;", "&amp;Teilnehmer!C27,"")</f>
-        <v/>
-      </c>
-      <c r="C58" s="33">
-        <f>IF(Teilnehmer!D27&lt;&gt;"",Teilnehmer!D27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="B59" s="32">
-        <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!B28&amp;", "&amp;Teilnehmer!C28,"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="33">
-        <f>IF(Teilnehmer!D28&lt;&gt;"",Teilnehmer!D28,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="32">
-        <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!B29&amp;", "&amp;Teilnehmer!C29,"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="33">
-        <f>IF(Teilnehmer!D29&lt;&gt;"",Teilnehmer!D29,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="32">
-        <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!B30&amp;", "&amp;Teilnehmer!C30,"")</f>
-        <v/>
-      </c>
-      <c r="C61" s="33">
-        <f>IF(Teilnehmer!D30&lt;&gt;"",Teilnehmer!D30,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="24" customHeight="1"/>
-    <row r="64">
-      <c r="B64" s="34" t="inlineStr">
-        <is>
-          <t>Dr. Schmidt, Sabine</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="34" t="inlineStr">
-        <is>
-          <t>07222/91-22111</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="35" t="inlineStr">
-        <is>
-          <t>sabine.m.schmidt@mercedes-benz.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="D67" s="36">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="8" customHeight="1"/>
-    <row r="71">
-      <c r="C71" s="36">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.0103</t>
-        </is>
-      </c>
-      <c r="C73" s="38">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="37">
-        <f>"  "&amp;Teilnehmer!C5</f>
-        <v/>
-      </c>
-      <c r="C75" s="38" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG, PKW-Werk Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="C78" s="38" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="C79" s="38" t="inlineStr">
-        <is>
-          <t>Werksärztlicher Dienst</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="C80" s="38" t="inlineStr">
-        <is>
-          <t>PKW-Werk Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="C81" s="38" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="36">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-      <c r="C82" s="38" t="inlineStr">
-        <is>
-          <t>76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C73:D73"/>
+  <mergeCells count="34">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B10:B19">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>", "</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10:C19">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B61">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
-      <formula>", "</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C52:C61">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.2" right="0.1" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="42" min="0" max="16383" man="1"/>
+    <brk id="48" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -6333,221 +6268,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Lehrgangsdokumentation</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>gem. Abschnitt 2.4.6 DGUV Grundsatz 304-001</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Angaben zur Ausbildungsstelle</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Bezeichnung</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG</t>
         </is>
       </c>
-      <c r="E6" s="44" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>QSEH-Kennziffer:</t>
         </is>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>Teilnehmer!F5</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Straße / Hausnr.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>Mercedesstr. 1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>PLZ / Ort</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>76437 Rastatt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>Angaben zum Seminar</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="45">
+      <c r="B15" s="46">
         <f>IF(Teilnehmer!F4="EH-Ausbildung","X","  ")&amp;" EH-Ausbildung       "&amp;IF(Teilnehmer!F4="EH-Fortbildung","X","  ")&amp;" EH-Fortbildung       "&amp;IF(Teilnehmer!F4="EH-Schulung","X","  ")&amp;" EH-Schulung"</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Registriernummer:</t>
         </is>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="44">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="E17" s="44" t="inlineStr">
+      <c r="E17" s="45" t="inlineStr">
         <is>
           <t>Lehrgangsort:</t>
         </is>
       </c>
-      <c r="F17" s="43" t="inlineStr">
+      <c r="F17" s="44" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, PKW-Werk Rastatt</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>(aus dem QSEH-Portal)</t>
         </is>
       </c>
-      <c r="F18" s="42" t="inlineStr">
+      <c r="F18" s="43" t="inlineStr">
         <is>
           <t>Gebäude 39, Gesundheitszentrum 1.OG</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>Lehrgangsdatum:</t>
         </is>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="47">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="E20" s="44" t="inlineStr">
+      <c r="E20" s="45" t="inlineStr">
         <is>
           <t>Uhrzeit:</t>
         </is>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="44">
         <f>"von "&amp;TEXT(Teilnehmer!F3,"HH:MM")&amp;" Uhr bis "&amp;TEXT(Teilnehmer!H3,"HH:MM")&amp;" Uhr"</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="45" t="inlineStr">
         <is>
           <t>Name der Lehrkraft:</t>
         </is>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="44">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="45" t="inlineStr">
         <is>
           <t>Verantwortlicher Arzt:</t>
         </is>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>Teilnehmer!C7</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
         <is>
           <t>Masken-Charge:</t>
         </is>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="48">
         <f>Teilnehmer!C8</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>Anzahl der Teilnehmenden</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="45" t="inlineStr">
         <is>
           <t>Gesamtanzahl der Teilnehmenden:</t>
         </is>
       </c>
-      <c r="E30" s="48">
+      <c r="E30" s="49">
         <f>Teilnehmer!C32</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
-      <c r="B31" s="42" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>(entspricht der Anzahl der Teilnehmerdatenblätter)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="45" t="inlineStr">
         <is>
           <t>davon betriebliche Ersthelfende:</t>
         </is>
       </c>
-      <c r="E33" s="48">
+      <c r="E33" s="49">
         <f>Teilnehmer!E32</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="41" t="inlineStr">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Anlagen</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="B36" s="45" t="inlineStr">
+      <c r="B36" s="46" t="inlineStr">
         <is>
           <t>Alle Teilnehmenden sind mit Namen, Vornamen, Geburtsdatum und Unterschrift zu erfassen. Für UVT-Teilnehmende sind zusätzlich der Name und die Anschrift des Arbeitgebers sowie der kostentragende UVT zu ergänzen. Dies kann durch einzelne Teilnehmerdatenblätter erfolgen.</t>
         </is>
@@ -6556,43 +6491,43 @@
     <row r="37" ht="16" customHeight="1"/>
     <row r="38" ht="16" customHeight="1"/>
     <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="45" t="inlineStr">
+      <c r="B40" s="46" t="inlineStr">
         <is>
           <t>Die Dokumentation ist fünf Jahre aufzubewahren und auf Anforderung dem Unfallversicherungsträger vorzulegen.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="45" t="inlineStr">
         <is>
           <t>Für die Richtigkeit der Angaben:</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="49">
+      <c r="B47" s="50">
         <f>"Rastatt, "&amp;TEXT(Teilnehmer!C3,"DD.MM.YYYY")</f>
         <v/>
       </c>
-      <c r="E47" s="49">
+      <c r="E47" s="50">
         <f>"Rastatt, "&amp;TEXT(Teilnehmer!C3,"DD.MM.YYYY")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
-      <c r="B48" s="42" t="inlineStr">
+      <c r="B48" s="43" t="inlineStr">
         <is>
           <t>Ort, Datum     Unterschrift Lehrgangsleitung</t>
         </is>
       </c>
-      <c r="E48" s="42" t="inlineStr">
+      <c r="E48" s="43" t="inlineStr">
         <is>
           <t>Ort, Datum     Unterschrift Ausbildungsstelle</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="B50" s="50" t="inlineStr">
+      <c r="B50" s="51" t="inlineStr">
         <is>
           <t>Stand: 2026</t>
         </is>
@@ -6619,4 +6554,78 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009E9E9E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Lehrkräfte</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Putschler, Walter</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>Kaya, Michelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>Krempl, Elke</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>Breig, Bernd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>Zuber, Harry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>Jochim, Benjamin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>Siebert, Emanuel</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -15,6 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="Lehrkraefte">Hilfslisten!$A$2:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'BG-Liste'!$A$1:$E$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="165" formatCode="HH:MM"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,13 +98,29 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -235,9 +252,6 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="0070D2A6"/>
-      </left>
       <right style="medium">
         <color rgb="0070D2A6"/>
       </right>
@@ -252,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -338,73 +352,75 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -414,7 +430,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -422,6 +438,11 @@
           <bgColor rgb="00FFCDD2"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00FFFFFF"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -494,6 +515,1361 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11374437" cy="2048161"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="514422" cy="4277322"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5601481" cy="314369"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1810003" cy="2181529"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5401429" cy="238157"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="438211" cy="2486372"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5544324" cy="304843"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5410955" cy="476315"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11336332" cy="1086002"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="533474" cy="6049219"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1409897" cy="5296639"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11355385" cy="771633"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1381318" cy="2734057"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6763694" cy="666843"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="200053" cy="1943371"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="790685" cy="314369"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3877216" cy="876422"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="504895" cy="2162477"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11279174" cy="760400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1458493" cy="4727593"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10470280" cy="255763"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152421" cy="4242233"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10918018" cy="258657"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10813228" cy="275661"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10565543" cy="550839"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="114316" cy="4196409"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="724000" cy="266737"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11374437" cy="2048161"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="514422" cy="4277322"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5601481" cy="314369"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1810003" cy="2181529"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5401429" cy="238157"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="438211" cy="2486372"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5544324" cy="304843"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5410955" cy="476315"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11336332" cy="1086002"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="533474" cy="6049219"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1409897" cy="5296639"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11355385" cy="771633"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1381318" cy="2734057"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6763694" cy="666843"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="200053" cy="1943371"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="790685" cy="314369"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3877216" cy="876422"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="504895" cy="2162477"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11279174" cy="760400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1458493" cy="4727593"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10470280" cy="255763"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152421" cy="4242233"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10918018" cy="258657"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10813228" cy="275661"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10565543" cy="550839"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="114316" cy="4196409"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="724000" cy="266737"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5579,7 +6955,7 @@
     <mergeCell ref="I155:O155"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;1Internal</oddHeader>
     <oddFooter/>
@@ -5609,642 +6985,600 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A5:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10.66" customWidth="1" min="1" max="1"/>
+    <col width="62.44" customWidth="1" min="2" max="2"/>
+    <col width="38.55" customWidth="1" min="3" max="3"/>
+    <col width="40.66" customWidth="1" min="4" max="4"/>
+    <col width="21.66" customWidth="1" min="5" max="5"/>
+    <col width="4.33" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>Teilnehmerliste (BG)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="30" t="inlineStr">
-        <is>
-          <t>Unternehmen:</t>
-        </is>
-      </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>BG / UV-Träger:</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
+    <row r="1" ht="42" customHeight="1"/>
+    <row r="2" ht="41.25" customHeight="1"/>
+    <row r="3" ht="38.25" customHeight="1"/>
+    <row r="4" ht="38.25" customHeight="1"/>
+    <row r="5" ht="42" customHeight="1">
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>BG-Metall Nord-Süd</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1, 76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="6" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Nr.</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Nachname, Vorname</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Geburtsdatum</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="32" t="n">
+    <row r="6" ht="41.25" customHeight="1">
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Mercedesstr. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32.25" customHeight="1">
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>76437 Rastatt</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="41.25" customHeight="1"/>
+    <row r="9" ht="34.5" customHeight="1"/>
+    <row r="10" ht="39.75" customHeight="1">
+      <c r="A10" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B10" s="34">
         <f>IF(Teilnehmer!B11&lt;&gt;"",Teilnehmer!B11&amp;", "&amp;Teilnehmer!C11,"")</f>
         <v/>
       </c>
-      <c r="D8" s="34">
+      <c r="C10" s="35">
         <f>IF(Teilnehmer!D11&lt;&gt;"",Teilnehmer!D11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="35" t="n">
+    <row r="11" ht="39.75" customHeight="1">
+      <c r="A11" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B11" s="34">
         <f>IF(Teilnehmer!B12&lt;&gt;"",Teilnehmer!B12&amp;", "&amp;Teilnehmer!C12,"")</f>
         <v/>
       </c>
-      <c r="D9" s="37">
+      <c r="C11" s="35">
         <f>IF(Teilnehmer!D12&lt;&gt;"",Teilnehmer!D12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="32" t="n">
+    <row r="12" ht="39.75" customHeight="1">
+      <c r="A12" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B12" s="34">
         <f>IF(Teilnehmer!B13&lt;&gt;"",Teilnehmer!B13&amp;", "&amp;Teilnehmer!C13,"")</f>
         <v/>
       </c>
-      <c r="D10" s="34">
+      <c r="C12" s="35">
         <f>IF(Teilnehmer!D13&lt;&gt;"",Teilnehmer!D13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="35" t="n">
+    <row r="13" ht="39.75" customHeight="1">
+      <c r="A13" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B13" s="34">
         <f>IF(Teilnehmer!B14&lt;&gt;"",Teilnehmer!B14&amp;", "&amp;Teilnehmer!C14,"")</f>
         <v/>
       </c>
-      <c r="D11" s="37">
+      <c r="C13" s="35">
         <f>IF(Teilnehmer!D14&lt;&gt;"",Teilnehmer!D14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="32" t="n">
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B14" s="34">
         <f>IF(Teilnehmer!B15&lt;&gt;"",Teilnehmer!B15&amp;", "&amp;Teilnehmer!C15,"")</f>
         <v/>
       </c>
-      <c r="D12" s="34">
+      <c r="C14" s="35">
         <f>IF(Teilnehmer!D15&lt;&gt;"",Teilnehmer!D15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="35" t="n">
+    <row r="15" ht="39.75" customHeight="1">
+      <c r="A15" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B15" s="34">
         <f>IF(Teilnehmer!B16&lt;&gt;"",Teilnehmer!B16&amp;", "&amp;Teilnehmer!C16,"")</f>
         <v/>
       </c>
-      <c r="D13" s="37">
+      <c r="C15" s="35">
         <f>IF(Teilnehmer!D16&lt;&gt;"",Teilnehmer!D16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="32" t="n">
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B16" s="34">
         <f>IF(Teilnehmer!B17&lt;&gt;"",Teilnehmer!B17&amp;", "&amp;Teilnehmer!C17,"")</f>
         <v/>
       </c>
-      <c r="D14" s="34">
+      <c r="C16" s="35">
         <f>IF(Teilnehmer!D17&lt;&gt;"",Teilnehmer!D17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="35" t="n">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="36">
+      <c r="B17" s="34">
         <f>IF(Teilnehmer!B18&lt;&gt;"",Teilnehmer!B18&amp;", "&amp;Teilnehmer!C18,"")</f>
         <v/>
       </c>
-      <c r="D15" s="37">
+      <c r="C17" s="35">
         <f>IF(Teilnehmer!D18&lt;&gt;"",Teilnehmer!D18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="32" t="n">
+    <row r="18" ht="39.75" customHeight="1">
+      <c r="A18" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="33">
+      <c r="B18" s="34">
         <f>IF(Teilnehmer!B19&lt;&gt;"",Teilnehmer!B19&amp;", "&amp;Teilnehmer!C19,"")</f>
         <v/>
       </c>
-      <c r="D16" s="34">
+      <c r="C18" s="35">
         <f>IF(Teilnehmer!D19&lt;&gt;"",Teilnehmer!D19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="35" t="n">
+    <row r="19" ht="39.75" customHeight="1">
+      <c r="A19" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="36">
+      <c r="B19" s="34">
         <f>IF(Teilnehmer!B20&lt;&gt;"",Teilnehmer!B20&amp;", "&amp;Teilnehmer!C20,"")</f>
         <v/>
       </c>
-      <c r="D17" s="37">
+      <c r="C19" s="35">
         <f>IF(Teilnehmer!D20&lt;&gt;"",Teilnehmer!D20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>Ansprechpartner:</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
+    <row r="20" ht="42" customHeight="1"/>
+    <row r="21" ht="27.75" customHeight="1"/>
+    <row r="22" ht="32.25" customHeight="1">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>Dr. Schmidt, Sabine</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
-        <is>
-          <t>Lehrkraft:</t>
-        </is>
-      </c>
-      <c r="E20" s="31">
+    </row>
+    <row r="23" ht="32.25" customHeight="1">
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>07222/91-22111</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32.25" customHeight="1">
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>sabine.m.schmidt@mercedes-benz.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="D25" s="38">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="25.5" customHeight="1"/>
+    <row r="27" ht="31.5" customHeight="1"/>
+    <row r="28" ht="8.25" customHeight="1"/>
+    <row r="29" ht="25.5" customHeight="1">
+      <c r="C29" s="38">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1"/>
+    <row r="31" ht="25.5" customHeight="1">
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.0103</t>
+        </is>
+      </c>
+      <c r="C31" s="40">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>Telefon:</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
+    <row r="32" ht="21" customHeight="1"/>
+    <row r="33" ht="26.25" customHeight="1">
+      <c r="B33" s="41">
+        <f>"  "&amp;Teilnehmer!C5</f>
+        <v/>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG, PKW Werk</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="29.25" customHeight="1">
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="29.25" customHeight="1">
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Werksärztlicher Dienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="29.25" customHeight="1">
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>PKW-Werk Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="29.25" customHeight="1">
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Mercedesstrasse 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="29.25" customHeight="1">
+      <c r="B40" s="38">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="21" customHeight="1"/>
+    <row r="42" ht="9" customHeight="1"/>
+    <row r="43" ht="9" customHeight="1"/>
+    <row r="44" ht="42" customHeight="1"/>
+    <row r="45" ht="41.25" customHeight="1"/>
+    <row r="46" ht="38.25" customHeight="1"/>
+    <row r="47" ht="38.25" customHeight="1"/>
+    <row r="48" ht="42" customHeight="1">
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>BG-Metall Nord-Süd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="41.25" customHeight="1">
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>Mercedesstr. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32.25" customHeight="1">
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>76437 Rastatt</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="n"/>
+    </row>
+    <row r="51" ht="41.25" customHeight="1"/>
+    <row r="52" ht="34.5" customHeight="1"/>
+    <row r="53" ht="39.75" customHeight="1">
+      <c r="A53" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="34">
+        <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!B21&amp;", "&amp;Teilnehmer!C21,"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="35">
+        <f>IF(Teilnehmer!D21&lt;&gt;"",Teilnehmer!D21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="39.75" customHeight="1">
+      <c r="A54" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="34">
+        <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!B22&amp;", "&amp;Teilnehmer!C22,"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="35">
+        <f>IF(Teilnehmer!D22&lt;&gt;"",Teilnehmer!D22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="39.75" customHeight="1">
+      <c r="A55" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="34">
+        <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!B23&amp;", "&amp;Teilnehmer!C23,"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="35">
+        <f>IF(Teilnehmer!D23&lt;&gt;"",Teilnehmer!D23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="39.75" customHeight="1">
+      <c r="A56" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="34">
+        <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!B24&amp;", "&amp;Teilnehmer!C24,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="35">
+        <f>IF(Teilnehmer!D24&lt;&gt;"",Teilnehmer!D24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="40.5" customHeight="1">
+      <c r="A57" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="34">
+        <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!B25&amp;", "&amp;Teilnehmer!C25,"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="35">
+        <f>IF(Teilnehmer!D25&lt;&gt;"",Teilnehmer!D25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="39.75" customHeight="1">
+      <c r="A58" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="34">
+        <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!B26&amp;", "&amp;Teilnehmer!C26,"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="35">
+        <f>IF(Teilnehmer!D26&lt;&gt;"",Teilnehmer!D26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="40.5" customHeight="1">
+      <c r="A59" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="34">
+        <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!B27&amp;", "&amp;Teilnehmer!C27,"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="35">
+        <f>IF(Teilnehmer!D27&lt;&gt;"",Teilnehmer!D27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="39" customHeight="1">
+      <c r="A60" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="34">
+        <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!B28&amp;", "&amp;Teilnehmer!C28,"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="35">
+        <f>IF(Teilnehmer!D28&lt;&gt;"",Teilnehmer!D28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="39.75" customHeight="1">
+      <c r="A61" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="34">
+        <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!B29&amp;", "&amp;Teilnehmer!C29,"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="35">
+        <f>IF(Teilnehmer!D29&lt;&gt;"",Teilnehmer!D29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="39.75" customHeight="1">
+      <c r="A62" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="34">
+        <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!B30&amp;", "&amp;Teilnehmer!C30,"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="35">
+        <f>IF(Teilnehmer!D30&lt;&gt;"",Teilnehmer!D30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1"/>
+    <row r="64" ht="27.75" customHeight="1"/>
+    <row r="65" ht="32.25" customHeight="1">
+      <c r="B65" s="36" t="inlineStr">
+        <is>
+          <t>Dr. Schmidt, Sabine</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32.25" customHeight="1">
+      <c r="B66" s="36" t="inlineStr">
         <is>
           <t>07222/91-22111</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>Datum:</t>
-        </is>
-      </c>
-      <c r="E21" s="38">
+    </row>
+    <row r="67" ht="32.25" customHeight="1">
+      <c r="B67" s="37" t="inlineStr">
+        <is>
+          <t>sabine.m.schmidt@mercedes-benz.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="D68" s="38">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>E-Mail:</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>sabine.m.schmidt@mercedes-benz.com</t>
-        </is>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>Registriernr.:</t>
-        </is>
-      </c>
-      <c r="E22" s="31">
-        <f>Teilnehmer!C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>QSEH-Kennziffer:</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>7.0103</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>Stempel / Anschrift:</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG, Werksärztlicher Dienst</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="D27" s="39" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1, 76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>Datum:</t>
-        </is>
-      </c>
-      <c r="C28" s="38">
+    <row r="69" ht="25.5" customHeight="1"/>
+    <row r="70" ht="31.5" customHeight="1"/>
+    <row r="71" ht="8.25" customHeight="1"/>
+    <row r="72" ht="25.5" customHeight="1">
+      <c r="C72" s="38">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>Teilnehmerliste (BG)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="18" customHeight="1">
-      <c r="B51" s="30" t="inlineStr">
-        <is>
-          <t>Unternehmen:</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>BG / UV-Träger:</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG</t>
-        </is>
-      </c>
-      <c r="D52" s="31" t="inlineStr">
-        <is>
-          <t>BG-Metall Nord-Süd</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1, 76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Nr.</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Nachname, Vorname</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Geburtsdatum</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B56" s="33">
-        <f>IF(Teilnehmer!B21&lt;&gt;"",Teilnehmer!B21&amp;", "&amp;Teilnehmer!C21,"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="34">
-        <f>IF(Teilnehmer!D21&lt;&gt;"",Teilnehmer!D21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" s="36">
-        <f>IF(Teilnehmer!B22&lt;&gt;"",Teilnehmer!B22&amp;", "&amp;Teilnehmer!C22,"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="37">
-        <f>IF(Teilnehmer!D22&lt;&gt;"",Teilnehmer!D22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="33">
-        <f>IF(Teilnehmer!B23&lt;&gt;"",Teilnehmer!B23&amp;", "&amp;Teilnehmer!C23,"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="34">
-        <f>IF(Teilnehmer!D23&lt;&gt;"",Teilnehmer!D23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="B59" s="36">
-        <f>IF(Teilnehmer!B24&lt;&gt;"",Teilnehmer!B24&amp;", "&amp;Teilnehmer!C24,"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="37">
-        <f>IF(Teilnehmer!D24&lt;&gt;"",Teilnehmer!D24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="B60" s="33">
-        <f>IF(Teilnehmer!B25&lt;&gt;"",Teilnehmer!B25&amp;", "&amp;Teilnehmer!C25,"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="34">
-        <f>IF(Teilnehmer!D25&lt;&gt;"",Teilnehmer!D25,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B61" s="36">
-        <f>IF(Teilnehmer!B26&lt;&gt;"",Teilnehmer!B26&amp;", "&amp;Teilnehmer!C26,"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="37">
-        <f>IF(Teilnehmer!D26&lt;&gt;"",Teilnehmer!D26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="B62" s="33">
-        <f>IF(Teilnehmer!B27&lt;&gt;"",Teilnehmer!B27&amp;", "&amp;Teilnehmer!C27,"")</f>
-        <v/>
-      </c>
-      <c r="D62" s="34">
-        <f>IF(Teilnehmer!D27&lt;&gt;"",Teilnehmer!D27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="B63" s="36">
-        <f>IF(Teilnehmer!B28&lt;&gt;"",Teilnehmer!B28&amp;", "&amp;Teilnehmer!C28,"")</f>
-        <v/>
-      </c>
-      <c r="D63" s="37">
-        <f>IF(Teilnehmer!D28&lt;&gt;"",Teilnehmer!D28,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="B64" s="33">
-        <f>IF(Teilnehmer!B29&lt;&gt;"",Teilnehmer!B29&amp;", "&amp;Teilnehmer!C29,"")</f>
-        <v/>
-      </c>
-      <c r="D64" s="34">
-        <f>IF(Teilnehmer!D29&lt;&gt;"",Teilnehmer!D29,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="36">
-        <f>IF(Teilnehmer!B30&lt;&gt;"",Teilnehmer!B30&amp;", "&amp;Teilnehmer!C30,"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="37">
-        <f>IF(Teilnehmer!D30&lt;&gt;"",Teilnehmer!D30,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>Ansprechpartner:</t>
-        </is>
-      </c>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>Dr. Schmidt, Sabine</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>Lehrkraft:</t>
-        </is>
-      </c>
-      <c r="E68" s="31">
+    <row r="73" ht="16.5" customHeight="1"/>
+    <row r="74" ht="25.5" customHeight="1">
+      <c r="B74" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.0103</t>
+        </is>
+      </c>
+      <c r="C74" s="40">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>Telefon:</t>
-        </is>
-      </c>
-      <c r="C69" s="31" t="inlineStr">
-        <is>
-          <t>07222/91-22111</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>Datum:</t>
-        </is>
-      </c>
-      <c r="E69" s="38">
+    <row r="75" ht="21" customHeight="1"/>
+    <row r="76" ht="26.25" customHeight="1">
+      <c r="B76" s="41">
+        <f>"  "&amp;Teilnehmer!C5</f>
+        <v/>
+      </c>
+      <c r="C76" s="40" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG, PKW Werk</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1"/>
+    <row r="78" ht="15" customHeight="1"/>
+    <row r="79" ht="29.25" customHeight="1">
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="29.25" customHeight="1">
+      <c r="C80" s="40" t="inlineStr">
+        <is>
+          <t>Werksärztlicher Dienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="29.25" customHeight="1">
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>PKW-Werk Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="29.25" customHeight="1">
+      <c r="C82" s="40" t="inlineStr">
+        <is>
+          <t>Mercedesstrasse 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="29.25" customHeight="1">
+      <c r="B83" s="38">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>E-Mail:</t>
-        </is>
-      </c>
-      <c r="C70" s="31" t="inlineStr">
-        <is>
-          <t>sabine.m.schmidt@mercedes-benz.com</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>Registriernr.:</t>
-        </is>
-      </c>
-      <c r="E70" s="31">
-        <f>Teilnehmer!C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="D71" s="30" t="inlineStr">
-        <is>
-          <t>QSEH-Kennziffer:</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>7.0103</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="30" t="inlineStr">
-        <is>
-          <t>Stempel / Anschrift:</t>
-        </is>
-      </c>
-      <c r="D74" s="39" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz AG, Werksärztlicher Dienst</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="D75" s="39" t="inlineStr">
-        <is>
-          <t>Mercedesstr. 1, 76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>Datum:</t>
-        </is>
-      </c>
-      <c r="C76" s="38">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-    </row>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
+          <t>76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="21" customHeight="1"/>
+    <row r="85" ht="9" customHeight="1"/>
+    <row r="86" ht="9" customHeight="1"/>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B4:C4"/>
+  <mergeCells count="16">
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C39:D39"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="B10:B19">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>", "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10:C19">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:B62">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>", "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C53:C62">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.197" right="0.079" top="0.394" bottom="0.394" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="48" min="0" max="16383" man="1"/>
+    <brk id="43" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6268,221 +7602,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Lehrgangsdokumentation</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>gem. Abschnitt 2.4.6 DGUV Grundsatz 304-001</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Angaben zur Ausbildungsstelle</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Bezeichnung</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG</t>
         </is>
       </c>
-      <c r="E6" s="45" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>QSEH-Kennziffer:</t>
         </is>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="46">
         <f>Teilnehmer!F5</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>Straße / Hausnr.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Mercedesstr. 1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>PLZ / Ort</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>76437 Rastatt</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>Angaben zum Seminar</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="46">
+      <c r="B15" s="48">
         <f>IF(Teilnehmer!F4="EH-Ausbildung","X","  ")&amp;" EH-Ausbildung       "&amp;IF(Teilnehmer!F4="EH-Fortbildung","X","  ")&amp;" EH-Fortbildung       "&amp;IF(Teilnehmer!F4="EH-Schulung","X","  ")&amp;" EH-Schulung"</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>Registriernummer:</t>
         </is>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="46">
         <f>Teilnehmer!C5</f>
         <v/>
       </c>
-      <c r="E17" s="45" t="inlineStr">
+      <c r="E17" s="47" t="inlineStr">
         <is>
           <t>Lehrgangsort:</t>
         </is>
       </c>
-      <c r="F17" s="44" t="inlineStr">
+      <c r="F17" s="46" t="inlineStr">
         <is>
           <t>Mercedes-Benz AG, PKW-Werk Rastatt</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="45" t="inlineStr">
         <is>
           <t>(aus dem QSEH-Portal)</t>
         </is>
       </c>
-      <c r="F18" s="43" t="inlineStr">
+      <c r="F18" s="45" t="inlineStr">
         <is>
           <t>Gebäude 39, Gesundheitszentrum 1.OG</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>Lehrgangsdatum:</t>
         </is>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="49">
         <f>Teilnehmer!C3</f>
         <v/>
       </c>
-      <c r="E20" s="45" t="inlineStr">
+      <c r="E20" s="47" t="inlineStr">
         <is>
           <t>Uhrzeit:</t>
         </is>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="46">
         <f>"von "&amp;TEXT(Teilnehmer!F3,"HH:MM")&amp;" Uhr bis "&amp;TEXT(Teilnehmer!H3,"HH:MM")&amp;" Uhr"</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>Name der Lehrkraft:</t>
         </is>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="46">
         <f>Teilnehmer!C4</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>Verantwortlicher Arzt:</t>
         </is>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="46">
         <f>Teilnehmer!C7</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>Masken-Charge:</t>
         </is>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="50">
         <f>Teilnehmer!C8</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>Anzahl der Teilnehmenden</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="45" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>Gesamtanzahl der Teilnehmenden:</t>
         </is>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="51">
         <f>Teilnehmer!C32</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
-      <c r="B31" s="43" t="inlineStr">
+      <c r="B31" s="45" t="inlineStr">
         <is>
           <t>(entspricht der Anzahl der Teilnehmerdatenblätter)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="47" t="inlineStr">
         <is>
           <t>davon betriebliche Ersthelfende:</t>
         </is>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="51">
         <f>Teilnehmer!E32</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B35" s="44" t="inlineStr">
         <is>
           <t>Anlagen</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="B36" s="46" t="inlineStr">
+      <c r="B36" s="48" t="inlineStr">
         <is>
           <t>Alle Teilnehmenden sind mit Namen, Vornamen, Geburtsdatum und Unterschrift zu erfassen. Für UVT-Teilnehmende sind zusätzlich der Name und die Anschrift des Arbeitgebers sowie der kostentragende UVT zu ergänzen. Dies kann durch einzelne Teilnehmerdatenblätter erfolgen.</t>
         </is>
@@ -6491,43 +7825,43 @@
     <row r="37" ht="16" customHeight="1"/>
     <row r="38" ht="16" customHeight="1"/>
     <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="46" t="inlineStr">
+      <c r="B40" s="48" t="inlineStr">
         <is>
           <t>Die Dokumentation ist fünf Jahre aufzubewahren und auf Anforderung dem Unfallversicherungsträger vorzulegen.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="45" t="inlineStr">
+      <c r="B42" s="47" t="inlineStr">
         <is>
           <t>Für die Richtigkeit der Angaben:</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="50">
+      <c r="B47" s="52">
         <f>"Rastatt, "&amp;TEXT(Teilnehmer!C3,"DD.MM.YYYY")</f>
         <v/>
       </c>
-      <c r="E47" s="50">
+      <c r="E47" s="52">
         <f>"Rastatt, "&amp;TEXT(Teilnehmer!C3,"DD.MM.YYYY")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
-      <c r="B48" s="43" t="inlineStr">
+      <c r="B48" s="45" t="inlineStr">
         <is>
           <t>Ort, Datum     Unterschrift Lehrgangsleitung</t>
         </is>
       </c>
-      <c r="E48" s="43" t="inlineStr">
+      <c r="E48" s="45" t="inlineStr">
         <is>
           <t>Ort, Datum     Unterschrift Ausbildungsstelle</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="B50" s="51" t="inlineStr">
+      <c r="B50" s="53" t="inlineStr">
         <is>
           <t>Stand: 2026</t>
         </is>
@@ -6577,49 +7911,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Putschler, Walter</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Kaya, Michelle</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Krempl, Elke</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Breig, Bernd</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Zuber, Harry</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Jochim, Benjamin</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Siebert, Emanuel</t>
         </is>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -10,15 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teilnehmer" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bescheinigungen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BG-Liste" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BG-Liste_2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lehrgangsdoku" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hilfslisten" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lehrgangsdoku" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hilfslisten" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Lehrkraefte">Hilfslisten!$A$2:$A$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bescheinigungen'!$A$1:$AZ$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'BG-Liste'!$A$1:$E$51</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'BG-Liste_2'!$A$1:$E$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'BG-Liste'!$A$1:$E$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3343,1114 +3340,812 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>219075</colOff>
-      <row>7</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <to>
       <col>1</col>
       <colOff>38174</colOff>
-      <row>19</row>
+      <row>62</row>
       <rowOff>29419</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Grafik 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="219075" y="3495675"/>
-          <a:ext cx="533474" cy="6049219"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>3</col>
       <colOff>2686050</colOff>
-      <row>8</row>
+      <row>51</row>
       <rowOff>409575</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1381322</colOff>
-      <row>19</row>
+      <row>62</row>
       <rowOff>210289</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Grafik 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="10134600" y="4429125"/>
-          <a:ext cx="1409897" cy="5296639"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>190500</colOff>
-      <row>0</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1401762</colOff>
-      <row>4</row>
+      <row>47</row>
       <rowOff>19336</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Grafik 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="190500" y="0"/>
-          <a:ext cx="11374437" cy="2048161"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>228600</colOff>
-      <row>0</row>
+      <row>43</row>
       <rowOff>19050</rowOff>
     </from>
     <to>
       <col>1</col>
       <colOff>28647</colOff>
-      <row>8</row>
+      <row>51</row>
       <rowOff>276822</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Grafik 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="228600" y="19050"/>
-          <a:ext cx="514422" cy="4277322"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>219075</colOff>
-      <row>6</row>
+      <row>49</row>
       <rowOff>400050</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1392232</colOff>
-      <row>9</row>
+      <row>52</row>
       <rowOff>114452</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Grafik 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="219075" y="3486150"/>
-          <a:ext cx="11336332" cy="1086002"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>542925</colOff>
-      <row>4</row>
+      <row>47</row>
       <rowOff>495300</rowOff>
     </from>
     <to>
       <col>2</col>
       <colOff>1267607</colOff>
-      <row>5</row>
+      <row>48</row>
       <rowOff>276269</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Grafik 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="542925" y="2524125"/>
-          <a:ext cx="5601482" cy="314369"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>1</col>
       <colOff>3914775</colOff>
-      <row>2</row>
+      <row>45</row>
       <rowOff>476250</rowOff>
     </from>
     <to>
       <col>2</col>
       <colOff>1562353</colOff>
-      <row>7</row>
+      <row>50</row>
       <rowOff>219379</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Grafik 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4629150" y="1533525"/>
-          <a:ext cx="1810003" cy="2181529"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>285750</colOff>
-      <row>5</row>
+      <row>48</row>
       <rowOff>466725</rowOff>
     </from>
     <to>
       <col>2</col>
       <colOff>810379</colOff>
-      <row>6</row>
+      <row>49</row>
       <rowOff>181008</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Grafik 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="285750" y="3028950"/>
-          <a:ext cx="5401429" cy="238158"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>4</col>
       <colOff>942975</colOff>
-      <row>2</row>
+      <row>45</row>
       <rowOff>161925</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1381186</colOff>
-      <row>7</row>
+      <row>50</row>
       <rowOff>209897</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Grafik 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="11106150" y="1219200"/>
-          <a:ext cx="438211" cy="2486372"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>2</col>
       <colOff>1019175</colOff>
-      <row>5</row>
+      <row>48</row>
       <rowOff>142875</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1277124</colOff>
-      <row>5</row>
+      <row>48</row>
       <rowOff>447718</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Grafik 10"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5895975" y="2705100"/>
-          <a:ext cx="5544324" cy="304843"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>2</col>
       <colOff>1047750</colOff>
-      <row>3</row>
+      <row>46</row>
       <rowOff>209550</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1172330</colOff>
-      <row>4</row>
+      <row>47</row>
       <rowOff>200091</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Grafik 11"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5924550" y="1752600"/>
-          <a:ext cx="5410955" cy="476316"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>200025</colOff>
-      <row>19</row>
+      <row>62</row>
       <rowOff>66675</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1392235</colOff>
-      <row>20</row>
+      <row>63</row>
       <rowOff>304908</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Grafik 12"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="200025" y="9582150"/>
-          <a:ext cx="11355385" cy="771633"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>190500</colOff>
-      <row>20</row>
+      <row>63</row>
       <rowOff>47625</rowOff>
     </from>
     <to>
       <col>1</col>
       <colOff>857443</colOff>
-      <row>27</row>
+      <row>70</row>
       <rowOff>95632</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Grafik 13"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="190500" y="10096500"/>
-          <a:ext cx="1381318" cy="2734057"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>171450</colOff>
-      <row>23</row>
+      <row>66</row>
       <rowOff>342900</rowOff>
     </from>
     <to>
       <col>2</col>
       <colOff>2058344</colOff>
-      <row>25</row>
+      <row>68</row>
       <rowOff>219168</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Grafik 14"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="171450" y="11563350"/>
-          <a:ext cx="6763694" cy="666843"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>2</col>
       <colOff>876300</colOff>
-      <row>20</row>
+      <row>63</row>
       <rowOff>38100</rowOff>
     </from>
     <to>
       <col>2</col>
       <colOff>1076353</colOff>
-      <row>25</row>
+      <row>68</row>
       <rowOff>19321</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Grafik 15"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5753100" y="10086975"/>
-          <a:ext cx="200053" cy="1943371"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>2</col>
       <colOff>2057400</colOff>
-      <row>24</row>
+      <row>67</row>
       <rowOff>95250</rowOff>
     </from>
     <to>
       <col>3</col>
       <colOff>276335</colOff>
-      <row>25</row>
+      <row>68</row>
       <rowOff>28619</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Grafik 16"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6934200" y="11725275"/>
-          <a:ext cx="790685" cy="314369"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>3</col>
       <colOff>209550</colOff>
-      <row>24</row>
+      <row>67</row>
       <rowOff>314325</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1372141</colOff>
-      <row>27</row>
+      <row>70</row>
       <rowOff>85847</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Grafik 17"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="7658100" y="11944350"/>
-          <a:ext cx="3877216" cy="876422"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>4</col>
       <colOff>904875</colOff>
-      <row>20</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1409770</colOff>
-      <row>25</row>
+      <row>68</row>
       <rowOff>200327</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Grafik 18"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="11068050" y="10048875"/>
-          <a:ext cx="504895" cy="2162477"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>285750</colOff>
-      <row>25</row>
+      <row>68</row>
       <rowOff>60846</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>1401749</colOff>
-      <row>27</row>
+      <row>70</row>
       <rowOff>97346</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="20" name="Grafik 19"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="285750" y="12071871"/>
-          <a:ext cx="11279174" cy="760400"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>3</col>
       <colOff>2679539</colOff>
-      <row>25</row>
+      <row>68</row>
       <rowOff>265132</rowOff>
     </from>
     <to>
       <col>5</col>
       <colOff>3217</colOff>
-      <row>42</row>
+      <row>85</row>
       <rowOff>94584</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="21" name="Grafik 20"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="10128089" y="12276157"/>
-          <a:ext cx="1457528" cy="4734827"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>284664</colOff>
-      <row>31</row>
+      <row>74</row>
       <rowOff>54852</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>590925</colOff>
-      <row>32</row>
+      <row>75</row>
       <rowOff>45363</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="22" name="Grafik 21"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="284664" y="13751802"/>
-          <a:ext cx="10469436" cy="257211"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>2</col>
       <colOff>841214</colOff>
-      <row>27</row>
+      <row>70</row>
       <rowOff>43899</rowOff>
     </from>
     <to>
       <col>2</col>
       <colOff>993635</colOff>
-      <row>42</row>
+      <row>85</row>
       <rowOff>111408</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="23" name="Grafik 22"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5718014" y="12778824"/>
-          <a:ext cx="152421" cy="4248984"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>192234</colOff>
-      <row>29</row>
+      <row>72</row>
       <rowOff>7900</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>946233</colOff>
-      <row>30</row>
+      <row>73</row>
       <rowOff>55561</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="24" name="Grafik 23"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="192234" y="13171450"/>
-          <a:ext cx="10917174" cy="257211"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>180975</colOff>
-      <row>33</row>
+      <row>76</row>
       <rowOff>14208</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>830184</colOff>
-      <row>34</row>
+      <row>77</row>
       <rowOff>99972</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Grafik 24"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="180975" y="14311233"/>
-          <a:ext cx="10812384" cy="276264"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>193031</colOff>
-      <row>39</row>
+      <row>82</row>
       <rowOff>312275</rowOff>
     </from>
     <to>
       <col>4</col>
       <colOff>594555</colOff>
-      <row>42</row>
+      <row>85</row>
       <rowOff>112568</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Grafik 25"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="193031" y="16476200"/>
-          <a:ext cx="10564699" cy="552768"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>171450</colOff>
-      <row>26</row>
+      <row>69</row>
       <rowOff>197975</rowOff>
     </from>
     <to>
       <col>0</col>
       <colOff>285766</colOff>
-      <row>40</row>
+      <row>83</row>
       <rowOff>198561</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Grafik 26"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="171450" y="12532850"/>
-          <a:ext cx="114316" cy="4201111"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>1</col>
       <colOff>304800</colOff>
-      <row>39</row>
+      <row>82</row>
       <rowOff>47625</rowOff>
     </from>
     <to>
       <col>1</col>
       <colOff>1028801</colOff>
-      <row>39</row>
+      <row>82</row>
       <rowOff>314362</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Grafik 27"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1019175" y="16211550"/>
-          <a:ext cx="724001" cy="266737"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -12208,7 +11903,7 @@
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
   <pageMargins left="0.3149606299212598" right="0.3149606299212598" top="0.3937007874015748" bottom="0.3937007874015748" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToWidth="0"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToWidth="0"/>
   <rowBreaks count="8" manualBreakCount="8">
     <brk id="38" min="0" max="16383" man="1"/>
     <brk id="77" min="0" max="16383" man="1"/>
@@ -12230,7 +11925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" customWidth="1" min="1" max="1"/>
@@ -12541,359 +12236,335 @@
     <row r="41" ht="21" customHeight="1"/>
     <row r="42" ht="9" customHeight="1"/>
     <row r="43" ht="9" customHeight="1"/>
+    <row r="44" ht="42" customHeight="1"/>
+    <row r="45" ht="41.25" customHeight="1">
+      <c r="D45" s="35" t="n"/>
+      <c r="J45">
+        <f>IF(Teilnehmer!F3,Teilnehmer!F3,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="38.25" customHeight="1">
+      <c r="D46" s="35" t="n"/>
+    </row>
+    <row r="47" ht="38.25" customHeight="1">
+      <c r="D47" s="36" t="n"/>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="inlineStr">
+        <is>
+          <t>BG-Metall Nord-Süd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="41.25" customHeight="1">
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>Mercedsstr. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32.25" customHeight="1">
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>76437 Rastatt</t>
+        </is>
+      </c>
+      <c r="D50" s="40" t="n">
+        <v>2.26255682176001e+19</v>
+      </c>
+    </row>
+    <row r="51" ht="41.25" customHeight="1">
+      <c r="D51" s="41" t="n"/>
+    </row>
+    <row r="52" ht="34.5" customHeight="1">
+      <c r="D52" s="36" t="n"/>
+    </row>
+    <row r="53" ht="39.75" customHeight="1">
+      <c r="A53" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="43">
+        <f>CONCATENATE(Teilnehmer!B21,", ",Teilnehmer!C21)</f>
+        <v/>
+      </c>
+      <c r="C53" s="44">
+        <f>IF(Teilnehmer!D21,Teilnehmer!D21,"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="45" t="n"/>
+    </row>
+    <row r="54" ht="39.75" customHeight="1">
+      <c r="A54" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="43">
+        <f>CONCATENATE(Teilnehmer!B22,", ",Teilnehmer!C22)</f>
+        <v/>
+      </c>
+      <c r="C54" s="44">
+        <f>IF(Teilnehmer!D22,Teilnehmer!D22,"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="46" t="n"/>
+    </row>
+    <row r="55" ht="39.75" customHeight="1">
+      <c r="A55" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="43">
+        <f>CONCATENATE(Teilnehmer!B23,", ",Teilnehmer!C23)</f>
+        <v/>
+      </c>
+      <c r="C55" s="44">
+        <f>IF(Teilnehmer!D23,Teilnehmer!D23,"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="45" t="n"/>
+    </row>
+    <row r="56" ht="39.75" customHeight="1">
+      <c r="A56" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="43">
+        <f>CONCATENATE(Teilnehmer!B24,", ",Teilnehmer!C24)</f>
+        <v/>
+      </c>
+      <c r="C56" s="44">
+        <f>IF(Teilnehmer!D24,Teilnehmer!D24,"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="45" t="n"/>
+    </row>
+    <row r="57" ht="40.5" customHeight="1">
+      <c r="A57" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="43">
+        <f>CONCATENATE(Teilnehmer!B25,", ",Teilnehmer!C25)</f>
+        <v/>
+      </c>
+      <c r="C57" s="44">
+        <f>IF(Teilnehmer!D25,Teilnehmer!D25,"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="45" t="n"/>
+    </row>
+    <row r="58" ht="39.75" customHeight="1">
+      <c r="A58" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="43">
+        <f>CONCATENATE(Teilnehmer!B26,", ",Teilnehmer!C26)</f>
+        <v/>
+      </c>
+      <c r="C58" s="44">
+        <f>IF(Teilnehmer!D26,Teilnehmer!D26,"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="45" t="n"/>
+    </row>
+    <row r="59" ht="40.5" customHeight="1">
+      <c r="A59" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="43">
+        <f>CONCATENATE(Teilnehmer!B27,", ",Teilnehmer!C27)</f>
+        <v/>
+      </c>
+      <c r="C59" s="44">
+        <f>IF(Teilnehmer!D27,Teilnehmer!D27,"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="45" t="n"/>
+    </row>
+    <row r="60" ht="39" customHeight="1">
+      <c r="A60" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="43">
+        <f>CONCATENATE(Teilnehmer!B28,", ",Teilnehmer!C28)</f>
+        <v/>
+      </c>
+      <c r="C60" s="44">
+        <f>IF(Teilnehmer!D28,Teilnehmer!D28,"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="45" t="n"/>
+    </row>
+    <row r="61" ht="39.75" customHeight="1">
+      <c r="A61" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="43">
+        <f>CONCATENATE(Teilnehmer!B29,", ",Teilnehmer!C29)</f>
+        <v/>
+      </c>
+      <c r="C61" s="44">
+        <f>IF(Teilnehmer!D29,Teilnehmer!D29,"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="47" t="n"/>
+    </row>
+    <row r="62" ht="39.75" customHeight="1">
+      <c r="A62" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="43">
+        <f>CONCATENATE(Teilnehmer!B30,", ",Teilnehmer!C30)</f>
+        <v/>
+      </c>
+      <c r="C62" s="44">
+        <f>IF(Teilnehmer!D30,Teilnehmer!D30,"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="45" t="n"/>
+    </row>
+    <row r="63" ht="42" customHeight="1"/>
+    <row r="64" ht="27.75" customHeight="1"/>
+    <row r="65" ht="32.25" customHeight="1">
+      <c r="B65" s="48" t="inlineStr">
+        <is>
+          <t>Dr. Schmidt, Sabine</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32.25" customHeight="1">
+      <c r="B66" s="48" t="inlineStr">
+        <is>
+          <t>07222/91-22111</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32.25" customHeight="1">
+      <c r="B67" s="55" t="inlineStr">
+        <is>
+          <t>sabine.m.schmidt@mercedes-benz.com</t>
+        </is>
+      </c>
+      <c r="D67" s="50" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="D68" s="51">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="25.5" customHeight="1"/>
+    <row r="70" ht="31.5" customHeight="1">
+      <c r="C70" s="51" t="n"/>
+    </row>
+    <row r="71" ht="8.25" customHeight="1"/>
+    <row r="72" ht="25.5" customHeight="1">
+      <c r="C72" s="51">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16.5" customHeight="1"/>
+    <row r="74" ht="25.5" customHeight="1">
+      <c r="B74" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.0103</t>
+        </is>
+      </c>
+      <c r="C74" s="50">
+        <f>Teilnehmer!C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="21" customHeight="1">
+      <c r="B75" s="53" t="n"/>
+    </row>
+    <row r="76" ht="26.25" customHeight="1">
+      <c r="B76" s="54">
+        <f>"  "&amp;Teilnehmer!C5</f>
+        <v/>
+      </c>
+      <c r="C76" s="50" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG, PKW Werk</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79" ht="29.25" customHeight="1">
+      <c r="C79" s="50" t="inlineStr">
+        <is>
+          <t>Mercedes Benz AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="29.25" customHeight="1">
+      <c r="C80" s="50" t="inlineStr">
+        <is>
+          <t>Werksärztlicher Dienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="29.25" customHeight="1">
+      <c r="C81" s="50" t="inlineStr">
+        <is>
+          <t>PKW-Werk Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="29.25" customHeight="1">
+      <c r="C82" s="50" t="inlineStr">
+        <is>
+          <t>Mercedesstraße 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="29.25" customHeight="1">
+      <c r="B83" s="51">
+        <f>Teilnehmer!C3</f>
+        <v/>
+      </c>
+      <c r="C83" s="50" t="inlineStr">
+        <is>
+          <t>76437 Rastatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="21" customHeight="1"/>
+    <row r="85" ht="9" customHeight="1"/>
+    <row r="86" ht="9" customHeight="1"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="16">
+    <mergeCell ref="C83:D83"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C82:D82"/>
     <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C76:D76"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C74:D74"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C79:D79"/>
     <mergeCell ref="C39:D39"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.07874015748031496" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="43" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF6F00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10.6640625" customWidth="1" min="1" max="1"/>
-    <col width="62.44140625" customWidth="1" min="2" max="2"/>
-    <col width="38.5546875" customWidth="1" min="3" max="3"/>
-    <col width="40.6640625" customWidth="1" min="4" max="4"/>
-    <col width="21.33203125" customWidth="1" min="5" max="5"/>
-    <col width="4.33203125" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1"/>
-    <row r="2" ht="41.25" customHeight="1">
-      <c r="D2" s="35" t="n"/>
-      <c r="J2">
-        <f>IF(Teilnehmer!F3,Teilnehmer!F3,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="38.25" customHeight="1">
-      <c r="D3" s="35" t="n"/>
-    </row>
-    <row r="4" ht="38.25" customHeight="1">
-      <c r="D4" s="36" t="n"/>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>Mercedes Benz AG</t>
-        </is>
-      </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>BG-Metall Nord-Süd</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="41.25" customHeight="1">
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Mercedsstr. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32.25" customHeight="1">
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>76437 Rastatt</t>
-        </is>
-      </c>
-      <c r="D7" s="40" t="n">
-        <v>2.26255682176001e+19</v>
-      </c>
-    </row>
-    <row r="8" ht="41.25" customHeight="1">
-      <c r="D8" s="41" t="n"/>
-    </row>
-    <row r="9" ht="34.5" customHeight="1">
-      <c r="D9" s="36" t="n"/>
-    </row>
-    <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="43">
-        <f>CONCATENATE(Teilnehmer!B21,", ",Teilnehmer!C21)</f>
-        <v/>
-      </c>
-      <c r="C10" s="44">
-        <f>IF(Teilnehmer!D21,Teilnehmer!D21,"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="45" t="n"/>
-    </row>
-    <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="43">
-        <f>CONCATENATE(Teilnehmer!B22,", ",Teilnehmer!C22)</f>
-        <v/>
-      </c>
-      <c r="C11" s="44">
-        <f>IF(Teilnehmer!D22,Teilnehmer!D22,"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="46" t="n"/>
-    </row>
-    <row r="12" ht="39.75" customHeight="1">
-      <c r="A12" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="43">
-        <f>CONCATENATE(Teilnehmer!B23,", ",Teilnehmer!C23)</f>
-        <v/>
-      </c>
-      <c r="C12" s="44">
-        <f>IF(Teilnehmer!D23,Teilnehmer!D23,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="45" t="n"/>
-    </row>
-    <row r="13" ht="39.75" customHeight="1">
-      <c r="A13" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="43">
-        <f>CONCATENATE(Teilnehmer!B24,", ",Teilnehmer!C24)</f>
-        <v/>
-      </c>
-      <c r="C13" s="44">
-        <f>IF(Teilnehmer!D24,Teilnehmer!D24,"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="45" t="n"/>
-    </row>
-    <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="43">
-        <f>CONCATENATE(Teilnehmer!B25,", ",Teilnehmer!C25)</f>
-        <v/>
-      </c>
-      <c r="C14" s="44">
-        <f>IF(Teilnehmer!D25,Teilnehmer!D25,"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="45" t="n"/>
-    </row>
-    <row r="15" ht="39.75" customHeight="1">
-      <c r="A15" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="43">
-        <f>CONCATENATE(Teilnehmer!B26,", ",Teilnehmer!C26)</f>
-        <v/>
-      </c>
-      <c r="C15" s="44">
-        <f>IF(Teilnehmer!D26,Teilnehmer!D26,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="45" t="n"/>
-    </row>
-    <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" s="43">
-        <f>CONCATENATE(Teilnehmer!B27,", ",Teilnehmer!C27)</f>
-        <v/>
-      </c>
-      <c r="C16" s="44">
-        <f>IF(Teilnehmer!D27,Teilnehmer!D27,"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="45" t="n"/>
-    </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="43">
-        <f>CONCATENATE(Teilnehmer!B28,", ",Teilnehmer!C28)</f>
-        <v/>
-      </c>
-      <c r="C17" s="44">
-        <f>IF(Teilnehmer!D28,Teilnehmer!D28,"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="45" t="n"/>
-    </row>
-    <row r="18" ht="39.75" customHeight="1">
-      <c r="A18" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="43">
-        <f>CONCATENATE(Teilnehmer!B29,", ",Teilnehmer!C29)</f>
-        <v/>
-      </c>
-      <c r="C18" s="44">
-        <f>IF(Teilnehmer!D29,Teilnehmer!D29,"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="47" t="n"/>
-    </row>
-    <row r="19" ht="39.75" customHeight="1">
-      <c r="A19" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="43">
-        <f>CONCATENATE(Teilnehmer!B30,", ",Teilnehmer!C30)</f>
-        <v/>
-      </c>
-      <c r="C19" s="44">
-        <f>IF(Teilnehmer!D30,Teilnehmer!D30,"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="45" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1"/>
-    <row r="21" ht="27.75" customHeight="1"/>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>Dr. Schmidt, Sabine</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32.25" customHeight="1">
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>07222/91-22111</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32.25" customHeight="1">
-      <c r="B24" s="55" t="inlineStr">
-        <is>
-          <t>sabine.m.schmidt@mercedes-benz.com</t>
-        </is>
-      </c>
-      <c r="D24" s="50" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="D25" s="51">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="25.5" customHeight="1"/>
-    <row r="27" ht="31.5" customHeight="1">
-      <c r="C27" s="51" t="n"/>
-    </row>
-    <row r="28" ht="8.25" customHeight="1"/>
-    <row r="29" ht="25.5" customHeight="1">
-      <c r="C29" s="51">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1"/>
-    <row r="31" ht="25.5" customHeight="1">
-      <c r="B31" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.0103</t>
-        </is>
-      </c>
-      <c r="C31" s="50">
-        <f>Teilnehmer!C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="B32" s="53" t="n"/>
-    </row>
-    <row r="33" ht="26.25" customHeight="1">
-      <c r="B33" s="54">
-        <f>"  "&amp;Teilnehmer!C5</f>
-        <v/>
-      </c>
-      <c r="C33" s="50" t="inlineStr">
-        <is>
-          <t>Mercedes Benz AG, PKW Werk</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36" ht="29.25" customHeight="1">
-      <c r="C36" s="50" t="inlineStr">
-        <is>
-          <t>Mercedes Benz AG</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="29.25" customHeight="1">
-      <c r="C37" s="50" t="inlineStr">
-        <is>
-          <t>Werksärztlicher Dienst</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="29.25" customHeight="1">
-      <c r="C38" s="50" t="inlineStr">
-        <is>
-          <t>PKW-Werk Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="29.25" customHeight="1">
-      <c r="C39" s="50" t="inlineStr">
-        <is>
-          <t>Mercedesstraße 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="29.25" customHeight="1">
-      <c r="B40" s="51">
-        <f>Teilnehmer!C3</f>
-        <v/>
-      </c>
-      <c r="C40" s="50" t="inlineStr">
-        <is>
-          <t>76437 Rastatt</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="21" customHeight="1"/>
-    <row r="42" ht="9" customHeight="1"/>
-    <row r="43" ht="9" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C39:D39"/>
-  </mergeCells>
-  <pageMargins left="0.1968503937007874" right="0.07874015748031496" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A1B9A"/>
@@ -13201,7 +12872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009E9E9E"/>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -4826,9 +4826,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.7109375" customWidth="1" min="1" max="1"/>
+    <col width="2.7109375" customWidth="1" min="2" max="2"/>
+    <col width="2.7109375" customWidth="1" min="3" max="3"/>
+    <col width="2.7109375" customWidth="1" min="4" max="4"/>
+    <col width="2.7109375" customWidth="1" min="5" max="5"/>
+    <col width="2.7109375" customWidth="1" min="6" max="6"/>
+    <col width="2.7109375" customWidth="1" min="7" max="7"/>
+    <col width="2.7109375" customWidth="1" min="8" max="8"/>
+    <col width="2.7109375" customWidth="1" min="9" max="9"/>
+    <col width="2.7109375" customWidth="1" min="10" max="10"/>
+    <col width="2.7109375" customWidth="1" min="11" max="11"/>
+    <col width="2.7109375" customWidth="1" min="12" max="12"/>
+    <col width="2.7109375" customWidth="1" min="13" max="13"/>
+    <col width="2.7109375" customWidth="1" min="14" max="14"/>
+    <col width="2.7109375" customWidth="1" min="15" max="15"/>
+    <col width="2.7109375" customWidth="1" min="16" max="16"/>
+    <col width="2.7109375" customWidth="1" min="17" max="17"/>
+    <col width="2.7109375" customWidth="1" min="18" max="18"/>
+    <col width="2.7109375" customWidth="1" min="19" max="19"/>
+    <col width="2.7109375" customWidth="1" min="20" max="20"/>
+    <col width="2.7109375" customWidth="1" min="21" max="21"/>
+    <col width="2.7109375" customWidth="1" min="22" max="22"/>
+    <col width="2.7109375" customWidth="1" min="23" max="23"/>
+    <col width="2.7109375" customWidth="1" min="24" max="24"/>
+    <col width="2.7109375" customWidth="1" min="25" max="25"/>
     <col width="2.42578125" customWidth="1" min="26" max="26"/>
+    <col width="2.42578125" customWidth="1" min="27" max="27"/>
     <col width="2.5703125" customWidth="1" min="28" max="28"/>
     <col width="2.7109375" customWidth="1" min="29" max="29"/>
+    <col width="2.7109375" customWidth="1" min="30" max="30"/>
+    <col width="2.7109375" customWidth="1" min="31" max="31"/>
+    <col width="2.7109375" customWidth="1" min="32" max="32"/>
+    <col width="2.7109375" customWidth="1" min="33" max="33"/>
+    <col width="2.7109375" customWidth="1" min="34" max="34"/>
+    <col width="2.7109375" customWidth="1" min="35" max="35"/>
+    <col width="2.7109375" customWidth="1" min="36" max="36"/>
+    <col width="2.7109375" customWidth="1" min="37" max="37"/>
+    <col width="2.7109375" customWidth="1" min="38" max="38"/>
+    <col width="2.7109375" customWidth="1" min="39" max="39"/>
+    <col width="2.7109375" customWidth="1" min="40" max="40"/>
+    <col width="2.7109375" customWidth="1" min="41" max="41"/>
+    <col width="2.7109375" customWidth="1" min="42" max="42"/>
+    <col width="2.7109375" customWidth="1" min="43" max="43"/>
+    <col width="2.7109375" customWidth="1" min="44" max="44"/>
+    <col width="2.7109375" customWidth="1" min="45" max="45"/>
+    <col width="2.7109375" customWidth="1" min="46" max="46"/>
+    <col width="2.7109375" customWidth="1" min="47" max="47"/>
+    <col width="2.7109375" customWidth="1" min="48" max="48"/>
+    <col width="2.7109375" customWidth="1" min="49" max="49"/>
+    <col width="2.7109375" customWidth="1" min="50" max="50"/>
+    <col width="2.7109375" customWidth="1" min="51" max="51"/>
+    <col width="2.7109375" customWidth="1" min="52" max="52"/>
     <col width="9.140625" customWidth="1" min="53" max="53"/>
     <col width="10.140625" customWidth="1" min="57" max="57"/>
     <col width="9.140625" customWidth="1" min="58" max="58"/>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -15,6 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="Lehrkraefte">Hilfslisten!$A$2:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bescheinigungen'!$A$1:$AZ$388</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'BG-Liste'!$A$1:$E$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4820,7 +4821,7 @@
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BE388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -11951,7 +11952,7 @@
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
   <pageMargins left="0.3149606299212598" right="0.3149606299212598" top="0.3937007874015748" bottom="0.3937007874015748" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToWidth="0"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="8" manualBreakCount="8">
     <brk id="38" min="0" max="16383" man="1"/>
     <brk id="77" min="0" max="16383" man="1"/>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -12,9 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lehrgangsdoku" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hilfslisten" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Lehrkraefte">Hilfslisten!$A$2:$A$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Bescheinigungen'!$A$1:$AZ$37</definedName>
@@ -652,3715 +649,4399 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>36</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <to>
-      <col>23</col>
-      <colOff>169404</colOff>
-      <row>37</row>
-      <rowOff>166670</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Grafik 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>169404</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>166670</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Grafik 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="19178" y="6702830"/>
           <a:ext cx="4340587" cy="204855"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>7</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Grafik 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Grafik 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="4363331" cy="1438977"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>159372</colOff>
-      <row>0</row>
-      <rowOff>3197</rowOff>
-    </from>
-    <to>
-      <col>51</col>
-      <colOff>162256</colOff>
-      <row>7</row>
-      <rowOff>167384</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Grafik 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>159372</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3197</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>162256</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167384</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Grafik 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5040135" y="3197"/>
           <a:ext cx="4365846" cy="1439514"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>22374</colOff>
-      <row>36</row>
-      <rowOff>139679</rowOff>
-    </from>
-    <to>
-      <col>51</col>
-      <colOff>158020</colOff>
-      <row>37</row>
-      <rowOff>160826</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Grafik 13"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>22374</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>139679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>158020</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>160826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Grafik 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="5075738" y="6698505"/>
           <a:ext cx="4326007" cy="203336"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>46</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Grafik 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Grafik 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="6877050"/>
           <a:ext cx="4346153" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>46</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Grafik 44"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Grafik 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="6659104"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Grafik 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Grafik 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Grafik 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Grafik 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Grafik 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Grafik 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Grafik 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Grafik 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Grafik 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Grafik 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Grafik 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Grafik 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Grafik 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>348</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Grafik 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>348</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Grafik 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>387</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Grafik 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>387</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Grafik 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Grafik 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="6877050"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>85</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Grafik 45"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Grafik 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="13754100"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>85</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Grafik 46"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Grafik 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="13754100"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>124</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Grafik 47"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Grafik 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="20631150"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>171450</colOff>
-      <row>117</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>125</row>
-      <rowOff>1407</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Grafik 48"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>1407</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Grafik 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5276850" y="20640675"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>156</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>163</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Grafik 50"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Grafik 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="27508200"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>156</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>163</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Grafik 51"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Grafik 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="27508200"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>202</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Grafik 52"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Grafik 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="34385250"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>202</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Grafik 53"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Grafik 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="34385250"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>234</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>241</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Grafik 54"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Grafik 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="41262300"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>234</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>241</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Grafik 55"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Grafik 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="41262300"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>273</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>280</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Grafik 56"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>280</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Grafik 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="48139350"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>273</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>280</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Grafik 57"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>280</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Grafik 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="48139350"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>312</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>319</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Grafik 58"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>312</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>319</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Grafik 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="55016400"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>312</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>319</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Grafik 59"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>312</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>319</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Grafik 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="55016400"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>351</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>358</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Grafik 60"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>351</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>358</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Grafik 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="61893450"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>351</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>358</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Grafik 61"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>351</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>358</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Grafik 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5286375" y="61893450"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>75</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Grafik 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="6659104"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>75</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Grafik 10"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>114</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Grafik 12"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>114</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Grafik 15"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>153</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Grafik 17"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>153</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Grafik 19"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>192</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Grafik 21"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>192</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Grafik 23"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>231</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Grafik 25"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>231</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Grafik 27"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>270</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Grafik 29"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>270</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Grafik 31"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>309</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Grafik 33"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>309</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Grafik 35"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>348</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Grafik 37"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>348</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Grafik 39"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>387</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Grafik 41"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>387</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Grafik 43"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>38174</colOff>
-      <row>19</row>
-      <rowOff>29419</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Grafik 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38174</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>29419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Grafik 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="219075" y="3495675"/>
           <a:ext cx="533474" cy="6049219"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>2686050</colOff>
-      <row>8</row>
-      <rowOff>409575</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381322</colOff>
-      <row>19</row>
-      <rowOff>210289</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Grafik 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2686050</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381322</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>210289</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Grafik 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="10134600" y="4429125"/>
           <a:ext cx="1409897" cy="5296639"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401762</colOff>
-      <row>4</row>
-      <rowOff>19336</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Grafik 32"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401762</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19336</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Grafik 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="190500" y="0"/>
           <a:ext cx="11374437" cy="2048161"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>228600</colOff>
-      <row>0</row>
-      <rowOff>19050</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>28647</colOff>
-      <row>8</row>
-      <rowOff>276822</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Grafik 33"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28647</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>276822</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Grafik 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="228600" y="19050"/>
           <a:ext cx="514422" cy="4277322"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>6</row>
-      <rowOff>400050</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392232</colOff>
-      <row>9</row>
-      <rowOff>114452</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Grafik 34"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392232</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Grafik 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="219075" y="3486150"/>
           <a:ext cx="11336332" cy="1086002"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>542925</colOff>
-      <row>4</row>
-      <rowOff>495300</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1267607</colOff>
-      <row>5</row>
-      <rowOff>276269</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Grafik 36"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>495300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1267607</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>276269</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Grafik 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="542925" y="2524125"/>
           <a:ext cx="5601482" cy="314369"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>3914775</colOff>
-      <row>2</row>
-      <rowOff>476250</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1562353</colOff>
-      <row>7</row>
-      <rowOff>219379</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Grafik 37"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3914775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1562353</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>219379</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Grafik 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="4629150" y="1533525"/>
           <a:ext cx="1810003" cy="2181529"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>5</row>
-      <rowOff>466725</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>810379</colOff>
-      <row>6</row>
-      <rowOff>181008</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Grafik 38"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>466725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>810379</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>181008</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Grafik 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="285750" y="3028950"/>
           <a:ext cx="5401429" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>942975</colOff>
-      <row>2</row>
-      <rowOff>161925</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381186</colOff>
-      <row>7</row>
-      <rowOff>209897</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Grafik 39"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381186</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>209897</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Grafik 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="11106150" y="1219200"/>
           <a:ext cx="438211" cy="2486372"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1019175</colOff>
-      <row>5</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1277124</colOff>
-      <row>5</row>
-      <rowOff>447718</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Grafik 40"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1277124</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>447718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Grafik 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="5895975" y="2705100"/>
           <a:ext cx="5544324" cy="304843"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1047750</colOff>
-      <row>3</row>
-      <rowOff>209550</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1172330</colOff>
-      <row>4</row>
-      <rowOff>200091</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Grafik 41"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1172330</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>200091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Grafik 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="5924550" y="1752600"/>
           <a:ext cx="5410955" cy="476316"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>200025</colOff>
-      <row>19</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392235</colOff>
-      <row>20</row>
-      <rowOff>304908</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Grafik 42"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392235</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>304908</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Grafik 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="200025" y="9572625"/>
           <a:ext cx="11355385" cy="771633"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>20</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>857443</colOff>
-      <row>27</row>
-      <rowOff>95632</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Grafik 43"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857443</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95632</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Grafik 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="190500" y="10096500"/>
           <a:ext cx="1381318" cy="2734057"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>23</row>
-      <rowOff>342900</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>2058344</colOff>
-      <row>25</row>
-      <rowOff>219168</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Grafik 44"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2058344</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>219168</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Grafik 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="171450" y="11563350"/>
           <a:ext cx="6763694" cy="666843"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>876300</colOff>
-      <row>20</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1076353</colOff>
-      <row>25</row>
-      <rowOff>19321</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Grafik 45"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1076353</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19321</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Grafik 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="5753100" y="10086975"/>
           <a:ext cx="200053" cy="1943371"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>2057400</colOff>
-      <row>24</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>276335</colOff>
-      <row>25</row>
-      <rowOff>28619</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Grafik 47"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2057400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>276335</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Grafik 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="6934200" y="11725275"/>
           <a:ext cx="790685" cy="314369"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>209550</colOff>
-      <row>24</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1372141</colOff>
-      <row>27</row>
-      <rowOff>85847</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Grafik 48"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1372141</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>85847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Grafik 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="7658100" y="11944350"/>
           <a:ext cx="3877216" cy="876422"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>904875</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1409770</colOff>
-      <row>25</row>
-      <rowOff>200327</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Grafik 49"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>904875</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1409770</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>200327</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Grafik 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="11068050" y="10048875"/>
           <a:ext cx="504895" cy="2162477"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>25</row>
-      <rowOff>60846</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401749</colOff>
-      <row>27</row>
-      <rowOff>97346</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Grafik 51"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>60846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401749</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>97346</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Grafik 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="285750" y="12071871"/>
           <a:ext cx="11279174" cy="760400"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>2679539</colOff>
-      <row>25</row>
-      <rowOff>265132</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1422442</colOff>
-      <row>42</row>
-      <rowOff>94584</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Grafik 55"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2679539</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>265132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1422442</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>94584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Grafik 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="10127727" y="12267838"/>
           <a:ext cx="1458493" cy="4727593"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>284664</colOff>
-      <row>31</row>
-      <rowOff>54852</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>590925</colOff>
-      <row>32</row>
-      <rowOff>45363</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Grafik 56"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>284664</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>54852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>590925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>45363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Grafik 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="284664" y="13742518"/>
           <a:ext cx="10470280" cy="255764"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>841214</colOff>
-      <row>27</row>
-      <rowOff>43899</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>993635</colOff>
-      <row>42</row>
-      <rowOff>111408</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Grafik 57"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>841214</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>43899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>993635</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>111408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Grafik 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="5718255" y="12770022"/>
           <a:ext cx="152421" cy="4242233"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>192234</colOff>
-      <row>29</row>
-      <rowOff>7900</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>946233</colOff>
-      <row>30</row>
-      <rowOff>55561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Grafik 59"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>192234</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>7900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>946233</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>55561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Grafik 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="192234" y="13162046"/>
           <a:ext cx="10918018" cy="258657"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>180975</colOff>
-      <row>33</row>
-      <rowOff>14208</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>830184</colOff>
-      <row>34</row>
-      <rowOff>99972</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Grafik 61"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>14208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>830184</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>99972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Grafik 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="180975" y="14301708"/>
           <a:ext cx="10813228" cy="275661"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>193031</colOff>
-      <row>39</row>
-      <rowOff>312275</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>594555</colOff>
-      <row>42</row>
-      <rowOff>112568</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Grafik 62"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>193031</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>312275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>594555</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>112568</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Grafik 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="193031" y="16462576"/>
           <a:ext cx="10565543" cy="550839"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>26</row>
-      <rowOff>197975</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>285766</colOff>
-      <row>40</row>
-      <rowOff>198561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Grafik 63"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>197975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285766</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>198561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Grafik 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="171450" y="12523204"/>
           <a:ext cx="114316" cy="4196409"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>304800</colOff>
-      <row>39</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1028801</colOff>
-      <row>39</row>
-      <rowOff>314362</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Grafik 64"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1028801</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>314362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Grafik 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="1019175" y="16211550"/>
           <a:ext cx="724001" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>38174</colOff>
-      <row>62</row>
-      <rowOff>29419</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38174</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>29419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId113"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>2686050</colOff>
-      <row>51</row>
-      <rowOff>409575</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381322</colOff>
-      <row>62</row>
-      <rowOff>210289</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="219075" y="3495675"/>
+          <a:ext cx="533474" cy="6049219"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2686050</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381322</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>210289</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId110"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401762</colOff>
-      <row>47</row>
-      <rowOff>19336</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10134600" y="4429125"/>
+          <a:ext cx="1409897" cy="5296639"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401762</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>19336</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Grafik 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId104"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>228600</colOff>
-      <row>43</row>
-      <rowOff>19050</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>28647</colOff>
-      <row>51</row>
-      <rowOff>276822</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="0"/>
+          <a:ext cx="11374437" cy="2048161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28647</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>276822</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Grafik 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>49</row>
-      <rowOff>400050</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392232</colOff>
-      <row>52</row>
-      <rowOff>114452</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="19050"/>
+          <a:ext cx="514422" cy="4277322"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392232</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>114452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Grafik 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId117"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>542925</colOff>
-      <row>47</row>
-      <rowOff>495300</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1267607</colOff>
-      <row>48</row>
-      <rowOff>276269</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="219075" y="3486150"/>
+          <a:ext cx="11336332" cy="1086002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>495300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1267607</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>276269</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Grafik 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId114"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>3914775</colOff>
-      <row>45</row>
-      <rowOff>476250</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1562353</colOff>
-      <row>50</row>
-      <rowOff>219379</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="542925" y="2524125"/>
+          <a:ext cx="5601482" cy="314369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3914775</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1562353</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>219379</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Grafik 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId106"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>48</row>
-      <rowOff>466725</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>810379</colOff>
-      <row>49</row>
-      <rowOff>181008</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4629150" y="1533525"/>
+          <a:ext cx="1810003" cy="2181529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>466725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>810379</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>181008</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Grafik 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>942975</colOff>
-      <row>45</row>
-      <rowOff>161925</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381186</colOff>
-      <row>50</row>
-      <rowOff>209897</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285750" y="3028950"/>
+          <a:ext cx="5401429" cy="238158"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381186</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>209897</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Grafik 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId123"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>1019175</colOff>
-      <row>48</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1277124</colOff>
-      <row>48</row>
-      <rowOff>447718</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11106150" y="1219200"/>
+          <a:ext cx="438211" cy="2486372"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1277124</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>447718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Grafik 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>1047750</colOff>
-      <row>46</row>
-      <rowOff>209550</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1172330</colOff>
-      <row>47</row>
-      <rowOff>200091</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5895975" y="2705100"/>
+          <a:ext cx="5544324" cy="304843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1172330</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>200091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Grafik 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId115"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>200025</colOff>
-      <row>62</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392235</colOff>
-      <row>63</row>
-      <rowOff>304908</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5924550" y="1752600"/>
+          <a:ext cx="5410955" cy="476316"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392235</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>304908</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Grafik 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId107"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>63</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>857443</colOff>
-      <row>70</row>
-      <rowOff>95632</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="200025" y="9582150"/>
+          <a:ext cx="11355385" cy="771633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857443</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>95632</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Grafik 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>66</row>
-      <rowOff>342900</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>2058344</colOff>
-      <row>68</row>
-      <rowOff>219168</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="10096500"/>
+          <a:ext cx="1381318" cy="2734057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2058344</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>219168</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Grafik 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>876300</colOff>
-      <row>63</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1076353</colOff>
-      <row>68</row>
-      <rowOff>19321</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="171450" y="11563350"/>
+          <a:ext cx="6763694" cy="666843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1076353</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>19321</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Grafik 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>2057400</colOff>
-      <row>67</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>276335</colOff>
-      <row>68</row>
-      <rowOff>28619</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5753100" y="10086975"/>
+          <a:ext cx="200053" cy="1943371"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2057400</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>276335</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>28619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Grafik 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>209550</colOff>
-      <row>67</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1372141</colOff>
-      <row>70</row>
-      <rowOff>85847</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6934200" y="11725275"/>
+          <a:ext cx="790685" cy="314369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1372141</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>85847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Grafik 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>904875</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1409770</colOff>
-      <row>68</row>
-      <rowOff>200327</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7658100" y="11944350"/>
+          <a:ext cx="3877216" cy="876422"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>904875</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1409770</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>200327</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Grafik 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId102"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>68</row>
-      <rowOff>60846</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401749</colOff>
-      <row>70</row>
-      <rowOff>97346</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11068050" y="10048875"/>
+          <a:ext cx="504895" cy="2162477"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>60846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401749</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>97346</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Grafik 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId121"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>2679539</colOff>
-      <row>68</row>
-      <rowOff>265132</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>3217</colOff>
-      <row>85</row>
-      <rowOff>94584</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285750" y="12071871"/>
+          <a:ext cx="11279174" cy="760400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2679539</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>265132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3217</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>94584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Grafik 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>284664</colOff>
-      <row>74</row>
-      <rowOff>54852</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>590925</colOff>
-      <row>75</row>
-      <rowOff>45363</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10128089" y="12276157"/>
+          <a:ext cx="1457528" cy="4734827"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>284664</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>54852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>590925</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>45363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Grafik 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId105"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>841214</colOff>
-      <row>70</row>
-      <rowOff>43899</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>993635</colOff>
-      <row>85</row>
-      <rowOff>111408</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="284664" y="13751802"/>
+          <a:ext cx="10469436" cy="257211"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>841214</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>43899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>993635</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>111408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Grafik 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId125"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>192234</colOff>
-      <row>72</row>
-      <rowOff>7900</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>946233</colOff>
-      <row>73</row>
-      <rowOff>55561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5718014" y="12778824"/>
+          <a:ext cx="152421" cy="4248984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>192234</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>7900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>946233</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>55561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Grafik 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId119"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>180975</colOff>
-      <row>76</row>
-      <rowOff>14208</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>830184</colOff>
-      <row>77</row>
-      <rowOff>99972</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="192234" y="13171450"/>
+          <a:ext cx="10917174" cy="257211"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>14208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>830184</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>99972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Grafik 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId116"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>193031</colOff>
-      <row>82</row>
-      <rowOff>312275</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>594555</colOff>
-      <row>85</row>
-      <rowOff>112568</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="180975" y="14311233"/>
+          <a:ext cx="10812384" cy="276264"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>193031</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>312275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>594555</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>112568</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Grafik 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>69</row>
-      <rowOff>197975</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>285766</colOff>
-      <row>83</row>
-      <rowOff>198561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="193031" y="16476200"/>
+          <a:ext cx="10564699" cy="552768"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>197975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285766</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>198561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Grafik 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId103"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>304800</colOff>
-      <row>82</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1028801</colOff>
-      <row>82</row>
-      <rowOff>314362</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="171450" y="12532850"/>
+          <a:ext cx="114316" cy="4201111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1028801</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>314362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Grafik 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Tabelle1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Uezuemyemez</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>Ali</v>
-          </cell>
-          <cell r="C2"/>
-          <cell r="D2" t="str">
-            <v>202512XGWK</v>
-          </cell>
-          <cell r="E2">
-            <v>46064</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>Putschler, Walter</v>
-          </cell>
-          <cell r="G2">
-            <v>0.33333333333333331</v>
-          </cell>
-          <cell r="H2">
-            <v>0.66666666666666663</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Bumiller</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>Andrea</v>
-          </cell>
-          <cell r="C3"/>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Jochim</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>Anton</v>
-          </cell>
-          <cell r="C4"/>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Meisel</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Arlene</v>
-          </cell>
-          <cell r="C5"/>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Koelmel</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>Benjamin</v>
-          </cell>
-          <cell r="C6"/>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Piecha</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Ewa</v>
-          </cell>
-          <cell r="C7"/>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Di Battista</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Fabrizio</v>
-          </cell>
-          <cell r="C8"/>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Allgeier</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Horst</v>
-          </cell>
-          <cell r="C9"/>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Anselm</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Jens</v>
-          </cell>
-          <cell r="C10"/>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Eren</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Kenan</v>
-          </cell>
-          <cell r="C11"/>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>Fischer</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>Martin</v>
-          </cell>
-          <cell r="C12"/>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>Oezcan</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>Oezguer</v>
-          </cell>
-          <cell r="C13"/>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>Gommel</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Peter</v>
-          </cell>
-          <cell r="C14"/>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>Regenauer</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Sebastian</v>
-          </cell>
-          <cell r="C15"/>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>Radu</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Zeljko</v>
-          </cell>
-          <cell r="C16"/>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>test</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>supertest</v>
-          </cell>
-          <cell r="C17"/>
-        </row>
-        <row r="18">
-          <cell r="A18"/>
-          <cell r="B18"/>
-          <cell r="C18"/>
-        </row>
-        <row r="19">
-          <cell r="A19"/>
-          <cell r="B19"/>
-          <cell r="C19"/>
-        </row>
-        <row r="20">
-          <cell r="A20"/>
-          <cell r="B20"/>
-          <cell r="C20"/>
-        </row>
-        <row r="21">
-          <cell r="A21"/>
-          <cell r="B21"/>
-          <cell r="C21"/>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1019175" y="16211550"/>
+          <a:ext cx="724001" cy="266737"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teilnehmer" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bescheinigungen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BG-Liste" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lehrgangsdoku" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hilfslisten" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Teilnehmer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bescheinigungen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BG-Liste" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lehrgangsdoku" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Hilfslisten" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Lehrkraefte">Hilfslisten!$A$2:$A$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bescheinigungen'!$A$1:$AZ$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bescheinigungen'!$A$1:$AZ$388</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'BG-Liste'!$A$1:$E$86</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -5713,7 +5713,7 @@
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BE388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1"/>
@@ -12796,7 +12796,7 @@
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" fitToWidth="0" orientation="landscape"/>
+  <pageSetup paperSize="8" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"CorpoS"&amp;1 &amp;K000000Internal#</oddHeader>
     <oddFooter/>
@@ -12805,7 +12805,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="8" manualBreakCount="8">
+  <rowBreaks count="9" manualBreakCount="9">
     <brk id="38" min="0" max="16383" man="1"/>
     <brk id="77" min="0" max="16383" man="1"/>
     <brk id="116" min="0" max="16383" man="1"/>
@@ -12814,8 +12814,8 @@
     <brk id="233" min="0" max="16383" man="1"/>
     <brk id="272" min="0" max="16383" man="1"/>
     <brk id="311" min="0" max="16383" man="1"/>
+    <brk id="350" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13461,7 +13461,6 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="43" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -5709,7 +5709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12816,11 +12816,12 @@
     <brk id="311" min="0" max="16383" man="1"/>
     <brk id="350" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13461,6 +13462,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="43" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -12796,7 +12796,7 @@
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"CorpoS"&amp;1 &amp;K000000Internal#</oddHeader>
     <oddFooter/>
@@ -12825,7 +12825,7 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -13458,7 +13458,7 @@
     <mergeCell ref="C39:D39"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.07874015748031496" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="43" min="0" max="16383" man="1"/>
   </rowBreaks>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -12796,7 +12796,7 @@
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="10" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"CorpoS"&amp;1 &amp;K000000Internal#</oddHeader>
     <oddFooter/>

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -23,10 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="165" formatCode="HH:MM"/>
-    <numFmt numFmtId="166" formatCode="00000"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -219,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -360,11 +359,55 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -562,6 +605,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -649,4399 +694,3817 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>169404</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>166670</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Grafik 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>36</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>169404</colOff>
+      <row>37</row>
+      <rowOff>166670</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Grafik 3"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="6702830"/>
           <a:ext cx="4340587" cy="204855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Grafik 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>7</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Grafik 7"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId20"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="4363331" cy="1438977"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>159372</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>3197</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>51</xdr:col>
-      <xdr:colOff>162256</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>167384</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Grafik 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>27</col>
+      <colOff>159372</colOff>
+      <row>0</row>
+      <rowOff>3197</rowOff>
+    </from>
+    <to>
+      <col>51</col>
+      <colOff>162256</colOff>
+      <row>7</row>
+      <rowOff>167384</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Grafik 9"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId21"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5040135" y="3197"/>
           <a:ext cx="4365846" cy="1439514"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>22374</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>139679</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>51</xdr:col>
-      <xdr:colOff>158020</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>160826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Grafik 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>22374</colOff>
+      <row>36</row>
+      <rowOff>139679</rowOff>
+    </from>
+    <to>
+      <col>51</col>
+      <colOff>158020</colOff>
+      <row>37</row>
+      <rowOff>160826</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Grafik 13"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5075738" y="6698505"/>
           <a:ext cx="4326007" cy="203336"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Grafik 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>46</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Grafik 5"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId23"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="6877050"/>
           <a:ext cx="4346153" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Grafik 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>46</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Grafik 44"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId24"/>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="6877050"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>85</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Grafik 45"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId25"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="13754100"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>85</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Grafik 46"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId26"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="13754100"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>124</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Grafik 47"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId27"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="20631150"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>27</col>
+      <colOff>171450</colOff>
+      <row>117</row>
+      <rowOff>9525</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>125</row>
+      <rowOff>1407</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Grafik 48"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId28"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5276850" y="20640675"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>156</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>163</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Grafik 50"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId29"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="27508200"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>156</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>163</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Grafik 51"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId30"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="27508200"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>195</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>202</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Grafik 52"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId31"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="34385250"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>195</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>202</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Grafik 53"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId32"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="34385250"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>234</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>241</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Grafik 54"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId33"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="41262300"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>234</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>241</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Grafik 55"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId34"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="41262300"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>273</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>280</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Grafik 56"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId35"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="48139350"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>273</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>280</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Grafik 57"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId36"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="48139350"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>319</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Grafik 58"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId37"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="55016400"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>319</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Grafik 59"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId38"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="55016400"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>351</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>24</col>
+      <colOff>2753</colOff>
+      <row>358</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Grafik 60"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId39"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="61893450"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>351</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>52</col>
+      <colOff>2753</colOff>
+      <row>358</row>
+      <rowOff>167142</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Grafik 61"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId40"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5286375" y="61893450"/>
+          <a:ext cx="4574753" cy="1433967"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>75</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Grafik 6"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="6659104"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Grafik 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>75</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Grafik 10"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="13536154"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Grafik 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>114</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Grafik 12"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="13536154"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Grafik 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>114</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Grafik 15"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="13536154"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>153</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Grafik 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>153</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Grafik 17"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="13536154"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>153</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Grafik 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>153</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Grafik 19"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="13536154"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>192</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Grafik 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>192</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Grafik 21"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>192</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Grafik 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>192</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Grafik 23"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>231</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Grafik 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>231</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Grafik 25"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>231</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Grafik 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>231</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Grafik 27"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>270</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Grafik 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>270</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Grafik 29"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>270</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Grafik 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>270</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Grafik 31"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>309</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Grafik 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>309</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Grafik 33"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>309</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Grafik 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>309</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Grafik 35"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>348</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Grafik 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>348</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Grafik 37"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>348</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Grafik 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>348</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Grafik 39"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>387</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Grafik 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19178</colOff>
+      <row>387</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Grafik 41"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>19178</xdr:colOff>
-      <xdr:row>387</xdr:row>
-      <xdr:rowOff>144004</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4312651" cy="203641"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Grafik 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>19178</colOff>
+      <row>387</row>
+      <rowOff>144004</rowOff>
+    </from>
+    <ext cx="4312651" cy="203641"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Grafik 43"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="19178" y="27290254"/>
           <a:ext cx="4312651" cy="203641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Grafik 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>219075</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>38174</colOff>
+      <row>19</row>
+      <rowOff>29419</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Grafik 8"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="6877050"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Grafik 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="13754100"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Grafik 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="13754100"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Grafik 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="20631150"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>1407</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Grafik 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5276850" y="20640675"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>163</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Grafik 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="27508200"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>163</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Grafik 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="27508200"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Grafik 52">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="34385250"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Grafik 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="34385250"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>234</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>241</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Grafik 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="41262300"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>234</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>241</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Grafik 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="41262300"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>273</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>280</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Grafik 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="48139350"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>273</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>280</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Grafik 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="48139350"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>312</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>319</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Grafik 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="55016400"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>312</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>319</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Grafik 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="55016400"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>351</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>358</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Grafik 60">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="61893450"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>351</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>2753</xdr:colOff>
-      <xdr:row>358</xdr:row>
-      <xdr:rowOff>167142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Grafik 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5286375" y="61893450"/>
-          <a:ext cx="4574753" cy="1433967"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>38174</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>29419</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Grafik 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="219075" y="3495675"/>
           <a:ext cx="533474" cy="6049219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2686050</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>409575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1381322</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>210289</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Grafik 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>3</col>
+      <colOff>2686050</colOff>
+      <row>8</row>
+      <rowOff>409575</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1381322</colOff>
+      <row>19</row>
+      <rowOff>210289</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Grafik 9"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="10134600" y="4429125"/>
           <a:ext cx="1409897" cy="5296639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1401762</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>19336</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Grafik 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>190500</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1401762</colOff>
+      <row>4</row>
+      <rowOff>19336</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Grafik 32"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="190500" y="0"/>
           <a:ext cx="11374437" cy="2048161"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28647</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>276822</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Grafik 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>228600</colOff>
+      <row>0</row>
+      <rowOff>19050</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>28647</colOff>
+      <row>8</row>
+      <rowOff>276822</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Grafik 33"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="228600" y="19050"/>
           <a:ext cx="514422" cy="4277322"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>400050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1392232</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>114452</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Grafik 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>219075</colOff>
+      <row>6</row>
+      <rowOff>400050</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1392232</colOff>
+      <row>9</row>
+      <rowOff>114452</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Grafik 34"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="219075" y="3486150"/>
           <a:ext cx="11336332" cy="1086002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>495300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1267607</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>276269</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Grafik 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>542925</colOff>
+      <row>4</row>
+      <rowOff>495300</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1267607</colOff>
+      <row>5</row>
+      <rowOff>276269</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Grafik 36"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="542925" y="2524125"/>
           <a:ext cx="5601482" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3914775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1562353</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>219379</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Grafik 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>3914775</colOff>
+      <row>2</row>
+      <rowOff>476250</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1562353</colOff>
+      <row>7</row>
+      <rowOff>219379</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Grafik 37"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="4629150" y="1533525"/>
           <a:ext cx="1810003" cy="2181529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>466725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>810379</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>181008</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Grafik 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>285750</colOff>
+      <row>5</row>
+      <rowOff>466725</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>810379</colOff>
+      <row>6</row>
+      <rowOff>181008</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Grafik 38"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="285750" y="3028950"/>
           <a:ext cx="5401429" cy="238158"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1381186</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>209897</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Grafik 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>942975</colOff>
+      <row>2</row>
+      <rowOff>161925</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1381186</colOff>
+      <row>7</row>
+      <rowOff>209897</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Grafik 39"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="11106150" y="1219200"/>
           <a:ext cx="438211" cy="2486372"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1019175</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1277124</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>447718</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Grafik 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>1019175</colOff>
+      <row>5</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1277124</colOff>
+      <row>5</row>
+      <rowOff>447718</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Grafik 40"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5895975" y="2705100"/>
           <a:ext cx="5544324" cy="304843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1172330</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>200091</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Grafik 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>1047750</colOff>
+      <row>3</row>
+      <rowOff>209550</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1172330</colOff>
+      <row>4</row>
+      <rowOff>200091</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Grafik 41"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5924550" y="1752600"/>
           <a:ext cx="5410955" cy="476316"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1392235</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>304908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Grafik 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>200025</colOff>
+      <row>19</row>
+      <rowOff>66675</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1392235</colOff>
+      <row>20</row>
+      <rowOff>304908</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Grafik 42"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="200025" y="9572625"/>
           <a:ext cx="11355385" cy="771633"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>857443</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>95632</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Grafik 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>190500</colOff>
+      <row>20</row>
+      <rowOff>47625</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>857443</colOff>
+      <row>27</row>
+      <rowOff>95632</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Grafik 43"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="190500" y="10096500"/>
           <a:ext cx="1381318" cy="2734057"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2058344</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>219168</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Grafik 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>171450</colOff>
+      <row>23</row>
+      <rowOff>342900</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>2058344</colOff>
+      <row>25</row>
+      <rowOff>219168</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Grafik 44"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="171450" y="11563350"/>
           <a:ext cx="6763694" cy="666843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1076353</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>19321</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Grafik 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>876300</colOff>
+      <row>20</row>
+      <rowOff>38100</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1076353</colOff>
+      <row>25</row>
+      <rowOff>19321</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Grafik 45"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5753100" y="10086975"/>
           <a:ext cx="200053" cy="1943371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2057400</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>276335</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>28619</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Grafik 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>2057400</colOff>
+      <row>24</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <to>
+      <col>3</col>
+      <colOff>276335</colOff>
+      <row>25</row>
+      <rowOff>28619</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Grafik 47"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="6934200" y="11725275"/>
           <a:ext cx="790685" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>314325</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1372141</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>85847</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Grafik 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>3</col>
+      <colOff>209550</colOff>
+      <row>24</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1372141</colOff>
+      <row>27</row>
+      <rowOff>85847</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Grafik 48"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="7658100" y="11944350"/>
           <a:ext cx="3877216" cy="876422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>904875</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1409770</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>200327</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Grafik 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>904875</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1409770</colOff>
+      <row>25</row>
+      <rowOff>200327</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Grafik 49"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="11068050" y="10048875"/>
           <a:ext cx="504895" cy="2162477"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>60846</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1401749</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>97346</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Grafik 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>285750</colOff>
+      <row>25</row>
+      <rowOff>60846</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1401749</colOff>
+      <row>27</row>
+      <rowOff>97346</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Grafik 51"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="285750" y="12071871"/>
           <a:ext cx="11279174" cy="760400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2679539</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>265132</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1422442</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>94584</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Grafik 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>3</col>
+      <colOff>2679539</colOff>
+      <row>25</row>
+      <rowOff>265132</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1422442</colOff>
+      <row>42</row>
+      <rowOff>94584</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Grafik 55"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="10127727" y="12267838"/>
           <a:ext cx="1458493" cy="4727593"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>284664</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>54852</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>590925</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>45363</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Grafik 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>284664</colOff>
+      <row>31</row>
+      <rowOff>54852</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>590925</colOff>
+      <row>32</row>
+      <rowOff>45363</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Grafik 56"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="284664" y="13742518"/>
           <a:ext cx="10470280" cy="255764"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>841214</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>43899</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>993635</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>111408</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Grafik 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>841214</colOff>
+      <row>27</row>
+      <rowOff>43899</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>993635</colOff>
+      <row>42</row>
+      <rowOff>111408</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Grafik 57"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5718255" y="12770022"/>
           <a:ext cx="152421" cy="4242233"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>192234</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>7900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>946233</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>55561</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Grafik 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>192234</colOff>
+      <row>29</row>
+      <rowOff>7900</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>946233</colOff>
+      <row>30</row>
+      <rowOff>55561</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Grafik 59"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="192234" y="13162046"/>
           <a:ext cx="10918018" cy="258657"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>14208</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>830184</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>99972</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Grafik 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>180975</colOff>
+      <row>33</row>
+      <rowOff>14208</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>830184</colOff>
+      <row>34</row>
+      <rowOff>99972</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Grafik 61"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="180975" y="14301708"/>
           <a:ext cx="10813228" cy="275661"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>193031</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>312275</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>594555</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>112568</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Grafik 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>193031</colOff>
+      <row>39</row>
+      <rowOff>312275</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>594555</colOff>
+      <row>42</row>
+      <rowOff>112568</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Grafik 62"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="193031" y="16462576"/>
           <a:ext cx="10565543" cy="550839"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>197975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>285766</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>198561</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Grafik 63">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>171450</colOff>
+      <row>26</row>
+      <rowOff>197975</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>285766</colOff>
+      <row>40</row>
+      <rowOff>198561</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Grafik 63"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="171450" y="12523204"/>
           <a:ext cx="114316" cy="4196409"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1028801</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>314362</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Grafik 64">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>304800</colOff>
+      <row>39</row>
+      <rowOff>47625</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>1028801</colOff>
+      <row>39</row>
+      <rowOff>314362</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Grafik 64"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="1019175" y="16211550"/>
           <a:ext cx="724001" cy="266737"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>38174</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>29419</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Grafik 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>219075</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>38174</colOff>
+      <row>62</row>
+      <rowOff>29419</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Grafik 1"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId113"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId28"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="219075" y="3495675"/>
           <a:ext cx="533474" cy="6049219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2686050</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>409575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1381322</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>210289</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Grafik 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>3</col>
+      <colOff>2686050</colOff>
+      <row>51</row>
+      <rowOff>409575</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1381322</colOff>
+      <row>62</row>
+      <rowOff>210289</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Grafik 2"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId110"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId29"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="10134600" y="4429125"/>
           <a:ext cx="1409897" cy="5296639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1401762</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>19336</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Grafik 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>190500</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1401762</colOff>
+      <row>47</row>
+      <rowOff>19336</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Grafik 3"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId104"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId30"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="190500" y="0"/>
           <a:ext cx="11374437" cy="2048161"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28647</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>276822</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Grafik 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>228600</colOff>
+      <row>43</row>
+      <rowOff>19050</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>28647</colOff>
+      <row>51</row>
+      <rowOff>276822</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Grafik 4"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId31"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="228600" y="19050"/>
           <a:ext cx="514422" cy="4277322"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>400050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1392232</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>114452</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Grafik 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>219075</colOff>
+      <row>49</row>
+      <rowOff>400050</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1392232</colOff>
+      <row>52</row>
+      <rowOff>114452</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Grafik 5"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId117"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId32"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="219075" y="3486150"/>
           <a:ext cx="11336332" cy="1086002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>495300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1267607</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>276269</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Grafik 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>542925</colOff>
+      <row>47</row>
+      <rowOff>495300</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1267607</colOff>
+      <row>48</row>
+      <rowOff>276269</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Grafik 6"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId114"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId33"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="542925" y="2524125"/>
           <a:ext cx="5601482" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3914775</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1562353</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>219379</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Grafik 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>3914775</colOff>
+      <row>45</row>
+      <rowOff>476250</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1562353</colOff>
+      <row>50</row>
+      <rowOff>219379</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Grafik 7"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId106"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="4629150" y="1533525"/>
           <a:ext cx="1810003" cy="2181529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>466725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>810379</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>181008</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Grafik 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>285750</colOff>
+      <row>48</row>
+      <rowOff>466725</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>810379</colOff>
+      <row>49</row>
+      <rowOff>181008</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Grafik 8"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId35"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="285750" y="3028950"/>
           <a:ext cx="5401429" cy="238158"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1381186</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>209897</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Grafik 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>942975</colOff>
+      <row>45</row>
+      <rowOff>161925</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1381186</colOff>
+      <row>50</row>
+      <rowOff>209897</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Grafik 9"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId123"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId36"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="11106150" y="1219200"/>
           <a:ext cx="438211" cy="2486372"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1019175</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1277124</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>447718</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Grafik 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>1019175</colOff>
+      <row>48</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1277124</colOff>
+      <row>48</row>
+      <rowOff>447718</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Grafik 10"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId37"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5895975" y="2705100"/>
           <a:ext cx="5544324" cy="304843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1172330</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>200091</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Grafik 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>1047750</colOff>
+      <row>46</row>
+      <rowOff>209550</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1172330</colOff>
+      <row>47</row>
+      <rowOff>200091</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Grafik 11"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId115"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId38"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5924550" y="1752600"/>
           <a:ext cx="5410955" cy="476316"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1392235</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>304908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Grafik 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>200025</colOff>
+      <row>62</row>
+      <rowOff>66675</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1392235</colOff>
+      <row>63</row>
+      <rowOff>304908</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Grafik 12"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId107"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId39"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="200025" y="9582150"/>
           <a:ext cx="11355385" cy="771633"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>857443</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>95632</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Grafik 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>190500</colOff>
+      <row>63</row>
+      <rowOff>47625</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>857443</colOff>
+      <row>70</row>
+      <rowOff>95632</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Grafik 13"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId40"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="190500" y="10096500"/>
           <a:ext cx="1381318" cy="2734057"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2058344</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>219168</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Grafik 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>171450</colOff>
+      <row>66</row>
+      <rowOff>342900</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>2058344</colOff>
+      <row>68</row>
+      <rowOff>219168</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Grafik 14"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId41"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="171450" y="11563350"/>
           <a:ext cx="6763694" cy="666843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1076353</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>19321</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Grafik 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>876300</colOff>
+      <row>63</row>
+      <rowOff>38100</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1076353</colOff>
+      <row>68</row>
+      <rowOff>19321</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Grafik 15"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId42"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5753100" y="10086975"/>
           <a:ext cx="200053" cy="1943371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2057400</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>276335</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>28619</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Grafik 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>2057400</colOff>
+      <row>67</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <to>
+      <col>3</col>
+      <colOff>276335</colOff>
+      <row>68</row>
+      <rowOff>28619</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Grafik 16"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId43"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="6934200" y="11725275"/>
           <a:ext cx="790685" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>314325</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1372141</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>85847</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Grafik 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>3</col>
+      <colOff>209550</colOff>
+      <row>67</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1372141</colOff>
+      <row>70</row>
+      <rowOff>85847</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Grafik 17"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="7658100" y="11944350"/>
           <a:ext cx="3877216" cy="876422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>904875</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1409770</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>200327</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Grafik 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>904875</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1409770</colOff>
+      <row>68</row>
+      <rowOff>200327</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Grafik 18"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId102"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId45"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="11068050" y="10048875"/>
           <a:ext cx="504895" cy="2162477"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>60846</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1401749</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>97346</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Grafik 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>285750</colOff>
+      <row>68</row>
+      <rowOff>60846</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>1401749</colOff>
+      <row>70</row>
+      <rowOff>97346</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Grafik 19"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId121"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId46"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="285750" y="12071871"/>
           <a:ext cx="11279174" cy="760400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2679539</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>265132</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3217</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>94584</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Grafik 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>3</col>
+      <colOff>2679539</colOff>
+      <row>68</row>
+      <rowOff>265132</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>3217</colOff>
+      <row>85</row>
+      <rowOff>94584</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Grafik 20"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId47"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="10128089" y="12276157"/>
           <a:ext cx="1457528" cy="4734827"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>284664</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>54852</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>590925</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>45363</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Grafik 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>284664</colOff>
+      <row>74</row>
+      <rowOff>54852</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>590925</colOff>
+      <row>75</row>
+      <rowOff>45363</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Grafik 21"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId105"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId48"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="284664" y="13751802"/>
           <a:ext cx="10469436" cy="257211"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>841214</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>43899</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>993635</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>111408</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Grafik 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>841214</colOff>
+      <row>70</row>
+      <rowOff>43899</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>993635</colOff>
+      <row>85</row>
+      <rowOff>111408</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Grafik 22"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId125"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId49"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="5718014" y="12778824"/>
           <a:ext cx="152421" cy="4248984"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>192234</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>7900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>946233</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>55561</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Grafik 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>192234</colOff>
+      <row>72</row>
+      <rowOff>7900</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>946233</colOff>
+      <row>73</row>
+      <rowOff>55561</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Grafik 23"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId119"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId50"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="192234" y="13171450"/>
           <a:ext cx="10917174" cy="257211"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>14208</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>830184</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>99972</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Grafik 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>180975</colOff>
+      <row>76</row>
+      <rowOff>14208</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>830184</colOff>
+      <row>77</row>
+      <rowOff>99972</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Grafik 24"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId116"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId51"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="180975" y="14311233"/>
           <a:ext cx="10812384" cy="276264"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>193031</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>312275</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>594555</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>112568</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Grafik 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>193031</colOff>
+      <row>82</row>
+      <rowOff>312275</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>594555</colOff>
+      <row>85</row>
+      <rowOff>112568</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Grafik 25"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId52"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="193031" y="16476200"/>
           <a:ext cx="10564699" cy="552768"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>197975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>285766</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>198561</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Grafik 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>171450</colOff>
+      <row>69</row>
+      <rowOff>197975</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>285766</colOff>
+      <row>83</row>
+      <rowOff>198561</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Grafik 26"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId103"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId53"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="171450" y="12532850"/>
           <a:ext cx="114316" cy="4201111"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1028801</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>314362</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Grafik 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>304800</colOff>
+      <row>82</row>
+      <rowOff>47625</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>1028801</colOff>
+      <row>82</row>
+      <rowOff>314362</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Grafik 27"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId54"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="1019175" y="16211550"/>
           <a:ext cx="724001" cy="266737"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5419,6 +4882,8 @@
           <t>Mercedes-Benz AG, PKW-Werk Rastatt</t>
         </is>
       </c>
+      <c r="D6" s="73" t="n"/>
+      <c r="E6" s="74" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="22" t="inlineStr">
@@ -5709,22 +5174,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BE388"/>
+  <dimension ref="A1:BE390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="25" width="2.7109375" style="5" customWidth="1"/>
-    <col min="26" max="27" width="2.42578125" style="5" customWidth="1"/>
-    <col min="28" max="28" width="2.5703125" style="5" customWidth="1"/>
-    <col min="29" max="52" width="2.7109375" style="5" customWidth="1"/>
-    <col min="53" max="56" width="9.140625" style="1"/>
-    <col min="57" max="57" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.140625" style="1"/>
+    <col width="2.7109375" customWidth="1" style="5" min="1" max="25"/>
+    <col width="2.42578125" customWidth="1" style="5" min="26" max="27"/>
+    <col width="2.5703125" customWidth="1" style="5" min="28" max="28"/>
+    <col width="2.7109375" customWidth="1" style="5" min="29" max="52"/>
+    <col width="9.140625" customWidth="1" style="1" min="53" max="56"/>
+    <col width="10.140625" bestFit="1" customWidth="1" style="1" min="57" max="57"/>
+    <col width="9.140625" customWidth="1" style="1" min="58" max="16384"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -6267,11 +5732,7 @@
       <c r="K27" s="11" t="n"/>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>
-      <c r="O27" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O27" s="16" t="n"/>
       <c r="P27" s="38" t="n"/>
       <c r="Q27" s="38" t="n"/>
       <c r="R27" s="38" t="n"/>
@@ -6293,11 +5754,7 @@
       <c r="AM27" s="11" t="n"/>
       <c r="AN27" s="11" t="n"/>
       <c r="AO27" s="11" t="n"/>
-      <c r="AQ27" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ27" s="16" t="n"/>
       <c r="AR27" s="38" t="n"/>
       <c r="AS27" s="38" t="n"/>
       <c r="AT27" s="38" t="n"/>
@@ -6347,7 +5804,7 @@
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
@@ -6357,7 +5814,7 @@
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM32" s="15" t="inlineStr">
@@ -6413,7 +5870,18 @@
       </c>
     </row>
     <row r="38"/>
-    <row r="39"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
@@ -6948,11 +6416,7 @@
       <c r="K66" s="11" t="n"/>
       <c r="L66" s="11" t="n"/>
       <c r="M66" s="11" t="n"/>
-      <c r="O66" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O66" s="16" t="n"/>
       <c r="P66" s="38" t="n"/>
       <c r="Q66" s="38" t="n"/>
       <c r="R66" s="38" t="n"/>
@@ -6973,11 +6437,7 @@
       <c r="AM66" s="11" t="n"/>
       <c r="AN66" s="11" t="n"/>
       <c r="AO66" s="11" t="n"/>
-      <c r="AQ66" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ66" s="16" t="n"/>
       <c r="AR66" s="38" t="n"/>
       <c r="AS66" s="38" t="n"/>
       <c r="AT66" s="38" t="n"/>
@@ -7027,7 +6487,7 @@
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
@@ -7037,7 +6497,7 @@
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM71" s="15" t="inlineStr">
@@ -7093,7 +6553,18 @@
       </c>
     </row>
     <row r="77"/>
-    <row r="78"/>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="79"/>
     <row r="80"/>
     <row r="81"/>
@@ -7628,11 +7099,7 @@
       <c r="K105" s="11" t="n"/>
       <c r="L105" s="11" t="n"/>
       <c r="M105" s="11" t="n"/>
-      <c r="O105" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O105" s="16" t="n"/>
       <c r="P105" s="38" t="n"/>
       <c r="Q105" s="38" t="n"/>
       <c r="R105" s="38" t="n"/>
@@ -7653,11 +7120,7 @@
       <c r="AM105" s="11" t="n"/>
       <c r="AN105" s="11" t="n"/>
       <c r="AO105" s="11" t="n"/>
-      <c r="AQ105" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ105" s="16" t="n"/>
       <c r="AR105" s="38" t="n"/>
       <c r="AS105" s="38" t="n"/>
       <c r="AT105" s="38" t="n"/>
@@ -7707,7 +7170,7 @@
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K110" s="15" t="inlineStr">
@@ -7717,7 +7180,7 @@
       </c>
       <c r="AC110" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM110" s="15" t="inlineStr">
@@ -7773,7 +7236,18 @@
       </c>
     </row>
     <row r="116"/>
-    <row r="117"/>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="118"/>
     <row r="119"/>
     <row r="120"/>
@@ -8308,11 +7782,7 @@
       <c r="K144" s="11" t="n"/>
       <c r="L144" s="11" t="n"/>
       <c r="M144" s="11" t="n"/>
-      <c r="O144" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O144" s="16" t="n"/>
       <c r="P144" s="38" t="n"/>
       <c r="Q144" s="38" t="n"/>
       <c r="R144" s="38" t="n"/>
@@ -8333,11 +7803,7 @@
       <c r="AM144" s="11" t="n"/>
       <c r="AN144" s="11" t="n"/>
       <c r="AO144" s="11" t="n"/>
-      <c r="AQ144" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ144" s="16" t="n"/>
       <c r="AR144" s="38" t="n"/>
       <c r="AS144" s="38" t="n"/>
       <c r="AT144" s="38" t="n"/>
@@ -8387,7 +7853,7 @@
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K149" s="15" t="inlineStr">
@@ -8397,7 +7863,7 @@
       </c>
       <c r="AC149" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM149" s="15" t="inlineStr">
@@ -8453,7 +7919,18 @@
       </c>
     </row>
     <row r="155"/>
-    <row r="156"/>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="157"/>
     <row r="158"/>
     <row r="159"/>
@@ -8988,11 +8465,7 @@
       <c r="K183" s="11" t="n"/>
       <c r="L183" s="11" t="n"/>
       <c r="M183" s="11" t="n"/>
-      <c r="O183" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O183" s="16" t="n"/>
       <c r="P183" s="38" t="n"/>
       <c r="Q183" s="38" t="n"/>
       <c r="R183" s="38" t="n"/>
@@ -9013,11 +8486,7 @@
       <c r="AM183" s="11" t="n"/>
       <c r="AN183" s="11" t="n"/>
       <c r="AO183" s="11" t="n"/>
-      <c r="AQ183" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ183" s="16" t="n"/>
       <c r="AR183" s="38" t="n"/>
       <c r="AS183" s="38" t="n"/>
       <c r="AT183" s="38" t="n"/>
@@ -9067,7 +8536,7 @@
     <row r="188" ht="14.25" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K188" s="15" t="inlineStr">
@@ -9077,7 +8546,7 @@
       </c>
       <c r="AC188" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM188" s="15" t="inlineStr">
@@ -9133,7 +8602,18 @@
       </c>
     </row>
     <row r="194"/>
-    <row r="195"/>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="196"/>
     <row r="197"/>
     <row r="198"/>
@@ -9668,11 +9148,7 @@
       <c r="K222" s="11" t="n"/>
       <c r="L222" s="11" t="n"/>
       <c r="M222" s="11" t="n"/>
-      <c r="O222" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O222" s="16" t="n"/>
       <c r="P222" s="38" t="n"/>
       <c r="Q222" s="38" t="n"/>
       <c r="R222" s="38" t="n"/>
@@ -9693,11 +9169,7 @@
       <c r="AM222" s="11" t="n"/>
       <c r="AN222" s="11" t="n"/>
       <c r="AO222" s="11" t="n"/>
-      <c r="AQ222" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ222" s="16" t="n"/>
       <c r="AR222" s="38" t="n"/>
       <c r="AS222" s="38" t="n"/>
       <c r="AT222" s="38" t="n"/>
@@ -9747,7 +9219,7 @@
     <row r="227" ht="14.25" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K227" s="15" t="inlineStr">
@@ -9757,7 +9229,7 @@
       </c>
       <c r="AC227" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM227" s="15" t="inlineStr">
@@ -9813,7 +9285,18 @@
       </c>
     </row>
     <row r="233"/>
-    <row r="234"/>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="235"/>
     <row r="236"/>
     <row r="237"/>
@@ -10348,11 +9831,7 @@
       <c r="K261" s="11" t="n"/>
       <c r="L261" s="11" t="n"/>
       <c r="M261" s="11" t="n"/>
-      <c r="O261" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O261" s="16" t="n"/>
       <c r="P261" s="38" t="n"/>
       <c r="Q261" s="38" t="n"/>
       <c r="R261" s="38" t="n"/>
@@ -10373,11 +9852,7 @@
       <c r="AM261" s="11" t="n"/>
       <c r="AN261" s="11" t="n"/>
       <c r="AO261" s="11" t="n"/>
-      <c r="AQ261" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ261" s="16" t="n"/>
       <c r="AR261" s="38" t="n"/>
       <c r="AS261" s="38" t="n"/>
       <c r="AT261" s="38" t="n"/>
@@ -10427,7 +9902,7 @@
     <row r="266" ht="14.25" customHeight="1">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K266" s="15" t="inlineStr">
@@ -10437,7 +9912,7 @@
       </c>
       <c r="AC266" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM266" s="15" t="inlineStr">
@@ -10493,7 +9968,18 @@
       </c>
     </row>
     <row r="272"/>
-    <row r="273"/>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="274"/>
     <row r="275"/>
     <row r="276"/>
@@ -11028,11 +10514,7 @@
       <c r="K300" s="11" t="n"/>
       <c r="L300" s="11" t="n"/>
       <c r="M300" s="11" t="n"/>
-      <c r="O300" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O300" s="16" t="n"/>
       <c r="P300" s="38" t="n"/>
       <c r="Q300" s="38" t="n"/>
       <c r="R300" s="38" t="n"/>
@@ -11053,11 +10535,7 @@
       <c r="AM300" s="11" t="n"/>
       <c r="AN300" s="11" t="n"/>
       <c r="AO300" s="11" t="n"/>
-      <c r="AQ300" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ300" s="16" t="n"/>
       <c r="AR300" s="38" t="n"/>
       <c r="AS300" s="38" t="n"/>
       <c r="AT300" s="38" t="n"/>
@@ -11107,7 +10585,7 @@
     <row r="305" ht="14.25" customHeight="1">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K305" s="15" t="inlineStr">
@@ -11117,7 +10595,7 @@
       </c>
       <c r="AC305" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM305" s="15" t="inlineStr">
@@ -11173,7 +10651,18 @@
       </c>
     </row>
     <row r="311"/>
-    <row r="312"/>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="313"/>
     <row r="314"/>
     <row r="315"/>
@@ -11708,11 +11197,7 @@
       <c r="K339" s="11" t="n"/>
       <c r="L339" s="11" t="n"/>
       <c r="M339" s="11" t="n"/>
-      <c r="O339" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O339" s="16" t="n"/>
       <c r="P339" s="38" t="n"/>
       <c r="Q339" s="38" t="n"/>
       <c r="R339" s="38" t="n"/>
@@ -11733,11 +11218,7 @@
       <c r="AM339" s="11" t="n"/>
       <c r="AN339" s="11" t="n"/>
       <c r="AO339" s="11" t="n"/>
-      <c r="AQ339" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ339" s="16" t="n"/>
       <c r="AR339" s="38" t="n"/>
       <c r="AS339" s="38" t="n"/>
       <c r="AT339" s="38" t="n"/>
@@ -11787,7 +11268,7 @@
     <row r="344" ht="14.25" customHeight="1">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K344" s="15" t="inlineStr">
@@ -11797,7 +11278,7 @@
       </c>
       <c r="AC344" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM344" s="15" t="inlineStr">
@@ -11853,7 +11334,18 @@
       </c>
     </row>
     <row r="350"/>
-    <row r="351"/>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="352"/>
     <row r="353"/>
     <row r="354"/>
@@ -12388,11 +11880,7 @@
       <c r="K378" s="11" t="n"/>
       <c r="L378" s="11" t="n"/>
       <c r="M378" s="11" t="n"/>
-      <c r="O378" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="O378" s="16" t="n"/>
       <c r="P378" s="38" t="n"/>
       <c r="Q378" s="38" t="n"/>
       <c r="R378" s="38" t="n"/>
@@ -12413,11 +11901,7 @@
       <c r="AM378" s="11" t="n"/>
       <c r="AN378" s="11" t="n"/>
       <c r="AO378" s="11" t="n"/>
-      <c r="AQ378" s="16" t="inlineStr">
-        <is>
-          <t>Ausbildungsverantwortlicher</t>
-        </is>
-      </c>
+      <c r="AQ378" s="16" t="n"/>
       <c r="AR378" s="38" t="n"/>
       <c r="AS378" s="38" t="n"/>
       <c r="AT378" s="38" t="n"/>
@@ -12467,7 +11951,7 @@
     <row r="383" ht="14.25" customHeight="1">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="K383" s="15" t="inlineStr">
@@ -12477,7 +11961,7 @@
       </c>
       <c r="AC383" s="3" t="inlineStr">
         <is>
-          <t>gemäß § 26 DGUV Vorschri_x001F_ft:</t>
+          <t>gemäß § 26 DGUV Vorschrift 1:</t>
         </is>
       </c>
       <c r="AM383" s="15" t="inlineStr">
@@ -12529,6 +12013,18 @@
       <c r="AC388" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   (FeV).</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
         </is>
       </c>
     </row>
@@ -12795,8 +12291,8 @@
     <mergeCell ref="I140:M140"/>
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
-  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="10" orientation="landscape"/>
+  <pageMargins left="0.3149606299212598" right="0.3149606299212598" top="0.3937007874015748" bottom="0.3937007874015748" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="10" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"CorpoS"&amp;1 &amp;K000000Internal#</oddHeader>
     <oddFooter/>
@@ -12816,18 +12312,18 @@
     <brk id="311" min="0" max="16383" man="1"/>
     <brk id="350" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A2:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" customWidth="1" min="1" max="1"/>
@@ -13094,8 +12590,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="29.25" customHeight="1">
       <c r="C36" s="54" t="inlineStr">
         <is>
@@ -13394,8 +12888,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79" ht="29.25" customHeight="1">
       <c r="C79" s="54" t="inlineStr">
         <is>
@@ -13443,9 +12935,9 @@
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C72:D72"/>
     <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C82:D82"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C76:D76"/>
@@ -13462,7 +12954,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="43" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/EH_Kurs_2026.xlsx
+++ b/EH_Kurs_2026.xlsx
@@ -23,9 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="165" formatCode="HH:MM"/>
+    <numFmt numFmtId="166" formatCode="00000"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -218,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -359,55 +360,11 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -605,8 +562,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -694,3817 +649,4399 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>36</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <to>
-      <col>23</col>
-      <colOff>169404</colOff>
-      <row>37</row>
-      <rowOff>166670</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Grafik 3"/>
-        <cNvPicPr>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>169404</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>166670</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Grafik 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId19"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="19178" y="6702830"/>
           <a:ext cx="4340587" cy="204855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>7</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Grafik 7"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Grafik 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId20"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="4363331" cy="1438977"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>159372</colOff>
-      <row>0</row>
-      <rowOff>3197</rowOff>
-    </from>
-    <to>
-      <col>51</col>
-      <colOff>162256</colOff>
-      <row>7</row>
-      <rowOff>167384</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Grafik 9"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>159372</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3197</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>162256</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167384</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Grafik 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId21"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5040135" y="3197"/>
           <a:ext cx="4365846" cy="1439514"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>22374</colOff>
-      <row>36</row>
-      <rowOff>139679</rowOff>
-    </from>
-    <to>
-      <col>51</col>
-      <colOff>158020</colOff>
-      <row>37</row>
-      <rowOff>160826</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Grafik 13"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>22374</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>139679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>158020</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>160826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Grafik 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId22"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5075738" y="6698505"/>
           <a:ext cx="4326007" cy="203336"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>46</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Grafik 5"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Grafik 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId23"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="6877050"/>
           <a:ext cx="4346153" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>46</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Grafik 44"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Grafik 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="6659104"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Grafik 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Grafik 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Grafik 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Grafik 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Grafik 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="13536154"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Grafik 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Grafik 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Grafik 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Grafik 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Grafik 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Grafik 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Grafik 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Grafik 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>348</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Grafik 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>348</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Grafik 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>387</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Grafik 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>19178</xdr:colOff>
+      <xdr:row>387</xdr:row>
+      <xdr:rowOff>144004</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4312651" cy="203641"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Grafik 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19178" y="27290254"/>
+          <a:ext cx="4312651" cy="203641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Grafik 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId24"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="6877050"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>85</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Grafik 45"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Grafik 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId25"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="13754100"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>85</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Grafik 46"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Grafik 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId26"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="13754100"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>124</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Grafik 47"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Grafik 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId27"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="20631150"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>171450</colOff>
-      <row>117</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>125</row>
-      <rowOff>1407</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Grafik 48"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>1407</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Grafik 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId28"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5276850" y="20640675"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>156</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>163</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Grafik 50"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Grafik 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId29"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="27508200"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>156</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>163</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Grafik 51"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Grafik 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId30"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="27508200"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>202</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Grafik 52"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Grafik 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId31"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="34385250"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>202</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Grafik 53"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Grafik 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId32"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="34385250"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>234</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>241</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Grafik 54"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Grafik 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId33"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="41262300"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>234</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>241</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Grafik 55"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Grafik 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId34"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="41262300"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>273</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>280</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Grafik 56"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>280</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Grafik 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId35"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="48139350"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>273</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>280</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Grafik 57"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>280</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Grafik 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId36"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="48139350"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>312</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>319</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Grafik 58"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>312</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>319</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Grafik 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId37"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="55016400"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>312</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>319</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Grafik 59"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>312</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>319</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Grafik 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId38"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="55016400"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>351</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>24</col>
-      <colOff>2753</colOff>
-      <row>358</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Grafik 60"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>351</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>358</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Grafik 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId39"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="61893450"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>28</col>
-      <colOff>0</colOff>
-      <row>351</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>52</col>
-      <colOff>2753</colOff>
-      <row>358</row>
-      <rowOff>167142</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Grafik 61"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>351</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>2753</xdr:colOff>
+      <xdr:row>358</xdr:row>
+      <xdr:rowOff>167142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Grafik 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId40"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="5286375" y="61893450"/>
           <a:ext cx="4574753" cy="1433967"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>75</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Grafik 6"/>
-        <cNvPicPr>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38174</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>29419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Grafik 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="6659104"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>75</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Grafik 10"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>114</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Grafik 12"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>114</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Grafik 15"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>153</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Grafik 17"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>153</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Grafik 19"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="13536154"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>192</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Grafik 21"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>192</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Grafik 23"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>231</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Grafik 25"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>231</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Grafik 27"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>270</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Grafik 29"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>270</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Grafik 31"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>309</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Grafik 33"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>309</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Grafik 35"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>348</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Grafik 37"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>348</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Grafik 39"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>19178</colOff>
-      <row>387</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Grafik 41"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>28</col>
-      <colOff>19178</colOff>
-      <row>387</row>
-      <rowOff>144004</rowOff>
-    </from>
-    <ext cx="4312651" cy="203641"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Grafik 43"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="19178" y="27290254"/>
-          <a:ext cx="4312651" cy="203641"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>38174</colOff>
-      <row>19</row>
-      <rowOff>29419</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Grafik 8"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="219075" y="3495675"/>
           <a:ext cx="533474" cy="6049219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>2686050</colOff>
-      <row>8</row>
-      <rowOff>409575</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381322</colOff>
-      <row>19</row>
-      <rowOff>210289</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Grafik 9"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2686050</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381322</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>210289</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Grafik 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId2"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="10134600" y="4429125"/>
           <a:ext cx="1409897" cy="5296639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401762</colOff>
-      <row>4</row>
-      <rowOff>19336</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Grafik 32"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401762</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19336</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Grafik 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId3"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="190500" y="0"/>
           <a:ext cx="11374437" cy="2048161"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>228600</colOff>
-      <row>0</row>
-      <rowOff>19050</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>28647</colOff>
-      <row>8</row>
-      <rowOff>276822</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Grafik 33"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28647</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>276822</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Grafik 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId4"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="228600" y="19050"/>
           <a:ext cx="514422" cy="4277322"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>6</row>
-      <rowOff>400050</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392232</colOff>
-      <row>9</row>
-      <rowOff>114452</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Grafik 34"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392232</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Grafik 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId5"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="219075" y="3486150"/>
           <a:ext cx="11336332" cy="1086002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>542925</colOff>
-      <row>4</row>
-      <rowOff>495300</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1267607</colOff>
-      <row>5</row>
-      <rowOff>276269</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Grafik 36"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>495300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1267607</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>276269</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Grafik 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId6"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="542925" y="2524125"/>
           <a:ext cx="5601482" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>3914775</colOff>
-      <row>2</row>
-      <rowOff>476250</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1562353</colOff>
-      <row>7</row>
-      <rowOff>219379</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Grafik 37"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3914775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1562353</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>219379</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Grafik 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId7"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="4629150" y="1533525"/>
           <a:ext cx="1810003" cy="2181529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>5</row>
-      <rowOff>466725</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>810379</colOff>
-      <row>6</row>
-      <rowOff>181008</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Grafik 38"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>466725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>810379</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>181008</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Grafik 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId8"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="285750" y="3028950"/>
           <a:ext cx="5401429" cy="238158"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>942975</colOff>
-      <row>2</row>
-      <rowOff>161925</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381186</colOff>
-      <row>7</row>
-      <rowOff>209897</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Grafik 39"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381186</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>209897</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Grafik 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId9"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="11106150" y="1219200"/>
           <a:ext cx="438211" cy="2486372"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1019175</colOff>
-      <row>5</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1277124</colOff>
-      <row>5</row>
-      <rowOff>447718</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Grafik 40"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1277124</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>447718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Grafik 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId10"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5895975" y="2705100"/>
           <a:ext cx="5544324" cy="304843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1047750</colOff>
-      <row>3</row>
-      <rowOff>209550</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1172330</colOff>
-      <row>4</row>
-      <rowOff>200091</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Grafik 41"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1172330</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>200091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Grafik 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId11"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5924550" y="1752600"/>
           <a:ext cx="5410955" cy="476316"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>200025</colOff>
-      <row>19</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392235</colOff>
-      <row>20</row>
-      <rowOff>304908</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Grafik 42"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392235</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>304908</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Grafik 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId12"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="200025" y="9572625"/>
           <a:ext cx="11355385" cy="771633"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>20</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>857443</colOff>
-      <row>27</row>
-      <rowOff>95632</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Grafik 43"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857443</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95632</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Grafik 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId13"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="190500" y="10096500"/>
           <a:ext cx="1381318" cy="2734057"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>23</row>
-      <rowOff>342900</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>2058344</colOff>
-      <row>25</row>
-      <rowOff>219168</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Grafik 44"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2058344</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>219168</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Grafik 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId14"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="171450" y="11563350"/>
           <a:ext cx="6763694" cy="666843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>876300</colOff>
-      <row>20</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1076353</colOff>
-      <row>25</row>
-      <rowOff>19321</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Grafik 45"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1076353</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19321</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Grafik 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId15"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5753100" y="10086975"/>
           <a:ext cx="200053" cy="1943371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>2057400</colOff>
-      <row>24</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>276335</colOff>
-      <row>25</row>
-      <rowOff>28619</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Grafik 47"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2057400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>276335</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Grafik 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId16"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="6934200" y="11725275"/>
           <a:ext cx="790685" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>209550</colOff>
-      <row>24</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1372141</colOff>
-      <row>27</row>
-      <rowOff>85847</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Grafik 48"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1372141</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>85847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Grafik 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId17"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="7658100" y="11944350"/>
           <a:ext cx="3877216" cy="876422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>904875</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1409770</colOff>
-      <row>25</row>
-      <rowOff>200327</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Grafik 49"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>904875</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1409770</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>200327</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Grafik 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId18"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="11068050" y="10048875"/>
           <a:ext cx="504895" cy="2162477"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>25</row>
-      <rowOff>60846</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401749</colOff>
-      <row>27</row>
-      <rowOff>97346</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Grafik 51"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>60846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401749</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>97346</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Grafik 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId19"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="285750" y="12071871"/>
           <a:ext cx="11279174" cy="760400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>2679539</colOff>
-      <row>25</row>
-      <rowOff>265132</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1422442</colOff>
-      <row>42</row>
-      <rowOff>94584</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Grafik 55"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2679539</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>265132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1422442</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>94584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Grafik 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId20"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="10127727" y="12267838"/>
           <a:ext cx="1458493" cy="4727593"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>284664</colOff>
-      <row>31</row>
-      <rowOff>54852</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>590925</colOff>
-      <row>32</row>
-      <rowOff>45363</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Grafik 56"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>284664</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>54852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>590925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>45363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Grafik 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId21"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="284664" y="13742518"/>
           <a:ext cx="10470280" cy="255764"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>841214</colOff>
-      <row>27</row>
-      <rowOff>43899</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>993635</colOff>
-      <row>42</row>
-      <rowOff>111408</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Grafik 57"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>841214</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>43899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>993635</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>111408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Grafik 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId22"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5718255" y="12770022"/>
           <a:ext cx="152421" cy="4242233"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>192234</colOff>
-      <row>29</row>
-      <rowOff>7900</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>946233</colOff>
-      <row>30</row>
-      <rowOff>55561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Grafik 59"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>192234</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>7900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>946233</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>55561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Grafik 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId23"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="192234" y="13162046"/>
           <a:ext cx="10918018" cy="258657"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>180975</colOff>
-      <row>33</row>
-      <rowOff>14208</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>830184</colOff>
-      <row>34</row>
-      <rowOff>99972</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Grafik 61"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>14208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>830184</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>99972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Grafik 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId24"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="180975" y="14301708"/>
           <a:ext cx="10813228" cy="275661"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>193031</colOff>
-      <row>39</row>
-      <rowOff>312275</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>594555</colOff>
-      <row>42</row>
-      <rowOff>112568</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Grafik 62"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>193031</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>312275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>594555</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>112568</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Grafik 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId25"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="193031" y="16462576"/>
           <a:ext cx="10565543" cy="550839"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>26</row>
-      <rowOff>197975</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>285766</colOff>
-      <row>40</row>
-      <rowOff>198561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Grafik 63"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>197975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285766</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>198561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Grafik 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId26"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="171450" y="12523204"/>
           <a:ext cx="114316" cy="4196409"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>304800</colOff>
-      <row>39</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1028801</colOff>
-      <row>39</row>
-      <rowOff>314362</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Grafik 64"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1028801</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>314362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Grafik 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId27"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="1019175" y="16211550"/>
           <a:ext cx="724001" cy="266737"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>38174</colOff>
-      <row>62</row>
-      <rowOff>29419</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Grafik 1"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38174</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>29419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId28"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId113"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="219075" y="3495675"/>
           <a:ext cx="533474" cy="6049219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>2686050</colOff>
-      <row>51</row>
-      <rowOff>409575</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381322</colOff>
-      <row>62</row>
-      <rowOff>210289</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Grafik 2"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2686050</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381322</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>210289</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId29"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId110"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="10134600" y="4429125"/>
           <a:ext cx="1409897" cy="5296639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401762</colOff>
-      <row>47</row>
-      <rowOff>19336</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Grafik 3"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401762</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>19336</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Grafik 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId30"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId104"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="190500" y="0"/>
           <a:ext cx="11374437" cy="2048161"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>228600</colOff>
-      <row>43</row>
-      <rowOff>19050</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>28647</colOff>
-      <row>51</row>
-      <rowOff>276822</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Grafik 4"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28647</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>276822</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Grafik 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId31"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="228600" y="19050"/>
           <a:ext cx="514422" cy="4277322"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>49</row>
-      <rowOff>400050</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392232</colOff>
-      <row>52</row>
-      <rowOff>114452</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Grafik 5"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392232</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>114452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Grafik 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId32"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId117"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="219075" y="3486150"/>
           <a:ext cx="11336332" cy="1086002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>542925</colOff>
-      <row>47</row>
-      <rowOff>495300</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1267607</colOff>
-      <row>48</row>
-      <rowOff>276269</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Grafik 6"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>495300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1267607</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>276269</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Grafik 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId33"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId114"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="542925" y="2524125"/>
           <a:ext cx="5601482" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>3914775</colOff>
-      <row>45</row>
-      <rowOff>476250</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1562353</colOff>
-      <row>50</row>
-      <rowOff>219379</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Grafik 7"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3914775</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1562353</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>219379</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Grafik 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId34"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId106"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="4629150" y="1533525"/>
           <a:ext cx="1810003" cy="2181529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>48</row>
-      <rowOff>466725</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>810379</colOff>
-      <row>49</row>
-      <rowOff>181008</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Grafik 8"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>466725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>810379</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>181008</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Grafik 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId35"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="285750" y="3028950"/>
           <a:ext cx="5401429" cy="238158"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>942975</colOff>
-      <row>45</row>
-      <rowOff>161925</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1381186</colOff>
-      <row>50</row>
-      <rowOff>209897</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Grafik 9"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1381186</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>209897</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Grafik 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId36"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId123"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="11106150" y="1219200"/>
           <a:ext cx="438211" cy="2486372"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1019175</colOff>
-      <row>48</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1277124</colOff>
-      <row>48</row>
-      <rowOff>447718</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Grafik 10"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1277124</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>447718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Grafik 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId37"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5895975" y="2705100"/>
           <a:ext cx="5544324" cy="304843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1047750</colOff>
-      <row>46</row>
-      <rowOff>209550</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1172330</colOff>
-      <row>47</row>
-      <rowOff>200091</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Grafik 11"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1172330</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>200091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Grafik 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId38"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId115"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5924550" y="1752600"/>
           <a:ext cx="5410955" cy="476316"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>200025</colOff>
-      <row>62</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1392235</colOff>
-      <row>63</row>
-      <rowOff>304908</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Grafik 12"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1392235</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>304908</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Grafik 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId39"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId107"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="200025" y="9582150"/>
           <a:ext cx="11355385" cy="771633"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>190500</colOff>
-      <row>63</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>857443</colOff>
-      <row>70</row>
-      <rowOff>95632</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Grafik 13"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857443</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>95632</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Grafik 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId40"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="190500" y="10096500"/>
           <a:ext cx="1381318" cy="2734057"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>66</row>
-      <rowOff>342900</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>2058344</colOff>
-      <row>68</row>
-      <rowOff>219168</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Grafik 14"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2058344</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>219168</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Grafik 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId41"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="171450" y="11563350"/>
           <a:ext cx="6763694" cy="666843"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>876300</colOff>
-      <row>63</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1076353</colOff>
-      <row>68</row>
-      <rowOff>19321</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Grafik 15"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1076353</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>19321</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Grafik 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId42"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5753100" y="10086975"/>
           <a:ext cx="200053" cy="1943371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>2057400</colOff>
-      <row>67</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>276335</colOff>
-      <row>68</row>
-      <rowOff>28619</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Grafik 16"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2057400</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>276335</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>28619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Grafik 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId43"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="6934200" y="11725275"/>
           <a:ext cx="790685" cy="314369"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>209550</colOff>
-      <row>67</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1372141</colOff>
-      <row>70</row>
-      <rowOff>85847</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Grafik 17"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1372141</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>85847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Grafik 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId44"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="7658100" y="11944350"/>
           <a:ext cx="3877216" cy="876422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>904875</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1409770</colOff>
-      <row>68</row>
-      <rowOff>200327</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Grafik 18"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>904875</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1409770</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>200327</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Grafik 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId45"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId102"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="11068050" y="10048875"/>
           <a:ext cx="504895" cy="2162477"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>285750</colOff>
-      <row>68</row>
-      <rowOff>60846</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1401749</colOff>
-      <row>70</row>
-      <rowOff>97346</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Grafik 19"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>60846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1401749</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>97346</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Grafik 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId46"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId121"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="285750" y="12071871"/>
           <a:ext cx="11279174" cy="760400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>3</col>
-      <colOff>2679539</colOff>
-      <row>68</row>
-      <rowOff>265132</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>3217</colOff>
-      <row>85</row>
-      <rowOff>94584</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Grafik 20"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2679539</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>265132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3217</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>94584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Grafik 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId47"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="10128089" y="12276157"/>
           <a:ext cx="1457528" cy="4734827"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>284664</colOff>
-      <row>74</row>
-      <rowOff>54852</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>590925</colOff>
-      <row>75</row>
-      <rowOff>45363</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Grafik 21"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>284664</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>54852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>590925</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>45363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Grafik 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId48"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId105"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="284664" y="13751802"/>
           <a:ext cx="10469436" cy="257211"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>841214</colOff>
-      <row>70</row>
-      <rowOff>43899</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>993635</colOff>
-      <row>85</row>
-      <rowOff>111408</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Grafik 22"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>841214</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>43899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>993635</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>111408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Grafik 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId49"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId125"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="5718014" y="12778824"/>
           <a:ext cx="152421" cy="4248984"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>192234</colOff>
-      <row>72</row>
-      <rowOff>7900</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>946233</colOff>
-      <row>73</row>
-      <rowOff>55561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Grafik 23"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>192234</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>7900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>946233</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>55561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Grafik 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId50"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId119"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="192234" y="13171450"/>
           <a:ext cx="10917174" cy="257211"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>180975</colOff>
-      <row>76</row>
-      <rowOff>14208</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>830184</colOff>
-      <row>77</row>
-      <rowOff>99972</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Grafik 24"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>14208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>830184</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>99972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Grafik 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId51"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId116"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="180975" y="14311233"/>
           <a:ext cx="10812384" cy="276264"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>193031</colOff>
-      <row>82</row>
-      <rowOff>312275</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>594555</colOff>
-      <row>85</row>
-      <rowOff>112568</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Grafik 25"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>193031</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>312275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>594555</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>112568</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Grafik 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId52"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="193031" y="16476200"/>
           <a:ext cx="10564699" cy="552768"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>171450</colOff>
-      <row>69</row>
-      <rowOff>197975</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>285766</colOff>
-      <row>83</row>
-      <rowOff>198561</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Grafik 26"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>197975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285766</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>198561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Grafik 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId53"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId103"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="171450" y="12532850"/>
           <a:ext cx="114316" cy="4201111"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>304800</colOff>
-      <row>82</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1028801</colOff>
-      <row>82</row>
-      <rowOff>314362</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Grafik 27"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1028801</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>314362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Grafik 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId54"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="1019175" y="16211550"/>
           <a:ext cx="724001" cy="266737"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4882,8 +5419,6 @@
           <t>Mercedes-Benz AG, PKW-Werk Rastatt</t>
         </is>
       </c>
-      <c r="D6" s="73" t="n"/>
-      <c r="E6" s="74" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="22" t="inlineStr">
@@ -5174,22 +5709,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="001B5E20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BE390"/>
+  <dimension ref="A1:BE388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col width="2.7109375" customWidth="1" style="5" min="1" max="25"/>
-    <col width="2.42578125" customWidth="1" style="5" min="26" max="27"/>
-    <col width="2.5703125" customWidth="1" style="5" min="28" max="28"/>
-    <col width="2.7109375" customWidth="1" style="5" min="29" max="52"/>
-    <col width="9.140625" customWidth="1" style="1" min="53" max="56"/>
-    <col width="10.140625" bestFit="1" customWidth="1" style="1" min="57" max="57"/>
-    <col width="9.140625" customWidth="1" style="1" min="58" max="16384"/>
+    <col min="1" max="25" width="2.7109375" style="5" customWidth="1"/>
+    <col min="26" max="27" width="2.42578125" style="5" customWidth="1"/>
+    <col min="28" max="28" width="2.5703125" style="5" customWidth="1"/>
+    <col min="29" max="52" width="2.7109375" style="5" customWidth="1"/>
+    <col min="53" max="56" width="9.140625" style="1"/>
+    <col min="57" max="57" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -5732,7 +6267,6 @@
       <c r="K27" s="11" t="n"/>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>
-      <c r="O27" s="16" t="n"/>
       <c r="P27" s="38" t="n"/>
       <c r="Q27" s="38" t="n"/>
       <c r="R27" s="38" t="n"/>
@@ -5754,7 +6288,6 @@
       <c r="AM27" s="11" t="n"/>
       <c r="AN27" s="11" t="n"/>
       <c r="AO27" s="11" t="n"/>
-      <c r="AQ27" s="16" t="n"/>
       <c r="AR27" s="38" t="n"/>
       <c r="AS27" s="38" t="n"/>
       <c r="AT27" s="38" t="n"/>
@@ -5869,19 +6402,20 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC39" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
@@ -6416,7 +6950,6 @@
       <c r="K66" s="11" t="n"/>
       <c r="L66" s="11" t="n"/>
       <c r="M66" s="11" t="n"/>
-      <c r="O66" s="16" t="n"/>
       <c r="P66" s="38" t="n"/>
       <c r="Q66" s="38" t="n"/>
       <c r="R66" s="38" t="n"/>
@@ -6437,7 +6970,6 @@
       <c r="AM66" s="11" t="n"/>
       <c r="AN66" s="11" t="n"/>
       <c r="AO66" s="11" t="n"/>
-      <c r="AQ66" s="16" t="n"/>
       <c r="AR66" s="38" t="n"/>
       <c r="AS66" s="38" t="n"/>
       <c r="AT66" s="38" t="n"/>
@@ -6552,19 +7084,20 @@
         </is>
       </c>
     </row>
+    <row r="78" ht="14.25" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC78" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="77"/>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="78"/>
     <row r="79"/>
     <row r="80"/>
     <row r="81"/>
@@ -7099,7 +7632,6 @@
       <c r="K105" s="11" t="n"/>
       <c r="L105" s="11" t="n"/>
       <c r="M105" s="11" t="n"/>
-      <c r="O105" s="16" t="n"/>
       <c r="P105" s="38" t="n"/>
       <c r="Q105" s="38" t="n"/>
       <c r="R105" s="38" t="n"/>
@@ -7120,7 +7652,6 @@
       <c r="AM105" s="11" t="n"/>
       <c r="AN105" s="11" t="n"/>
       <c r="AO105" s="11" t="n"/>
-      <c r="AQ105" s="16" t="n"/>
       <c r="AR105" s="38" t="n"/>
       <c r="AS105" s="38" t="n"/>
       <c r="AT105" s="38" t="n"/>
@@ -7235,19 +7766,20 @@
         </is>
       </c>
     </row>
+    <row r="117" ht="14.25" customHeight="1">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC117" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="116"/>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="117"/>
     <row r="118"/>
     <row r="119"/>
     <row r="120"/>
@@ -7782,7 +8314,6 @@
       <c r="K144" s="11" t="n"/>
       <c r="L144" s="11" t="n"/>
       <c r="M144" s="11" t="n"/>
-      <c r="O144" s="16" t="n"/>
       <c r="P144" s="38" t="n"/>
       <c r="Q144" s="38" t="n"/>
       <c r="R144" s="38" t="n"/>
@@ -7803,7 +8334,6 @@
       <c r="AM144" s="11" t="n"/>
       <c r="AN144" s="11" t="n"/>
       <c r="AO144" s="11" t="n"/>
-      <c r="AQ144" s="16" t="n"/>
       <c r="AR144" s="38" t="n"/>
       <c r="AS144" s="38" t="n"/>
       <c r="AT144" s="38" t="n"/>
@@ -7918,19 +8448,20 @@
         </is>
       </c>
     </row>
+    <row r="156" ht="14.25" customHeight="1">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC156" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="155"/>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="156"/>
     <row r="157"/>
     <row r="158"/>
     <row r="159"/>
@@ -8465,7 +8996,6 @@
       <c r="K183" s="11" t="n"/>
       <c r="L183" s="11" t="n"/>
       <c r="M183" s="11" t="n"/>
-      <c r="O183" s="16" t="n"/>
       <c r="P183" s="38" t="n"/>
       <c r="Q183" s="38" t="n"/>
       <c r="R183" s="38" t="n"/>
@@ -8486,7 +9016,6 @@
       <c r="AM183" s="11" t="n"/>
       <c r="AN183" s="11" t="n"/>
       <c r="AO183" s="11" t="n"/>
-      <c r="AQ183" s="16" t="n"/>
       <c r="AR183" s="38" t="n"/>
       <c r="AS183" s="38" t="n"/>
       <c r="AT183" s="38" t="n"/>
@@ -8601,19 +9130,20 @@
         </is>
       </c>
     </row>
+    <row r="195" ht="14.25" customHeight="1">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC195" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="194"/>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="195"/>
     <row r="196"/>
     <row r="197"/>
     <row r="198"/>
@@ -9148,7 +9678,6 @@
       <c r="K222" s="11" t="n"/>
       <c r="L222" s="11" t="n"/>
       <c r="M222" s="11" t="n"/>
-      <c r="O222" s="16" t="n"/>
       <c r="P222" s="38" t="n"/>
       <c r="Q222" s="38" t="n"/>
       <c r="R222" s="38" t="n"/>
@@ -9169,7 +9698,6 @@
       <c r="AM222" s="11" t="n"/>
       <c r="AN222" s="11" t="n"/>
       <c r="AO222" s="11" t="n"/>
-      <c r="AQ222" s="16" t="n"/>
       <c r="AR222" s="38" t="n"/>
       <c r="AS222" s="38" t="n"/>
       <c r="AT222" s="38" t="n"/>
@@ -9284,19 +9812,20 @@
         </is>
       </c>
     </row>
+    <row r="234" ht="14.25" customHeight="1">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC234" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="233"/>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="234"/>
     <row r="235"/>
     <row r="236"/>
     <row r="237"/>
@@ -9831,7 +10360,6 @@
       <c r="K261" s="11" t="n"/>
       <c r="L261" s="11" t="n"/>
       <c r="M261" s="11" t="n"/>
-      <c r="O261" s="16" t="n"/>
       <c r="P261" s="38" t="n"/>
       <c r="Q261" s="38" t="n"/>
       <c r="R261" s="38" t="n"/>
@@ -9852,7 +10380,6 @@
       <c r="AM261" s="11" t="n"/>
       <c r="AN261" s="11" t="n"/>
       <c r="AO261" s="11" t="n"/>
-      <c r="AQ261" s="16" t="n"/>
       <c r="AR261" s="38" t="n"/>
       <c r="AS261" s="38" t="n"/>
       <c r="AT261" s="38" t="n"/>
@@ -9967,19 +10494,20 @@
         </is>
       </c>
     </row>
+    <row r="273" ht="14.25" customHeight="1">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC273" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="272"/>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="273"/>
     <row r="274"/>
     <row r="275"/>
     <row r="276"/>
@@ -10514,7 +11042,6 @@
       <c r="K300" s="11" t="n"/>
       <c r="L300" s="11" t="n"/>
       <c r="M300" s="11" t="n"/>
-      <c r="O300" s="16" t="n"/>
       <c r="P300" s="38" t="n"/>
       <c r="Q300" s="38" t="n"/>
       <c r="R300" s="38" t="n"/>
@@ -10535,7 +11062,6 @@
       <c r="AM300" s="11" t="n"/>
       <c r="AN300" s="11" t="n"/>
       <c r="AO300" s="11" t="n"/>
-      <c r="AQ300" s="16" t="n"/>
       <c r="AR300" s="38" t="n"/>
       <c r="AS300" s="38" t="n"/>
       <c r="AT300" s="38" t="n"/>
@@ -10650,19 +11176,20 @@
         </is>
       </c>
     </row>
+    <row r="312" ht="14.25" customHeight="1">
+      <c r="A312" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC312" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="311"/>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="312"/>
     <row r="313"/>
     <row r="314"/>
     <row r="315"/>
@@ -11197,7 +11724,6 @@
       <c r="K339" s="11" t="n"/>
       <c r="L339" s="11" t="n"/>
       <c r="M339" s="11" t="n"/>
-      <c r="O339" s="16" t="n"/>
       <c r="P339" s="38" t="n"/>
       <c r="Q339" s="38" t="n"/>
       <c r="R339" s="38" t="n"/>
@@ -11218,7 +11744,6 @@
       <c r="AM339" s="11" t="n"/>
       <c r="AN339" s="11" t="n"/>
       <c r="AO339" s="11" t="n"/>
-      <c r="AQ339" s="16" t="n"/>
       <c r="AR339" s="38" t="n"/>
       <c r="AS339" s="38" t="n"/>
       <c r="AT339" s="38" t="n"/>
@@ -11333,19 +11858,20 @@
         </is>
       </c>
     </row>
+    <row r="351" ht="14.25" customHeight="1">
+      <c r="A351" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+      <c r="AC351" s="9" t="inlineStr">
+        <is>
+          <t>Stand Oktober 2023</t>
+        </is>
+      </c>
+    </row>
     <row r="350"/>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-      <c r="AC351" t="inlineStr">
-        <is>
-          <t>Stand Oktober 2023</t>
-        </is>
-      </c>
-    </row>
+    <row r="351"/>
     <row r="352"/>
     <row r="353"/>
     <row r="354"/>
@@ -11880,7 +12406,6 @@
       <c r="K378" s="11" t="n"/>
       <c r="L378" s="11" t="n"/>
       <c r="M378" s="11" t="n"/>
-      <c r="O378" s="16" t="n"/>
       <c r="P378" s="38" t="n"/>
       <c r="Q378" s="38" t="n"/>
       <c r="R378" s="38" t="n"/>
@@ -11901,7 +12426,6 @@
       <c r="AM378" s="11" t="n"/>
       <c r="AN378" s="11" t="n"/>
       <c r="AO378" s="11" t="n"/>
-      <c r="AQ378" s="16" t="n"/>
       <c r="AR378" s="38" t="n"/>
       <c r="AS378" s="38" t="n"/>
       <c r="AT378" s="38" t="n"/>
@@ -12016,13 +12540,13 @@
         </is>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
+    <row r="390" ht="14.25" customHeight="1">
+      <c r="A390" s="9" t="inlineStr">
         <is>
           <t>Stand Oktober 2023</t>
         </is>
       </c>
-      <c r="AC390" t="inlineStr">
+      <c r="AC390" s="9" t="inlineStr">
         <is>
           <t>Stand Oktober 2023</t>
         </is>
@@ -12291,8 +12815,8 @@
     <mergeCell ref="I140:M140"/>
     <mergeCell ref="AV128:AZ128"/>
   </mergeCells>
-  <pageMargins left="0.3149606299212598" right="0.3149606299212598" top="0.3937007874015748" bottom="0.3937007874015748" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="10" fitToWidth="1"/>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="10" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"CorpoS"&amp;1 &amp;K000000Internal#</oddHeader>
     <oddFooter/>
@@ -12312,18 +12836,18 @@
     <brk id="311" min="0" max="16383" man="1"/>
     <brk id="350" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J83"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" customWidth="1" min="1" max="1"/>
@@ -12590,6 +13114,8 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36" ht="29.25" customHeight="1">
       <c r="C36" s="54" t="inlineStr">
         <is>
@@ -12888,6 +13414,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79" ht="29.25" customHeight="1">
       <c r="C79" s="54" t="inlineStr">
         <is>
@@ -12935,9 +13463,9 @@
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C72:D72"/>
     <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C80:D80"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C76:D76"/>
@@ -12954,7 +13482,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="43" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
